--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:18</v>
@@ -515,7 +515,7 @@
         <v>Mark Ronson - Live at The BRIT Awards 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>7:20</v>
       </c>
       <c r="H4" t="str">
-        <v>Mark Ronson</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,7 +545,7 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 - Mark Ronson</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         <v>HUNTR/ X Perform Golden | The BRIT Awards 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:01</v>
@@ -591,7 +591,7 @@
         <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:31</v>
       </c>
       <c r="H6" t="str">
-        <v>Olivia Dean</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,7 +621,7 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="7">
@@ -629,7 +629,7 @@
         <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B7" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:00</v>
@@ -667,7 +667,7 @@
         <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B8" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:11</v>
@@ -1123,7 +1123,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>5:12</v>
@@ -2225,7 +2225,7 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B49" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>2:28</v>
@@ -2377,7 +2377,7 @@
         <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B53" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>4:49</v>
@@ -2605,7 +2605,7 @@
         <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B59" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>5:32</v>
@@ -2719,7 +2719,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B62" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:57</v>
@@ -3137,7 +3137,7 @@
         <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>3:20</v>
@@ -3365,7 +3365,7 @@
         <v>Suburban Requiem</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>4:40</v>
@@ -3973,7 +3973,7 @@
         <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B95" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
         <v>5:38</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>9 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>9 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:18</v>
@@ -515,7 +515,7 @@
         <v>Mark Ronson - Live at The BRIT Awards 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>7:20</v>
@@ -550,10 +550,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HUNTR/ X Perform Golden | The BRIT Awards 2026</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B5" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:01</v>
@@ -583,7 +583,7 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>HUNTR/ X Perform Golden | The BRIT Awards 2026 - BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +591,7 @@
         <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>13 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>13 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:31</v>
@@ -629,7 +629,7 @@
         <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B7" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:00</v>
@@ -1009,7 +1009,7 @@
         <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:05</v>
@@ -1047,7 +1047,7 @@
         <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:59</v>
@@ -1085,7 +1085,7 @@
         <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:55</v>
@@ -1845,7 +1845,7 @@
         <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>4:50</v>
@@ -2149,7 +2149,7 @@
         <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B47" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:22</v>
@@ -2187,7 +2187,7 @@
         <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B48" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:53</v>
@@ -2453,7 +2453,7 @@
         <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B55" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>2:59</v>
@@ -2795,7 +2795,7 @@
         <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B64" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>4:49</v>
@@ -3897,7 +3897,7 @@
         <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:06</v>
@@ -3935,7 +3935,7 @@
         <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B94" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>3:01</v>
@@ -4201,7 +4201,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B101" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>5:24</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-01</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>LIVE</v>
+        <v>4:30</v>
       </c>
       <c r="H2" t="str">
-        <v>BRITs</v>
+        <v>Jessie J</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-01</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>5:18</v>
+        <v>LIVE</v>
       </c>
       <c r="H3" t="str">
-        <v>Harry Styles</v>
+        <v>BRITs</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B4" t="str">
         <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-01</v>
@@ -530,10 +530,10 @@
         <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>7:20</v>
+        <v>5:18</v>
       </c>
       <c r="H4" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 - Mark Ronson and BRITs</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-01</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:01</v>
+        <v>7:20</v>
       </c>
       <c r="H5" t="str">
-        <v>BRITs</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B6" t="str">
         <v>16 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-01</v>
@@ -606,10 +606,10 @@
         <v>16 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:31</v>
+        <v>3:01</v>
       </c>
       <c r="H6" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-01</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H7" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-01</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:11</v>
+        <v>3:00</v>
       </c>
       <c r="H8" t="str">
-        <v>The Kiffness</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-01</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:32</v>
+        <v>3:11</v>
       </c>
       <c r="H9" t="str">
-        <v>Lauv</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-01</v>
@@ -758,10 +758,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>5:03</v>
+        <v>3:32</v>
       </c>
       <c r="H10" t="str">
-        <v>RAYE</v>
+        <v>Lauv</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-01</v>
@@ -796,10 +796,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:50</v>
+        <v>5:03</v>
       </c>
       <c r="H11" t="str">
-        <v>Armik</v>
+        <v>RAYE</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B12" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-01</v>
@@ -834,10 +834,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:53</v>
+        <v>4:50</v>
       </c>
       <c r="H12" t="str">
-        <v>Scorpions</v>
+        <v>Armik</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-01</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:04</v>
+        <v>4:53</v>
       </c>
       <c r="H13" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Scorpions</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-01</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:32</v>
+        <v>3:04</v>
       </c>
       <c r="H14" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-01</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:47</v>
+        <v>4:32</v>
       </c>
       <c r="H15" t="str">
-        <v>Girl Tones</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-01</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:40</v>
+        <v>3:47</v>
       </c>
       <c r="H16" t="str">
-        <v>Jessie Ware</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026) - Jessie Ware</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-01</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:05</v>
+        <v>3:40</v>
       </c>
       <c r="H17" t="str">
-        <v>HAUSER</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-01</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:59</v>
+        <v>4:05</v>
       </c>
       <c r="H18" t="str">
-        <v>Queen Official</v>
+        <v>HAUSER</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-01</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:55</v>
+        <v>2:59</v>
       </c>
       <c r="H19" t="str">
-        <v>Tenille Townes</v>
+        <v>Queen Official</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-01</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>5:12</v>
+        <v>3:55</v>
       </c>
       <c r="H20" t="str">
-        <v>Self Esteem</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-01</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:47</v>
+        <v>5:12</v>
       </c>
       <c r="H21" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-01</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:18</v>
+        <v>3:47</v>
       </c>
       <c r="H22" t="str">
-        <v>Em Beihold</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-01</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:50</v>
+        <v>3:18</v>
       </c>
       <c r="H23" t="str">
-        <v>Michael Bublé</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-01</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:24</v>
+        <v>3:50</v>
       </c>
       <c r="H24" t="str">
-        <v>MyKey</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-01</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:36</v>
+        <v>3:24</v>
       </c>
       <c r="H25" t="str">
-        <v>Max McNown</v>
+        <v>MyKey</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-01</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:34</v>
+        <v>2:36</v>
       </c>
       <c r="H26" t="str">
-        <v>Megan Moroney</v>
+        <v>Max McNown</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-01</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:03</v>
+        <v>3:34</v>
       </c>
       <c r="H27" t="str">
-        <v>ERNEST</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-01</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:31</v>
+        <v>4:03</v>
       </c>
       <c r="H28" t="str">
-        <v>Bruno Mars</v>
+        <v>ERNEST</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-01</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:22</v>
+        <v>3:31</v>
       </c>
       <c r="H29" t="str">
-        <v>BLACKPINK</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-01</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>5:49</v>
+        <v>3:22</v>
       </c>
       <c r="H30" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-01</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:47</v>
+        <v>5:49</v>
       </c>
       <c r="H31" t="str">
-        <v>Nessa Barrett</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-01</v>
@@ -1594,10 +1594,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:20</v>
+        <v>3:47</v>
       </c>
       <c r="H32" t="str">
-        <v>Towa Bird</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-01</v>
@@ -1632,10 +1632,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:18</v>
+        <v>2:20</v>
       </c>
       <c r="H33" t="str">
-        <v>Ty Myers</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-01</v>
@@ -1670,10 +1670,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:39</v>
+        <v>4:18</v>
       </c>
       <c r="H34" t="str">
-        <v>kenzie</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B35" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-01</v>
@@ -1708,10 +1708,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:52</v>
+        <v>2:39</v>
       </c>
       <c r="H35" t="str">
-        <v>Leanna Crawford</v>
+        <v>kenzie</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B36" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-01</v>
@@ -1746,10 +1746,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:01</v>
+        <v>3:52</v>
       </c>
       <c r="H36" t="str">
-        <v>Bryan Adams</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B37" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-01</v>
@@ -1784,10 +1784,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:54</v>
+        <v>4:01</v>
       </c>
       <c r="H37" t="str">
-        <v>CHESCA</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B38" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-01</v>
@@ -1822,10 +1822,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:03</v>
+        <v>2:54</v>
       </c>
       <c r="H38" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CHESCA</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-01</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:50</v>
+        <v>4:03</v>
       </c>
       <c r="H39" t="str">
-        <v>earMUSIC</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B40" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-01</v>
@@ -1898,10 +1898,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:06</v>
+        <v>4:50</v>
       </c>
       <c r="H40" t="str">
-        <v>Y2K</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B41" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-01</v>
@@ -1936,10 +1936,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:43</v>
+        <v>3:06</v>
       </c>
       <c r="H41" t="str">
-        <v>Lainey Wilson</v>
+        <v>Y2K</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B42" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-01</v>
@@ -1974,10 +1974,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>6:21</v>
+        <v>2:43</v>
       </c>
       <c r="H42" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B43" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-01</v>
@@ -2012,10 +2012,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:46</v>
+        <v>6:21</v>
       </c>
       <c r="H43" t="str">
-        <v>Bryan Ferry</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B44" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-01</v>
@@ -2050,10 +2050,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H44" t="str">
-        <v>Saint Harison</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B45" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:04</v>
+        <v>2:42</v>
       </c>
       <c r="H45" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:59</v>
+        <v>3:04</v>
       </c>
       <c r="H46" t="str">
-        <v>Catie Turner</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B47" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-01</v>
@@ -2164,10 +2164,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:22</v>
+        <v>2:59</v>
       </c>
       <c r="H47" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B48" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-01</v>
@@ -2202,10 +2202,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:53</v>
+        <v>2:22</v>
       </c>
       <c r="H48" t="str">
-        <v>Roxette</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B49" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-01</v>
@@ -2240,10 +2240,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:28</v>
+        <v>3:53</v>
       </c>
       <c r="H49" t="str">
-        <v>Marcin</v>
+        <v>Roxette</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B50" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-01</v>
@@ -2278,10 +2278,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:47</v>
+        <v>2:28</v>
       </c>
       <c r="H50" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Marcin</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B51" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-01</v>
@@ -2316,10 +2316,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:40</v>
+        <v>2:47</v>
       </c>
       <c r="H51" t="str">
-        <v>Laufey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B52" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-01</v>
@@ -2354,10 +2354,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:49</v>
+        <v>3:40</v>
       </c>
       <c r="H52" t="str">
-        <v>Ava Max</v>
+        <v>Laufey</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:49</v>
+        <v>2:49</v>
       </c>
       <c r="H53" t="str">
-        <v>U2</v>
+        <v>Ava Max</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B54" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-01</v>
@@ -2430,10 +2430,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:35</v>
+        <v>4:49</v>
       </c>
       <c r="H54" t="str">
-        <v>Taylor Swift</v>
+        <v>U2</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B55" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-01</v>
@@ -2468,10 +2468,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:59</v>
+        <v>3:35</v>
       </c>
       <c r="H55" t="str">
-        <v>Kiana Ledé</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B56" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-01</v>
@@ -2506,10 +2506,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:38</v>
+        <v>2:59</v>
       </c>
       <c r="H56" t="str">
-        <v>Jessie Ware</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B57" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-01</v>
@@ -2544,10 +2544,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:46</v>
+        <v>4:38</v>
       </c>
       <c r="H57" t="str">
-        <v>Madison Beer</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B58" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-01</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:08</v>
+        <v>3:46</v>
       </c>
       <c r="H58" t="str">
-        <v>Sean Stemaly</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-01</v>
@@ -2620,10 +2620,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>5:32</v>
+        <v>3:08</v>
       </c>
       <c r="H59" t="str">
-        <v>earMUSIC</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B60" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-01</v>
@@ -2658,10 +2658,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:39</v>
+        <v>5:32</v>
       </c>
       <c r="H60" t="str">
-        <v>georgemichael</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-01</v>
@@ -2696,10 +2696,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:40</v>
+        <v>4:39</v>
       </c>
       <c r="H61" t="str">
-        <v>Nothing But Thieves</v>
+        <v>georgemichael</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B62" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-01</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:57</v>
+        <v>3:40</v>
       </c>
       <c r="H62" t="str">
-        <v>Self Esteem</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B63" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-01</v>
@@ -2772,10 +2772,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:27</v>
+        <v>3:57</v>
       </c>
       <c r="H63" t="str">
-        <v>070 Shake</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-01</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:49</v>
+        <v>2:27</v>
       </c>
       <c r="H64" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-01</v>
@@ -2848,7 +2848,7 @@
         <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>5:52</v>
+        <v>4:49</v>
       </c>
       <c r="H65" t="str">
         <v>georgemichael</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B66" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-01</v>
@@ -2886,10 +2886,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:22</v>
+        <v>5:52</v>
       </c>
       <c r="H66" t="str">
-        <v>Foo Fighters</v>
+        <v>georgemichael</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B67" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-01</v>
@@ -2924,10 +2924,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:08</v>
+        <v>3:22</v>
       </c>
       <c r="H67" t="str">
-        <v>Romeo Santos and 2 more</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B68" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-01</v>
@@ -2962,10 +2962,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>7:31</v>
+        <v>4:08</v>
       </c>
       <c r="H68" t="str">
-        <v>Jacob Collier</v>
+        <v>Romeo Santos and 2 more</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B69" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-01</v>
@@ -3000,10 +3000,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:21</v>
+        <v>7:31</v>
       </c>
       <c r="H69" t="str">
-        <v>Gabi Sklar</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B70" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-01</v>
@@ -3038,10 +3038,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:36</v>
+        <v>3:21</v>
       </c>
       <c r="H70" t="str">
-        <v>YUNGBLUD</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-01</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>5:06</v>
+        <v>4:36</v>
       </c>
       <c r="H71" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:17</v>
+        <v>5:06</v>
       </c>
       <c r="H72" t="str">
-        <v>Marc Anthony and 2 more</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-01</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:20</v>
+        <v>4:17</v>
       </c>
       <c r="H73" t="str">
-        <v>georgemichael</v>
+        <v>Marc Anthony and 2 more</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-01</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:50</v>
+        <v>3:20</v>
       </c>
       <c r="H74" t="str">
-        <v>Cliff Richard</v>
+        <v>georgemichael</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-01</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:14</v>
+        <v>4:50</v>
       </c>
       <c r="H75" t="str">
-        <v>Freya Ridings</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-01</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:37</v>
+        <v>3:14</v>
       </c>
       <c r="H76" t="str">
-        <v>Jessie Ware</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-01</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:16</v>
+        <v>4:37</v>
       </c>
       <c r="H77" t="str">
-        <v>Alan Walker</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-01</v>
@@ -3342,10 +3342,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:22</v>
+        <v>3:16</v>
       </c>
       <c r="H78" t="str">
-        <v>The Neighbourhood</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Suburban Requiem</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-01</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:40</v>
+        <v>4:22</v>
       </c>
       <c r="H79" t="str">
-        <v>YUNGBLUD</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-01</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:02</v>
+        <v>4:40</v>
       </c>
       <c r="H80" t="str">
-        <v>Calum Scott</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B81" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-01</v>
@@ -3456,10 +3456,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H81" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-01</v>
@@ -3494,10 +3494,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:38</v>
+        <v>3:12</v>
       </c>
       <c r="H82" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B83" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-01</v>
@@ -3532,10 +3532,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:40</v>
+        <v>3:38</v>
       </c>
       <c r="H83" t="str">
-        <v>Cannons</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-01</v>
@@ -3570,10 +3570,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:57</v>
+        <v>4:40</v>
       </c>
       <c r="H84" t="str">
-        <v>Mimi Webb</v>
+        <v>Cannons</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-01</v>
@@ -3608,10 +3608,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:13</v>
+        <v>2:57</v>
       </c>
       <c r="H85" t="str">
-        <v>Jorja Smith</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B86" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-01</v>
@@ -3646,10 +3646,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:12</v>
+        <v>2:13</v>
       </c>
       <c r="H86" t="str">
-        <v>Sam Williams</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-01</v>
@@ -3684,10 +3684,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:55</v>
+        <v>4:12</v>
       </c>
       <c r="H87" t="str">
-        <v>YUNGBLUD</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B88" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-01</v>
@@ -3722,10 +3722,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:51</v>
+        <v>2:55</v>
       </c>
       <c r="H88" t="str">
-        <v>Megan Moroney</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-01</v>
@@ -3760,10 +3760,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:51</v>
+        <v>3:51</v>
       </c>
       <c r="H89" t="str">
-        <v>Nico Santos</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-01</v>
@@ -3798,10 +3798,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:24</v>
+        <v>2:51</v>
       </c>
       <c r="H90" t="str">
-        <v>REALITY CLUB</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-01</v>
@@ -3836,10 +3836,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:11</v>
+        <v>3:24</v>
       </c>
       <c r="H91" t="str">
-        <v>We Three</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B92" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-01</v>
@@ -3874,10 +3874,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:27</v>
+        <v>4:11</v>
       </c>
       <c r="H92" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>We Three</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-01</v>
@@ -3912,10 +3912,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:06</v>
+        <v>3:27</v>
       </c>
       <c r="H93" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B94" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-01</v>
@@ -3950,10 +3950,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:01</v>
+        <v>3:06</v>
       </c>
       <c r="H94" t="str">
-        <v>Peach PRC</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B95" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-01</v>
@@ -3988,10 +3988,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>5:38</v>
+        <v>3:01</v>
       </c>
       <c r="H95" t="str">
-        <v>georgemichael</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B96" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-01</v>
@@ -4026,10 +4026,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:43</v>
+        <v>5:38</v>
       </c>
       <c r="H96" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>georgemichael</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B97" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-01</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:58</v>
+        <v>3:43</v>
       </c>
       <c r="H97" t="str">
-        <v>Catie Turner</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B98" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-01</v>
@@ -4102,10 +4102,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:13</v>
+        <v>2:58</v>
       </c>
       <c r="H98" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B99" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-01</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>5:48</v>
+        <v>4:13</v>
       </c>
       <c r="H99" t="str">
-        <v>U2</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-01</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:55</v>
+        <v>5:48</v>
       </c>
       <c r="H100" t="str">
-        <v>Lawrence</v>
+        <v>U2</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B101" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-01</v>
@@ -4216,10 +4216,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:24</v>
+        <v>3:55</v>
       </c>
       <c r="H101" t="str">
-        <v>BUNT. Music</v>
+        <v>Lawrence</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:30</v>
@@ -515,7 +515,7 @@
         <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>5:18</v>
@@ -553,7 +553,7 @@
         <v>Mark Ronson - Live at The BRIT Awards 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>7:20</v>
@@ -591,7 +591,7 @@
         <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:01</v>
@@ -629,7 +629,7 @@
         <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B7" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:31</v>
@@ -664,10 +664,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B8" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:00</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="9">
@@ -819,7 +819,7 @@
         <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>4:50</v>
@@ -1845,7 +1845,7 @@
         <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>4:03</v>
@@ -2035,7 +2035,7 @@
         <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B44" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>2:46</v>
@@ -2529,7 +2529,7 @@
         <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B57" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>4:38</v>
@@ -2985,7 +2985,7 @@
         <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B69" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>7:31</v>
@@ -3023,7 +3023,7 @@
         <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B70" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>3:21</v>
@@ -3859,7 +3859,7 @@
         <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B92" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>4:11</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:30</v>
@@ -515,7 +515,7 @@
         <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>5:18</v>
@@ -553,7 +553,7 @@
         <v>Mark Ronson - Live at The BRIT Awards 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>17 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>17 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>7:20</v>
@@ -591,7 +591,7 @@
         <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B6" t="str">
-        <v>17 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>17 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:01</v>
@@ -629,7 +629,7 @@
         <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B7" t="str">
-        <v>19 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>19 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:31</v>
@@ -667,7 +667,7 @@
         <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B8" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:00</v>
@@ -781,7 +781,7 @@
         <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>5:03</v>
@@ -2453,7 +2453,7 @@
         <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:35</v>
@@ -2795,7 +2795,7 @@
         <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B64" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>2:27</v>
@@ -3821,7 +3821,7 @@
         <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
         <v>3:24</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:30</v>
@@ -477,22 +477,22 @@
         <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>Streamed 15 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>Streamed 15 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>LIVE</v>
+        <v>27:54:45</v>
       </c>
       <c r="H3" t="str">
         <v>BRITs</v>
@@ -515,19 +515,19 @@
         <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>5:18</v>
@@ -550,22 +550,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B5" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v>7:20</v>
@@ -583,7 +583,7 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 - Mark Ronson and BRITs</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="6">
@@ -591,19 +591,19 @@
         <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B6" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:01</v>
@@ -629,19 +629,19 @@
         <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B7" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:31</v>
@@ -667,19 +667,19 @@
         <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:00</v>
@@ -705,19 +705,19 @@
         <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:11</v>
@@ -743,19 +743,19 @@
         <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:32</v>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -933,19 +933,19 @@
         <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>4:32</v>
@@ -971,19 +971,19 @@
         <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:47</v>
@@ -1006,22 +1006,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:40</v>
@@ -1039,7 +1039,7 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026) - Jessie Ware</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware</v>
       </c>
     </row>
     <row r="18">
@@ -1047,19 +1047,19 @@
         <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>4:05</v>
@@ -1085,19 +1085,19 @@
         <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:59</v>
@@ -1123,19 +1123,19 @@
         <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:55</v>
@@ -1161,19 +1161,19 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>5:12</v>
@@ -1199,19 +1199,19 @@
         <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:47</v>
@@ -1237,19 +1237,19 @@
         <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:18</v>
@@ -1275,19 +1275,19 @@
         <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:50</v>
@@ -1313,19 +1313,19 @@
         <v>MyKey - Ride With Me</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:24</v>
@@ -1351,19 +1351,19 @@
         <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:36</v>
@@ -1389,19 +1389,19 @@
         <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:34</v>
@@ -1427,19 +1427,19 @@
         <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>4:03</v>
@@ -1465,19 +1465,19 @@
         <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:31</v>
@@ -1503,19 +1503,19 @@
         <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:22</v>
@@ -1541,19 +1541,19 @@
         <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>5:49</v>
@@ -1579,19 +1579,19 @@
         <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:47</v>
@@ -1617,19 +1617,19 @@
         <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>2:20</v>
@@ -1655,19 +1655,19 @@
         <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:18</v>
@@ -1693,19 +1693,19 @@
         <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>2:39</v>
@@ -1731,19 +1731,19 @@
         <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:52</v>
@@ -1769,19 +1769,19 @@
         <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>4:01</v>
@@ -1807,19 +1807,19 @@
         <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:54</v>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:50</v>
@@ -1921,19 +1921,19 @@
         <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:06</v>
@@ -1959,19 +1959,19 @@
         <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B42" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:43</v>
@@ -1997,19 +1997,19 @@
         <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B43" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>6:21</v>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2187,19 +2187,19 @@
         <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B48" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:22</v>
@@ -2225,19 +2225,19 @@
         <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B49" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:53</v>
@@ -2263,19 +2263,19 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B50" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>2:28</v>
@@ -2301,19 +2301,19 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:47</v>
@@ -2339,19 +2339,19 @@
         <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B52" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:40</v>
@@ -2377,19 +2377,19 @@
         <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>2:49</v>
@@ -2415,19 +2415,19 @@
         <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B54" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>4:49</v>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2491,19 +2491,19 @@
         <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B56" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>2:59</v>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2605,19 +2605,19 @@
         <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:08</v>
@@ -2643,19 +2643,19 @@
         <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B60" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>5:32</v>
@@ -2681,19 +2681,19 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>4:39</v>
@@ -2719,19 +2719,19 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B62" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:40</v>
@@ -2757,19 +2757,19 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:57</v>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>4:49</v>
@@ -2871,19 +2871,19 @@
         <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>5:52</v>
@@ -2909,19 +2909,19 @@
         <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:22</v>
@@ -2947,19 +2947,19 @@
         <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B68" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>4:08</v>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3061,19 +3061,19 @@
         <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>4:36</v>
@@ -3099,19 +3099,19 @@
         <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>5:06</v>
@@ -3137,19 +3137,19 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>4:17</v>
@@ -3175,19 +3175,19 @@
         <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>3:20</v>
@@ -3213,19 +3213,19 @@
         <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>4:50</v>
@@ -3251,19 +3251,19 @@
         <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:14</v>
@@ -3289,19 +3289,19 @@
         <v>Jessie Ware - Ride</v>
       </c>
       <c r="B77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>4:37</v>
@@ -3327,19 +3327,19 @@
         <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>3:16</v>
@@ -3365,19 +3365,19 @@
         <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>4:22</v>
@@ -3403,19 +3403,19 @@
         <v>Suburban Requiem</v>
       </c>
       <c r="B80" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>4:40</v>
@@ -3441,19 +3441,19 @@
         <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>3:02</v>
@@ -3479,19 +3479,19 @@
         <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>3:12</v>
@@ -3517,19 +3517,19 @@
         <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B83" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>3:38</v>
@@ -3555,19 +3555,19 @@
         <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>4:40</v>
@@ -3593,19 +3593,19 @@
         <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>2:57</v>
@@ -3631,19 +3631,19 @@
         <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B86" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>2:13</v>
@@ -3669,19 +3669,19 @@
         <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
         <v>4:12</v>
@@ -3707,19 +3707,19 @@
         <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B88" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
         <v>2:55</v>
@@ -3745,19 +3745,19 @@
         <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:51</v>
@@ -3783,19 +3783,19 @@
         <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
         <v>2:51</v>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3935,19 +3935,19 @@
         <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B94" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>3:06</v>
@@ -3973,19 +3973,19 @@
         <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B95" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G95" t="str">
         <v>3:01</v>
@@ -4011,19 +4011,19 @@
         <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B96" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>5:38</v>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4087,19 +4087,19 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G98" t="str">
         <v>2:58</v>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E199" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -477,7 +477,7 @@
         <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B3" t="str">
-        <v>Streamed 15 hours ago</v>
+        <v>Streamed 17 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Streamed 15 hours ago</v>
+        <v>Streamed 17 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>27:54:45</v>
@@ -819,7 +819,7 @@
         <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>4:50</v>
@@ -857,7 +857,7 @@
         <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:53</v>
@@ -895,7 +895,7 @@
         <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:04</v>
@@ -2073,7 +2073,7 @@
         <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:42</v>
@@ -2111,7 +2111,7 @@
         <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:04</v>
@@ -2149,7 +2149,7 @@
         <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B47" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:59</v>
@@ -2567,7 +2567,7 @@
         <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B58" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:46</v>
@@ -3897,7 +3897,7 @@
         <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:27</v>
@@ -4049,7 +4049,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B97" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G97" t="str">
         <v>3:43</v>
@@ -4125,7 +4125,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B99" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G99" t="str">
         <v>4:13</v>
@@ -4163,7 +4163,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G100" t="str">
         <v>5:48</v>
@@ -4201,7 +4201,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B101" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:55</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
+        <v>Dog</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-02</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>The Mountain</v>
+        <v>Torn</v>
       </c>
       <c r="G102" t="str">
-        <v>4:57</v>
+        <v>2:37</v>
       </c>
       <c r="H102" t="str">
-        <v>Gorillaz</v>
+        <v>Cobrah</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L102" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>GO</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/go/1870067581</v>
+        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-02</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>DEADLINE - EP</v>
+        <v>The Mountain</v>
       </c>
       <c r="G103" t="str">
-        <v>3:15</v>
+        <v>4:57</v>
       </c>
       <c r="H103" t="str">
-        <v>BLACKPINK</v>
+        <v>Gorillaz</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
+        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/go/1870067304</v>
+        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
       </c>
       <c r="L103" t="str">
-        <v>GO - BLACKPINK</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Risk It All</v>
+        <v>GO</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
+        <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-02</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Romantic</v>
+        <v>DEADLINE - EP</v>
       </c>
       <c r="G104" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H104" t="str">
-        <v>Bruno Mars</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
+        <v>https://music.apple.com/us/album/go/1870067304</v>
       </c>
       <c r="L104" t="str">
-        <v>Risk It All - Bruno Mars</v>
+        <v>GO - BLACKPINK</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>FEVER DREAM</v>
+        <v>Risk It All</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
+        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-02</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>FEVER DREAM - Single</v>
+        <v>The Romantic</v>
       </c>
       <c r="G105" t="str">
-        <v>2:33</v>
+        <v>3:24</v>
       </c>
       <c r="H105" t="str">
-        <v>Alex Warren</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
+        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
       </c>
       <c r="L105" t="str">
-        <v>FEVER DREAM - Alex Warren</v>
+        <v>Risk It All - Bruno Mars</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Nightingale Lane.</v>
+        <v>FEVER DREAM</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
+        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-02</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>FEVER DREAM - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>5:02</v>
+        <v>2:33</v>
       </c>
       <c r="H106" t="str">
-        <v>RAYE</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
+        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
       </c>
       <c r="L106" t="str">
-        <v>Nightingale Lane. - RAYE</v>
+        <v>FEVER DREAM - Alex Warren</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Made It On Our Own</v>
+        <v>Nightingale Lane.</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
+        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-02</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Made It On Our Own - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G107" t="str">
-        <v>2:49</v>
+        <v>5:02</v>
       </c>
       <c r="H107" t="str">
-        <v>Yeat</v>
+        <v>RAYE</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
+        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
       </c>
       <c r="L107" t="str">
-        <v>Made It On Our Own - Yeat</v>
+        <v>Nightingale Lane. - RAYE</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ganga</v>
+        <v>Made It On Our Own</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/ganga/1879903219</v>
+        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-02</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>DINASTÍA (DELUXE)</v>
+        <v>Made It On Our Own - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:45</v>
+        <v>2:49</v>
       </c>
       <c r="H108" t="str">
-        <v>Peso Pluma</v>
+        <v>Yeat</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/ganga/1879902711</v>
+        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
       </c>
       <c r="L108" t="str">
-        <v>ganga - Peso Pluma</v>
+        <v>Made It On Our Own - Yeat</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WITH ME</v>
+        <v>ganga</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/with-me/1874015492</v>
+        <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-02</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>DINASTÍA (DELUXE)</v>
       </c>
       <c r="G109" t="str">
-        <v>3:03</v>
+        <v>2:45</v>
       </c>
       <c r="H109" t="str">
-        <v>John Summit</v>
+        <v>Peso Pluma</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/with-me/1874015470</v>
+        <v>https://music.apple.com/us/album/ganga/1879902711</v>
       </c>
       <c r="L109" t="str">
-        <v>WITH ME - John Summit</v>
+        <v>ganga - Peso Pluma</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Sorry... I Meant Tonight (Bonus)</v>
+        <v>WITH ME</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
+        <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-02</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Cloud 9</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G110" t="str">
-        <v>3:33</v>
+        <v>3:03</v>
       </c>
       <c r="H110" t="str">
-        <v>Megan Moroney</v>
+        <v>John Summit</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
+        <v>https://music.apple.com/us/album/with-me/1874015470</v>
       </c>
       <c r="L110" t="str">
-        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
+        <v>WITH ME - John Summit</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Miss That</v>
+        <v>Sorry... I Meant Tonight (Bonus)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
+        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-02</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Miss That - Single</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G111" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H111" t="str">
-        <v>Naomi Sharon</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
+        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
       </c>
       <c r="L111" t="str">
-        <v>Miss That - Naomi Sharon</v>
+        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>glass houses</v>
+        <v>Miss That</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
+        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-02</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>ghosted - EP</v>
+        <v>Miss That - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:09</v>
+        <v>2:56</v>
       </c>
       <c r="H112" t="str">
-        <v>Saint Harison</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
+        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
       </c>
       <c r="L112" t="str">
-        <v>glass houses - Saint Harison</v>
+        <v>Miss That - Naomi Sharon</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>glass houses</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-02</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G113" t="str">
-        <v>2:39</v>
+        <v>2:09</v>
       </c>
       <c r="H113" t="str">
-        <v>Slayyyter</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
       </c>
       <c r="L113" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>glass houses - Saint Harison</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ALICE</v>
+        <v>OLD TECHNOLOGY</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-02</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G114" t="str">
-        <v>4:39</v>
+        <v>2:39</v>
       </c>
       <c r="H114" t="str">
-        <v>Erin LeCount</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
       </c>
       <c r="L114" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>OLD TECHNOLOGY - Slayyyter</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Tiny Light</v>
+        <v>ALICE</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-02</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Tiny Light - Single</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G115" t="str">
-        <v>3:27</v>
+        <v>4:39</v>
       </c>
       <c r="H115" t="str">
-        <v>SEVENTEEN</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L115" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-02</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:50</v>
+        <v>3:27</v>
       </c>
       <c r="H116" t="str">
-        <v>aespa</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L116" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-02</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H117" t="str">
-        <v>Concrete Boys</v>
+        <v>aespa</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L117" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>If I Leave</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-02</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G118" t="str">
-        <v>3:00</v>
+        <v>3:23</v>
       </c>
       <c r="H118" t="str">
-        <v>Mitski</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L118" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Time Will Tell</v>
+        <v>If I Leave</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-02</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G119" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H119" t="str">
-        <v>Lee Brice</v>
+        <v>Mitski</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L119" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>How I Get</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-02</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H120" t="str">
-        <v>Laufey</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L120" t="str">
-        <v>How I Get - Laufey</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>How I Get</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-02</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G121" t="str">
-        <v>3:19</v>
+        <v>3:39</v>
       </c>
       <c r="H121" t="str">
-        <v>Jessie Murph</v>
+        <v>Laufey</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L121" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tonto</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-02</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Tonto - Single</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:20</v>
+        <v>3:19</v>
       </c>
       <c r="H122" t="str">
-        <v>J Balvin</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L122" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>Tonto</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-02</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:41</v>
+        <v>2:20</v>
       </c>
       <c r="H123" t="str">
-        <v>BLOND:ISH</v>
+        <v>J Balvin</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L123" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-02</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:50</v>
+        <v>2:41</v>
       </c>
       <c r="H124" t="str">
-        <v>Bautiii</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L124" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-02</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H125" t="str">
-        <v>Mýa</v>
+        <v>Bautiii</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L125" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-02</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>FENIAN</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:11</v>
+        <v>3:41</v>
       </c>
       <c r="H126" t="str">
-        <v>Kneecap</v>
+        <v>Mýa</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L126" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>What You Want</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-02</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>What You Want - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G127" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H127" t="str">
-        <v>Angèle</v>
+        <v>Kneecap</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L127" t="str">
-        <v>What You Want - Angèle</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>psychokiller</v>
+        <v>What You Want</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-02</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>getting up to no good</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>1:53</v>
+        <v>3:08</v>
       </c>
       <c r="H128" t="str">
-        <v>Artemas</v>
+        <v>Angèle</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L128" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>psychokiller</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-02</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>HADES</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G129" t="str">
-        <v>4:05</v>
+        <v>1:53</v>
       </c>
       <c r="H129" t="str">
-        <v>Melanie Martinez</v>
+        <v>Artemas</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L129" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>mariah</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-02</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>HADES</v>
       </c>
       <c r="G130" t="str">
-        <v>2:48</v>
+        <v>4:05</v>
       </c>
       <c r="H130" t="str">
-        <v>Lauv</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L130" t="str">
-        <v>mariah - Lauv</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>BLACKHOLE</v>
+        <v>mariah</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-02</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>REVIVE+</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G131" t="str">
-        <v>3:14</v>
+        <v>2:48</v>
       </c>
       <c r="H131" t="str">
-        <v>IVE</v>
+        <v>Lauv</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L131" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Walk</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-02</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Walk - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G132" t="str">
-        <v>2:56</v>
+        <v>3:14</v>
       </c>
       <c r="H132" t="str">
-        <v>Skye Newman</v>
+        <v>IVE</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L132" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>FLAMMABLE</v>
+        <v>Walk</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-02</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:17</v>
+        <v>2:56</v>
       </c>
       <c r="H133" t="str">
-        <v>Swae Lee</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L133" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>mutual destruction</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-02</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>mutual destruction - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="H134" t="str">
-        <v>kenzie</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L134" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Dear Worry</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-02</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Dear Worry - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H135" t="str">
-        <v>Common People</v>
+        <v>kenzie</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L135" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Gentleman</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-02</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Gentleman - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:16</v>
+        <v>3:01</v>
       </c>
       <c r="H136" t="str">
-        <v>Towa Bird</v>
+        <v>Common People</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L136" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>NYX00</v>
+        <v>Gentleman</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-02</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>NYX00 - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:00</v>
+        <v>2:16</v>
       </c>
       <c r="H137" t="str">
-        <v>Dei V</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L137" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Helicopters</v>
+        <v>NYX00</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-02</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>HELP(2)</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:58</v>
+        <v>3:00</v>
       </c>
       <c r="H138" t="str">
-        <v>Ezra Collective</v>
+        <v>Dei V</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L138" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Helicopters</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-02</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G139" t="str">
-        <v>4:58</v>
+        <v>3:58</v>
       </c>
       <c r="H139" t="str">
-        <v>Max Richter</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L139" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>It's You I Want</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-02</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G140" t="str">
-        <v>1:39</v>
+        <v>4:58</v>
       </c>
       <c r="H140" t="str">
-        <v>Kris Bowers</v>
+        <v>Max Richter</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L140" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>If I Was With You</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-02</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G141" t="str">
-        <v>3:25</v>
+        <v>1:39</v>
       </c>
       <c r="H141" t="str">
-        <v>Presley Regier</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L141" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Stay With Me</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-02</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H142" t="str">
-        <v>Nessa Barrett</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L142" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>My Loving</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-02</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>My Loving - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G143" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H143" t="str">
-        <v>Sonny Fodera</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L143" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Easy On The Eyes</v>
+        <v>My Loving</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-02</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:44</v>
+        <v>2:50</v>
       </c>
       <c r="H144" t="str">
-        <v>Willow Avalon</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L144" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Beautiful</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-02</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Let It Die Here</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:47</v>
+        <v>3:44</v>
       </c>
       <c r="H145" t="str">
-        <v>Linda Perry</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L145" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Beautiful</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-02</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G146" t="str">
-        <v>4:34</v>
+        <v>3:47</v>
       </c>
       <c r="H146" t="str">
-        <v>Jason Segel</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L146" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Control Freak</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-02</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Control Freak - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:53</v>
+        <v>4:34</v>
       </c>
       <c r="H147" t="str">
-        <v>Broadside</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L147" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Done For</v>
+        <v>Control Freak</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-02</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Done For - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:33</v>
+        <v>2:53</v>
       </c>
       <c r="H148" t="str">
-        <v>Max McNown</v>
+        <v>Broadside</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L148" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Ready for the Ride</v>
+        <v>Done For</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-02</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H149" t="str">
-        <v>Sean Paul</v>
+        <v>Max McNown</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L149" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>push the pipe</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-02</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H150" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L150" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>push the pipe</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-02</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>With No Due Respect</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G151" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H151" t="str">
-        <v>Foggieraw</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L151" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Moonlight</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-02</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>McKenzie 2.0</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G152" t="str">
-        <v>2:00</v>
+        <v>3:13</v>
       </c>
       <c r="H152" t="str">
-        <v>FattMack</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L152" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Boat Named After You</v>
+        <v>Moonlight</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-02</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G153" t="str">
-        <v>3:56</v>
+        <v>2:00</v>
       </c>
       <c r="H153" t="str">
-        <v>ERNEST</v>
+        <v>FattMack</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L153" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>fall into you</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-02</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>fall into you - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H154" t="str">
-        <v>Camylio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L154" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Van Gogh</v>
+        <v>fall into you</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-02</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:25</v>
+        <v>3:28</v>
       </c>
       <c r="H155" t="str">
-        <v>Em Beihold</v>
+        <v>Camylio</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L155" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>popstar Nervous</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-02</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>the rumors are true</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G156" t="str">
         <v>2:25</v>
       </c>
       <c r="H156" t="str">
-        <v>DC THE DON</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L156" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Free</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-02</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Free - Single</v>
+        <v>the rumors are true</v>
       </c>
       <c r="G157" t="str">
-        <v>3:08</v>
+        <v>2:25</v>
       </c>
       <c r="H157" t="str">
-        <v>Beartooth</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L157" t="str">
-        <v>Free - Beartooth</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>never come never morning</v>
+        <v>Free</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-02</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>a short history of decay</v>
+        <v>Free - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:39</v>
+        <v>3:08</v>
       </c>
       <c r="H158" t="str">
-        <v>Nothing</v>
+        <v>Beartooth</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L158" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Over My Head</v>
+        <v>never come never morning</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-02</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G159" t="str">
-        <v>2:28</v>
+        <v>3:39</v>
       </c>
       <c r="H159" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Nothing</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L159" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Mantis</v>
+        <v>Over My Head</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-02</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Creature of Habit</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G160" t="str">
-        <v>4:40</v>
+        <v>2:28</v>
       </c>
       <c r="H160" t="str">
-        <v>Courtney Barnett</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L160" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Soft Launch</v>
+        <v>Mantis</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-02</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G161" t="str">
-        <v>2:25</v>
+        <v>4:40</v>
       </c>
       <c r="H161" t="str">
-        <v>Cely</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L161" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>picky choosy</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-02</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:53</v>
+        <v>2:25</v>
       </c>
       <c r="H162" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Cely</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L162" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>La Mala Era Yo</v>
+        <v>picky choosy</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-02</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G163" t="str">
-        <v>2:30</v>
+        <v>2:53</v>
       </c>
       <c r="H163" t="str">
-        <v>Kany García</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L163" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Quiet Part Loud</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-02</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Joy Next Door</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:08</v>
+        <v>2:30</v>
       </c>
       <c r="H164" t="str">
-        <v>The Maine</v>
+        <v>Kany García</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L164" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>favorite girl</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-02</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>favorite girl - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G165" t="str">
-        <v>3:24</v>
+        <v>3:08</v>
       </c>
       <c r="H165" t="str">
-        <v>Alaina Castillo</v>
+        <v>The Maine</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L165" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>The Blade</v>
+        <v>favorite girl</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-02</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>The Blade - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H166" t="str">
-        <v>Kingfishr</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L166" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Blunt Force Blues</v>
+        <v>The Blade</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-02</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Into Oblivion</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:11</v>
+        <v>3:15</v>
       </c>
       <c r="H167" t="str">
-        <v>Lamb of God</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L167" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>The Black Scorpion</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-02</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>The Great Satan</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G168" t="str">
-        <v>1:33</v>
+        <v>4:11</v>
       </c>
       <c r="H168" t="str">
-        <v>Rob Zombie</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L168" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>The Place</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-02</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G169" t="str">
-        <v>5:58</v>
+        <v>1:33</v>
       </c>
       <c r="H169" t="str">
-        <v>Sepultura</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L169" t="str">
-        <v>The Place - Sepultura</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>The Place</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-02</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G170" t="str">
-        <v>3:18</v>
+        <v>5:58</v>
       </c>
       <c r="H170" t="str">
-        <v>Wage War</v>
+        <v>Sepultura</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L170" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-02</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H171" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Wage War</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L171" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Tu Cárcel</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-02</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:36</v>
+        <v>2:26</v>
       </c>
       <c r="H172" t="str">
-        <v>Morat</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L172" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Facts</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-02</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>BE VERY AFRAID (Vol. 1)</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H173" t="str">
-        <v>CHASE B</v>
+        <v>Morat</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L173" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>me &amp; you</v>
+        <v>Facts</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-02</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>big country</v>
+        <v>BE VERY AFRAID (Vol. 1)</v>
       </c>
       <c r="G174" t="str">
-        <v>2:29</v>
+        <v>3:29</v>
       </c>
       <c r="H174" t="str">
-        <v>sosocamo</v>
+        <v>CHASE B</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L174" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>badman</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-02</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>badman - Single</v>
+        <v>big country</v>
       </c>
       <c r="G175" t="str">
-        <v>2:54</v>
+        <v>2:29</v>
       </c>
       <c r="H175" t="str">
-        <v>nomi.</v>
+        <v>sosocamo</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L175" t="str">
-        <v>badman - nomi.</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Shut It Down</v>
+        <v>badman</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-02</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Shut It Down - Single</v>
+        <v>badman - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:26</v>
+        <v>2:54</v>
       </c>
       <c r="H176" t="str">
-        <v>TheARTI$t</v>
+        <v>nomi.</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L176" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>AUTOMATIC</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-02</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:08</v>
+        <v>2:26</v>
       </c>
       <c r="H177" t="str">
-        <v>Hulvey</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L177" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Leaving Egypt</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-02</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:17</v>
+        <v>2:08</v>
       </c>
       <c r="H178" t="str">
-        <v>Alex Jude</v>
+        <v>Hulvey</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L178" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Not Your Mother</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-02</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H179" t="str">
-        <v>gracie</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L179" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-02</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:50</v>
+        <v>3:03</v>
       </c>
       <c r="H180" t="str">
-        <v>Social Distortion</v>
+        <v>gracie</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L180" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>When the Love is Gone</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-02</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G181" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H181" t="str">
-        <v>Des Rocs</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L181" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Miami Crest</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-02</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Miami Crest - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:39</v>
+        <v>3:20</v>
       </c>
       <c r="H182" t="str">
-        <v>Namasenda</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L182" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Say No Prayer</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-02</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:29</v>
+        <v>2:39</v>
       </c>
       <c r="H183" t="str">
-        <v>oskar med k</v>
+        <v>Namasenda</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L183" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-02</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H184" t="str">
-        <v>eee gee</v>
+        <v>oskar med k</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L184" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Pink Tongue</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-02</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Porcelain Heart</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:43</v>
+        <v>3:09</v>
       </c>
       <c r="H185" t="str">
-        <v>Diane Emerita</v>
+        <v>eee gee</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L185" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-02</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G186" t="str">
-        <v>3:23</v>
+        <v>3:43</v>
       </c>
       <c r="H186" t="str">
-        <v>Ber</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L186" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-02</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:26</v>
+        <v>3:23</v>
       </c>
       <c r="H187" t="str">
-        <v>Forest Blakk</v>
+        <v>Ber</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L187" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Heartbeat</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-02</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Heartbeat - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:52</v>
+        <v>3:26</v>
       </c>
       <c r="H188" t="str">
-        <v>Lola Blue</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L188" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-02</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>4:16</v>
+        <v>2:52</v>
       </c>
       <c r="H189" t="str">
-        <v>doggone</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L189" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>I’m Every Woman</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-02</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:35</v>
+        <v>4:16</v>
       </c>
       <c r="H190" t="str">
-        <v>Ashley Jackson</v>
+        <v>doggone</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L190" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-02</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G191" t="str">
-        <v>2:46</v>
+        <v>4:35</v>
       </c>
       <c r="H191" t="str">
-        <v>Chris Morrissey</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L191" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Slow Tonight</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-02</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Full Circle</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G192" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H192" t="str">
-        <v>Tom Misch</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L192" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Freak No More</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-02</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Freak No More - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G193" t="str">
-        <v>3:57</v>
+        <v>3:12</v>
       </c>
       <c r="H193" t="str">
-        <v>AC Slater</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L193" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Don't Stop</v>
+        <v>Freak No More</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-02</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:55</v>
+        <v>3:57</v>
       </c>
       <c r="H194" t="str">
-        <v>HoneyLuv</v>
+        <v>AC Slater</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L194" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Cause I Do</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-02</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:39</v>
+        <v>2:55</v>
       </c>
       <c r="H195" t="str">
-        <v>Preston Pablo</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L195" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Morning Comes</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-02</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>4:11</v>
+        <v>2:39</v>
       </c>
       <c r="H196" t="str">
-        <v>Ty Myers</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L196" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>BETTER ON ME</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-02</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G197" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H197" t="str">
-        <v>Johnny Huynh</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L197" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Speed or Perish</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-02</v>
@@ -7899,68 +7899,106 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Leather Temple</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>4:30</v>
+        <v>3:24</v>
       </c>
       <c r="H198" t="str">
-        <v>Carpenter Brut</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L198" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G199" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D199" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
+      <c r="D200" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G199" t="str">
+      <c r="G200" t="str">
         <v>2:27</v>
       </c>
-      <c r="H199" t="str">
+      <c r="H200" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K199" t="str">
+      <c r="K200" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L199" t="str">
+      <c r="L200" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B3" t="str">
-        <v>Streamed 17 hours ago</v>
+        <v>Streamed 1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Streamed 17 hours ago</v>
+        <v>Streamed 1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>27:54:45</v>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>7:20</v>
@@ -591,19 +591,19 @@
         <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:01</v>
@@ -629,19 +629,19 @@
         <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:31</v>
@@ -667,19 +667,19 @@
         <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:00</v>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -743,19 +743,19 @@
         <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:32</v>
@@ -781,19 +781,19 @@
         <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>5:03</v>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>4:03</v>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1997,19 +1997,19 @@
         <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>6:21</v>
@@ -2035,19 +2035,19 @@
         <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>2:46</v>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2453,19 +2453,19 @@
         <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:35</v>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2529,19 +2529,19 @@
         <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B57" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>4:38</v>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>2:27</v>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:22</v>
@@ -2947,19 +2947,19 @@
         <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>4:08</v>
@@ -2985,19 +2985,19 @@
         <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>7:31</v>
@@ -3023,19 +3023,19 @@
         <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>3:21</v>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>4:17</v>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3783,19 +3783,19 @@
         <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
         <v>2:51</v>
@@ -3821,19 +3821,19 @@
         <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
         <v>3:24</v>
@@ -3859,19 +3859,19 @@
         <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B92" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>4:11</v>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4087,19 +4087,19 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G98" t="str">
         <v>2:58</v>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5490,2515 +5490,2553 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>mutual destruction</v>
+        <v>3am (Remix)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>mutual destruction - Single</v>
+        <v>3am (Remix) - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:31</v>
+        <v>2:44</v>
       </c>
       <c r="H135" t="str">
-        <v>kenzie</v>
+        <v>Łaszewo</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
       </c>
       <c r="L135" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>3am (Remix) - Łaszewo</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Dear Worry</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Dear Worry - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H136" t="str">
-        <v>Common People</v>
+        <v>kenzie</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L136" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Gentleman</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Gentleman - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:16</v>
+        <v>3:01</v>
       </c>
       <c r="H137" t="str">
-        <v>Towa Bird</v>
+        <v>Common People</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L137" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>NYX00</v>
+        <v>Gentleman</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>NYX00 - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:00</v>
+        <v>2:16</v>
       </c>
       <c r="H138" t="str">
-        <v>Dei V</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L138" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Helicopters</v>
+        <v>NYX00</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>HELP(2)</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:58</v>
+        <v>3:00</v>
       </c>
       <c r="H139" t="str">
-        <v>Ezra Collective</v>
+        <v>Dei V</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L139" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Helicopters</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G140" t="str">
-        <v>4:58</v>
+        <v>3:58</v>
       </c>
       <c r="H140" t="str">
-        <v>Max Richter</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L140" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>It's You I Want</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G141" t="str">
-        <v>1:39</v>
+        <v>4:58</v>
       </c>
       <c r="H141" t="str">
-        <v>Kris Bowers</v>
+        <v>Max Richter</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L141" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>If I Was With You</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G142" t="str">
-        <v>3:25</v>
+        <v>1:39</v>
       </c>
       <c r="H142" t="str">
-        <v>Presley Regier</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L142" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Stay With Me</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H143" t="str">
-        <v>Nessa Barrett</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L143" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>My Loving</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>My Loving - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G144" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H144" t="str">
-        <v>Sonny Fodera</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L144" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Easy On The Eyes</v>
+        <v>My Loving</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:44</v>
+        <v>2:50</v>
       </c>
       <c r="H145" t="str">
-        <v>Willow Avalon</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L145" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Beautiful</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Let It Die Here</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:47</v>
+        <v>3:44</v>
       </c>
       <c r="H146" t="str">
-        <v>Linda Perry</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L146" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Beautiful</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G147" t="str">
-        <v>4:34</v>
+        <v>3:47</v>
       </c>
       <c r="H147" t="str">
-        <v>Jason Segel</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L147" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Control Freak</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Control Freak - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:53</v>
+        <v>4:34</v>
       </c>
       <c r="H148" t="str">
-        <v>Broadside</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L148" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Done For</v>
+        <v>Control Freak</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Done For - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:33</v>
+        <v>2:53</v>
       </c>
       <c r="H149" t="str">
-        <v>Max McNown</v>
+        <v>Broadside</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L149" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Ready for the Ride</v>
+        <v>Done For</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H150" t="str">
-        <v>Sean Paul</v>
+        <v>Max McNown</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L150" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>push the pipe</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H151" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L151" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>push the pipe</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>With No Due Respect</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G152" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H152" t="str">
-        <v>Foggieraw</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L152" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Moonlight</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>McKenzie 2.0</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G153" t="str">
-        <v>2:00</v>
+        <v>3:13</v>
       </c>
       <c r="H153" t="str">
-        <v>FattMack</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L153" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Boat Named After You</v>
+        <v>Moonlight</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G154" t="str">
-        <v>3:56</v>
+        <v>2:00</v>
       </c>
       <c r="H154" t="str">
-        <v>ERNEST</v>
+        <v>FattMack</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L154" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>fall into you</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>fall into you - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H155" t="str">
-        <v>Camylio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L155" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Van Gogh</v>
+        <v>fall into you</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:25</v>
+        <v>3:28</v>
       </c>
       <c r="H156" t="str">
-        <v>Em Beihold</v>
+        <v>Camylio</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L156" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>popstar Nervous</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>the rumors are true</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G157" t="str">
         <v>2:25</v>
       </c>
       <c r="H157" t="str">
-        <v>DC THE DON</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L157" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Free</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Free - Single</v>
+        <v>the rumors are true - EP</v>
       </c>
       <c r="G158" t="str">
-        <v>3:08</v>
+        <v>2:25</v>
       </c>
       <c r="H158" t="str">
-        <v>Beartooth</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L158" t="str">
-        <v>Free - Beartooth</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>never come never morning</v>
+        <v>Free</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>a short history of decay</v>
+        <v>Free - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:39</v>
+        <v>3:08</v>
       </c>
       <c r="H159" t="str">
-        <v>Nothing</v>
+        <v>Beartooth</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L159" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Over My Head</v>
+        <v>never come never morning</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G160" t="str">
-        <v>2:28</v>
+        <v>3:39</v>
       </c>
       <c r="H160" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Nothing</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L160" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Mantis</v>
+        <v>Over My Head</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Creature of Habit</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G161" t="str">
-        <v>4:40</v>
+        <v>2:28</v>
       </c>
       <c r="H161" t="str">
-        <v>Courtney Barnett</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L161" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Soft Launch</v>
+        <v>Mantis</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G162" t="str">
-        <v>2:25</v>
+        <v>4:40</v>
       </c>
       <c r="H162" t="str">
-        <v>Cely</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L162" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>picky choosy</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:53</v>
+        <v>2:25</v>
       </c>
       <c r="H163" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Cely</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L163" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>La Mala Era Yo</v>
+        <v>picky choosy</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G164" t="str">
-        <v>2:30</v>
+        <v>2:53</v>
       </c>
       <c r="H164" t="str">
-        <v>Kany García</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L164" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Quiet Part Loud</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Joy Next Door</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:08</v>
+        <v>2:30</v>
       </c>
       <c r="H165" t="str">
-        <v>The Maine</v>
+        <v>Kany García</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L165" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>favorite girl</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>favorite girl - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G166" t="str">
-        <v>3:24</v>
+        <v>3:08</v>
       </c>
       <c r="H166" t="str">
-        <v>Alaina Castillo</v>
+        <v>The Maine</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L166" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>The Blade</v>
+        <v>favorite girl</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>The Blade - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H167" t="str">
-        <v>Kingfishr</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L167" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Blunt Force Blues</v>
+        <v>The Blade</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Into Oblivion</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:11</v>
+        <v>3:15</v>
       </c>
       <c r="H168" t="str">
-        <v>Lamb of God</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L168" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>The Black Scorpion</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>The Great Satan</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G169" t="str">
-        <v>1:33</v>
+        <v>4:11</v>
       </c>
       <c r="H169" t="str">
-        <v>Rob Zombie</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L169" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>The Place</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G170" t="str">
-        <v>5:58</v>
+        <v>1:33</v>
       </c>
       <c r="H170" t="str">
-        <v>Sepultura</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L170" t="str">
-        <v>The Place - Sepultura</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>The Place</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>3:18</v>
+        <v>5:58</v>
       </c>
       <c r="H171" t="str">
-        <v>Wage War</v>
+        <v>Sepultura</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L171" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G172" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H172" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Wage War</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L172" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Tu Cárcel</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:36</v>
+        <v>2:26</v>
       </c>
       <c r="H173" t="str">
-        <v>Morat</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L173" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Facts</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>BE VERY AFRAID (Vol. 1)</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H174" t="str">
-        <v>CHASE B</v>
+        <v>Morat</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L174" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>me &amp; you</v>
+        <v>Facts</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>big country</v>
+        <v>BE VERY AFRAID (Vol. 1)</v>
       </c>
       <c r="G175" t="str">
-        <v>2:29</v>
+        <v>3:29</v>
       </c>
       <c r="H175" t="str">
-        <v>sosocamo</v>
+        <v>CHASE B</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L175" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>badman</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>badman - Single</v>
+        <v>big country</v>
       </c>
       <c r="G176" t="str">
-        <v>2:54</v>
+        <v>2:29</v>
       </c>
       <c r="H176" t="str">
-        <v>nomi.</v>
+        <v>sosocamo</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L176" t="str">
-        <v>badman - nomi.</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Shut It Down</v>
+        <v>badman</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Shut It Down - Single</v>
+        <v>badman - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:26</v>
+        <v>2:54</v>
       </c>
       <c r="H177" t="str">
-        <v>TheARTI$t</v>
+        <v>nomi.</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L177" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>AUTOMATIC</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:08</v>
+        <v>2:26</v>
       </c>
       <c r="H178" t="str">
-        <v>Hulvey</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L178" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Leaving Egypt</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:17</v>
+        <v>2:08</v>
       </c>
       <c r="H179" t="str">
-        <v>Alex Jude</v>
+        <v>Hulvey</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L179" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Not Your Mother</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H180" t="str">
-        <v>gracie</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L180" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:50</v>
+        <v>3:03</v>
       </c>
       <c r="H181" t="str">
-        <v>Social Distortion</v>
+        <v>gracie</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L181" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>When the Love is Gone</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G182" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H182" t="str">
-        <v>Des Rocs</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L182" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Miami Crest</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Miami Crest - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:39</v>
+        <v>3:20</v>
       </c>
       <c r="H183" t="str">
-        <v>Namasenda</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L183" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Say No Prayer</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:29</v>
+        <v>2:39</v>
       </c>
       <c r="H184" t="str">
-        <v>oskar med k</v>
+        <v>Namasenda</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L184" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H185" t="str">
-        <v>eee gee</v>
+        <v>oskar med k</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L185" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Pink Tongue</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Porcelain Heart</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:43</v>
+        <v>3:09</v>
       </c>
       <c r="H186" t="str">
-        <v>Diane Emerita</v>
+        <v>eee gee</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L186" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G187" t="str">
-        <v>3:23</v>
+        <v>3:43</v>
       </c>
       <c r="H187" t="str">
-        <v>Ber</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L187" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:26</v>
+        <v>3:23</v>
       </c>
       <c r="H188" t="str">
-        <v>Forest Blakk</v>
+        <v>Ber</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L188" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Heartbeat</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Heartbeat - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:52</v>
+        <v>3:26</v>
       </c>
       <c r="H189" t="str">
-        <v>Lola Blue</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L189" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:16</v>
+        <v>2:52</v>
       </c>
       <c r="H190" t="str">
-        <v>doggone</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L190" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>I’m Every Woman</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:35</v>
+        <v>4:16</v>
       </c>
       <c r="H191" t="str">
-        <v>Ashley Jackson</v>
+        <v>doggone</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L191" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G192" t="str">
-        <v>2:46</v>
+        <v>4:35</v>
       </c>
       <c r="H192" t="str">
-        <v>Chris Morrissey</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L192" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Slow Tonight</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Full Circle</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G193" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H193" t="str">
-        <v>Tom Misch</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L193" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Freak No More</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Freak No More - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G194" t="str">
-        <v>3:57</v>
+        <v>3:12</v>
       </c>
       <c r="H194" t="str">
-        <v>AC Slater</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L194" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Don't Stop</v>
+        <v>Freak No More</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:55</v>
+        <v>3:57</v>
       </c>
       <c r="H195" t="str">
-        <v>HoneyLuv</v>
+        <v>AC Slater</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L195" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Cause I Do</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:39</v>
+        <v>2:55</v>
       </c>
       <c r="H196" t="str">
-        <v>Preston Pablo</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L196" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Morning Comes</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>4:11</v>
+        <v>2:39</v>
       </c>
       <c r="H197" t="str">
-        <v>Ty Myers</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L197" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>BETTER ON ME</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G198" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H198" t="str">
-        <v>Johnny Huynh</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L198" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Speed or Perish</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Leather Temple</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>4:30</v>
+        <v>3:24</v>
       </c>
       <c r="H199" t="str">
-        <v>Carpenter Brut</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L199" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G200" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D200" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
+      <c r="D201" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G200" t="str">
+      <c r="G201" t="str">
         <v>2:27</v>
       </c>
-      <c r="H200" t="str">
+      <c r="H201" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K200" t="str">
+      <c r="K201" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L200" t="str">
+      <c r="L201" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>5:18</v>
@@ -1237,7 +1237,7 @@
         <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:18</v>
@@ -1275,7 +1275,7 @@
         <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:50</v>
@@ -1313,7 +1313,7 @@
         <v>MyKey - Ride With Me</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:24</v>
@@ -1351,7 +1351,7 @@
         <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:36</v>
@@ -1389,7 +1389,7 @@
         <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:34</v>
@@ -1427,7 +1427,7 @@
         <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>4:03</v>
@@ -1465,7 +1465,7 @@
         <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:31</v>
@@ -1503,7 +1503,7 @@
         <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:22</v>
@@ -1541,7 +1541,7 @@
         <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>5:49</v>
@@ -1579,7 +1579,7 @@
         <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:47</v>
@@ -1617,7 +1617,7 @@
         <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>2:20</v>
@@ -1655,7 +1655,7 @@
         <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:18</v>
@@ -1693,7 +1693,7 @@
         <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>2:39</v>
@@ -1731,7 +1731,7 @@
         <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:52</v>
@@ -1769,7 +1769,7 @@
         <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>4:01</v>
@@ -1807,7 +1807,7 @@
         <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:54</v>
@@ -1921,7 +1921,7 @@
         <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:06</v>
@@ -1959,7 +1959,7 @@
         <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:43</v>
@@ -2339,7 +2339,7 @@
         <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B52" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:40</v>
@@ -2377,7 +2377,7 @@
         <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>2:49</v>
@@ -3365,7 +3365,7 @@
         <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>4:22</v>
@@ -3441,7 +3441,7 @@
         <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B81" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>3:02</v>
@@ -3479,7 +3479,7 @@
         <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>3:12</v>
@@ -3517,7 +3517,7 @@
         <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B83" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>3:38</v>
@@ -3555,7 +3555,7 @@
         <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>4:40</v>
@@ -3593,7 +3593,7 @@
         <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>2:57</v>
@@ -3631,7 +3631,7 @@
         <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B86" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>2:13</v>
@@ -3669,7 +3669,7 @@
         <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
         <v>4:12</v>
@@ -3707,7 +3707,7 @@
         <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B88" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
         <v>2:55</v>
@@ -3745,7 +3745,7 @@
         <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:51</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:30</v>
@@ -588,7 +588,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B6" t="str">
         <v>2 days ago</v>
@@ -621,7 +621,7 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="7">
@@ -1161,7 +1161,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>5:12</v>
@@ -1199,7 +1199,7 @@
         <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:47</v>
@@ -2301,7 +2301,7 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:47</v>
@@ -2415,7 +2415,7 @@
         <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B54" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>4:49</v>
@@ -2681,7 +2681,7 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>4:39</v>
@@ -2719,7 +2719,7 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:40</v>
@@ -2757,7 +2757,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:57</v>
@@ -2871,7 +2871,7 @@
         <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>5:52</v>
@@ -3213,7 +3213,7 @@
         <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>4:50</v>
@@ -3251,7 +3251,7 @@
         <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:14</v>
@@ -3289,7 +3289,7 @@
         <v>Jessie Ware - Ride</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>4:37</v>
@@ -3327,7 +3327,7 @@
         <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>3:16</v>
@@ -3403,7 +3403,7 @@
         <v>Suburban Requiem</v>
       </c>
       <c r="B80" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>4:40</v>
@@ -7025,7 +7025,7 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>BE VERY AFRAID (Vol. 1)</v>
+        <v>Be Very Afraid (Vol. 1)</v>
       </c>
       <c r="G175" t="str">
         <v>3:29</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -705,7 +705,7 @@
         <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:11</v>
@@ -781,7 +781,7 @@
         <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>5:03</v>
@@ -819,7 +819,7 @@
         <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>4:50</v>
@@ -857,7 +857,7 @@
         <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:53</v>
@@ -895,7 +895,7 @@
         <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:04</v>
@@ -933,7 +933,7 @@
         <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>4:32</v>
@@ -971,7 +971,7 @@
         <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:47</v>
@@ -1009,7 +1009,7 @@
         <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:40</v>
       </c>
       <c r="H17" t="str">
-        <v>Jessie Ware</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,7 +1039,7 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="18">
@@ -1047,7 +1047,7 @@
         <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>4:05</v>
@@ -1085,7 +1085,7 @@
         <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:59</v>
@@ -1123,7 +1123,7 @@
         <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:55</v>
@@ -1845,7 +1845,7 @@
         <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>4:03</v>
@@ -1883,7 +1883,7 @@
         <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:50</v>
@@ -2035,7 +2035,7 @@
         <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>2:46</v>
@@ -2073,7 +2073,7 @@
         <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:42</v>
@@ -2111,7 +2111,7 @@
         <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:04</v>
@@ -2149,7 +2149,7 @@
         <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:59</v>
@@ -2187,7 +2187,7 @@
         <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:22</v>
@@ -2225,7 +2225,7 @@
         <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B49" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:53</v>
@@ -2263,7 +2263,7 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B50" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>2:28</v>
@@ -2453,7 +2453,7 @@
         <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:35</v>
@@ -2491,7 +2491,7 @@
         <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B56" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>2:59</v>
@@ -2529,7 +2529,7 @@
         <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>4:38</v>
@@ -2567,7 +2567,7 @@
         <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:46</v>
@@ -2605,7 +2605,7 @@
         <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:08</v>
@@ -2643,7 +2643,7 @@
         <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>5:32</v>
@@ -2795,7 +2795,7 @@
         <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B64" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>2:27</v>
@@ -2833,7 +2833,7 @@
         <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>4:49</v>
@@ -2985,7 +2985,7 @@
         <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>7:31</v>
@@ -3023,7 +3023,7 @@
         <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>3:21</v>
@@ -3061,7 +3061,7 @@
         <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>4:36</v>
@@ -3099,7 +3099,7 @@
         <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>5:06</v>
@@ -3175,7 +3175,7 @@
         <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>3:20</v>
@@ -3821,7 +3821,7 @@
         <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
         <v>3:24</v>
@@ -3859,7 +3859,7 @@
         <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B92" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>4:11</v>
@@ -3897,7 +3897,7 @@
         <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:27</v>
@@ -3935,7 +3935,7 @@
         <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B94" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>3:06</v>
@@ -3973,7 +3973,7 @@
         <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B95" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G95" t="str">
         <v>3:01</v>
@@ -4011,7 +4011,7 @@
         <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B96" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>5:38</v>
@@ -4049,7 +4049,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B97" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G97" t="str">
         <v>3:43</v>
@@ -4125,7 +4125,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B99" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G99" t="str">
         <v>4:13</v>
@@ -4163,7 +4163,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G100" t="str">
         <v>5:48</v>
@@ -4201,7 +4201,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B101" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:55</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Dog</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-03</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Torn</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G102" t="str">
-        <v>2:37</v>
+        <v>4:11</v>
       </c>
       <c r="H102" t="str">
-        <v>Cobrah</v>
+        <v>TOMORA</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L102" t="str">
-        <v>Dog - Cobrah</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="103">
@@ -4654,13 +4654,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>glass houses</v>
+        <v>Dog</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-03</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ghosted - EP</v>
+        <v>Torn</v>
       </c>
       <c r="G113" t="str">
-        <v>2:09</v>
+        <v>2:37</v>
       </c>
       <c r="H113" t="str">
-        <v>Saint Harison</v>
+        <v>Cobrah</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L113" t="str">
-        <v>glass houses - Saint Harison</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>glass houses</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-03</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G114" t="str">
-        <v>2:39</v>
+        <v>2:09</v>
       </c>
       <c r="H114" t="str">
-        <v>Slayyyter</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
       </c>
       <c r="L114" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>glass houses - Saint Harison</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>ALICE</v>
+        <v>OLD TECHNOLOGY</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-03</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G115" t="str">
-        <v>4:39</v>
+        <v>2:39</v>
       </c>
       <c r="H115" t="str">
-        <v>Erin LeCount</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
       </c>
       <c r="L115" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>OLD TECHNOLOGY - Slayyyter</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Tiny Light</v>
+        <v>ALICE</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-03</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Tiny Light - Single</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G116" t="str">
-        <v>3:27</v>
+        <v>4:39</v>
       </c>
       <c r="H116" t="str">
-        <v>SEVENTEEN</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L116" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-03</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:50</v>
+        <v>3:27</v>
       </c>
       <c r="H117" t="str">
-        <v>aespa</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L117" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-03</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H118" t="str">
-        <v>Concrete Boys</v>
+        <v>aespa</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L118" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>If I Leave</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-03</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G119" t="str">
-        <v>3:00</v>
+        <v>3:23</v>
       </c>
       <c r="H119" t="str">
-        <v>Mitski</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L119" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Time Will Tell</v>
+        <v>If I Leave</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-03</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G120" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H120" t="str">
-        <v>Lee Brice</v>
+        <v>Mitski</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L120" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>How I Get</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-03</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H121" t="str">
-        <v>Laufey</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L121" t="str">
-        <v>How I Get - Laufey</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>How I Get</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-03</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G122" t="str">
-        <v>3:19</v>
+        <v>3:39</v>
       </c>
       <c r="H122" t="str">
-        <v>Jessie Murph</v>
+        <v>Laufey</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L122" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Tonto</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-03</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Tonto - Single</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:20</v>
+        <v>3:19</v>
       </c>
       <c r="H123" t="str">
-        <v>J Balvin</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L123" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>Tonto</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-03</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:41</v>
+        <v>2:20</v>
       </c>
       <c r="H124" t="str">
-        <v>BLOND:ISH</v>
+        <v>J Balvin</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L124" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-03</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:50</v>
+        <v>2:41</v>
       </c>
       <c r="H125" t="str">
-        <v>Bautiii</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L125" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-03</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H126" t="str">
-        <v>Mýa</v>
+        <v>Bautiii</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L126" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-03</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>FENIAN</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:11</v>
+        <v>3:41</v>
       </c>
       <c r="H127" t="str">
-        <v>Kneecap</v>
+        <v>Mýa</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L127" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>What You Want</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-03</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>What You Want - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G128" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H128" t="str">
-        <v>Angèle</v>
+        <v>Kneecap</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L128" t="str">
-        <v>What You Want - Angèle</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>psychokiller</v>
+        <v>What You Want</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-03</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>getting up to no good</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>1:53</v>
+        <v>3:08</v>
       </c>
       <c r="H129" t="str">
-        <v>Artemas</v>
+        <v>Angèle</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L129" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>psychokiller</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-03</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>HADES</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G130" t="str">
-        <v>4:05</v>
+        <v>1:53</v>
       </c>
       <c r="H130" t="str">
-        <v>Melanie Martinez</v>
+        <v>Artemas</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L130" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>mariah</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-03</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>HADES</v>
       </c>
       <c r="G131" t="str">
-        <v>2:48</v>
+        <v>4:05</v>
       </c>
       <c r="H131" t="str">
-        <v>Lauv</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L131" t="str">
-        <v>mariah - Lauv</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>BLACKHOLE</v>
+        <v>mariah</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-03</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>REVIVE+</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G132" t="str">
-        <v>3:14</v>
+        <v>2:48</v>
       </c>
       <c r="H132" t="str">
-        <v>IVE</v>
+        <v>Lauv</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L132" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Walk</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-03</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Walk - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G133" t="str">
-        <v>2:56</v>
+        <v>3:14</v>
       </c>
       <c r="H133" t="str">
-        <v>Skye Newman</v>
+        <v>IVE</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L133" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>FLAMMABLE</v>
+        <v>Walk</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-03</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:17</v>
+        <v>2:56</v>
       </c>
       <c r="H134" t="str">
-        <v>Swae Lee</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L134" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>3am (Remix)</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-03</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>3am (Remix) - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:44</v>
+        <v>3:17</v>
       </c>
       <c r="H135" t="str">
-        <v>Łaszewo</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L135" t="str">
-        <v>3am (Remix) - Łaszewo</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>mutual destruction</v>
+        <v>3am (Remix)</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-03</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>mutual destruction - Single</v>
+        <v>3am (Remix) - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:31</v>
+        <v>2:44</v>
       </c>
       <c r="H136" t="str">
-        <v>kenzie</v>
+        <v>Łaszewo</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
       </c>
       <c r="L136" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>3am (Remix) - Łaszewo</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Dear Worry</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-03</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Dear Worry - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H137" t="str">
-        <v>Common People</v>
+        <v>kenzie</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L137" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Gentleman</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-03</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Gentleman - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:16</v>
+        <v>3:01</v>
       </c>
       <c r="H138" t="str">
-        <v>Towa Bird</v>
+        <v>Common People</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L138" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>NYX00</v>
+        <v>Gentleman</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-03</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>NYX00 - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:00</v>
+        <v>2:16</v>
       </c>
       <c r="H139" t="str">
-        <v>Dei V</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L139" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Helicopters</v>
+        <v>NYX00</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-03</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>HELP(2)</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:58</v>
+        <v>3:00</v>
       </c>
       <c r="H140" t="str">
-        <v>Ezra Collective</v>
+        <v>Dei V</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L140" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Helicopters</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-03</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G141" t="str">
-        <v>4:58</v>
+        <v>3:58</v>
       </c>
       <c r="H141" t="str">
-        <v>Max Richter</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L141" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>It's You I Want</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-03</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G142" t="str">
-        <v>1:39</v>
+        <v>4:58</v>
       </c>
       <c r="H142" t="str">
-        <v>Kris Bowers</v>
+        <v>Max Richter</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L142" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>If I Was With You</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-03</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G143" t="str">
-        <v>3:25</v>
+        <v>1:39</v>
       </c>
       <c r="H143" t="str">
-        <v>Presley Regier</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L143" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Stay With Me</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-03</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H144" t="str">
-        <v>Nessa Barrett</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L144" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>My Loving</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-03</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>My Loving - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G145" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H145" t="str">
-        <v>Sonny Fodera</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L145" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Easy On The Eyes</v>
+        <v>My Loving</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-03</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:44</v>
+        <v>2:50</v>
       </c>
       <c r="H146" t="str">
-        <v>Willow Avalon</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L146" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Beautiful</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-03</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Let It Die Here</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:47</v>
+        <v>3:44</v>
       </c>
       <c r="H147" t="str">
-        <v>Linda Perry</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L147" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Beautiful</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-03</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G148" t="str">
-        <v>4:34</v>
+        <v>3:47</v>
       </c>
       <c r="H148" t="str">
-        <v>Jason Segel</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L148" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Control Freak</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-03</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Control Freak - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:53</v>
+        <v>4:34</v>
       </c>
       <c r="H149" t="str">
-        <v>Broadside</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L149" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Done For</v>
+        <v>Control Freak</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-03</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Done For - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:33</v>
+        <v>2:53</v>
       </c>
       <c r="H150" t="str">
-        <v>Max McNown</v>
+        <v>Broadside</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L150" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Ready for the Ride</v>
+        <v>Done For</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-03</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H151" t="str">
-        <v>Sean Paul</v>
+        <v>Max McNown</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L151" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>push the pipe</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-03</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H152" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L152" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>push the pipe</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-03</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>With No Due Respect</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G153" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H153" t="str">
-        <v>Foggieraw</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L153" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Moonlight</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-03</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>McKenzie 2.0</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G154" t="str">
-        <v>2:00</v>
+        <v>3:13</v>
       </c>
       <c r="H154" t="str">
-        <v>FattMack</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L154" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Boat Named After You</v>
+        <v>Moonlight</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-03</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G155" t="str">
-        <v>3:56</v>
+        <v>2:00</v>
       </c>
       <c r="H155" t="str">
-        <v>ERNEST</v>
+        <v>FattMack</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L155" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>fall into you</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-03</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>fall into you - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H156" t="str">
-        <v>Camylio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L156" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Van Gogh</v>
+        <v>fall into you</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-03</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:25</v>
+        <v>3:28</v>
       </c>
       <c r="H157" t="str">
-        <v>Em Beihold</v>
+        <v>Camylio</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L157" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>popstar Nervous</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-03</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>the rumors are true - EP</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G158" t="str">
         <v>2:25</v>
       </c>
       <c r="H158" t="str">
-        <v>DC THE DON</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L158" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Free</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-03</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Free - Single</v>
+        <v>the rumors are true - EP</v>
       </c>
       <c r="G159" t="str">
-        <v>3:08</v>
+        <v>2:25</v>
       </c>
       <c r="H159" t="str">
-        <v>Beartooth</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L159" t="str">
-        <v>Free - Beartooth</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>never come never morning</v>
+        <v>Free</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-03</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>a short history of decay</v>
+        <v>Free - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:39</v>
+        <v>3:08</v>
       </c>
       <c r="H160" t="str">
-        <v>Nothing</v>
+        <v>Beartooth</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L160" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Over My Head</v>
+        <v>never come never morning</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-03</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G161" t="str">
-        <v>2:28</v>
+        <v>3:39</v>
       </c>
       <c r="H161" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Nothing</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L161" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Mantis</v>
+        <v>Over My Head</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-03</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Creature of Habit</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G162" t="str">
-        <v>4:40</v>
+        <v>2:30</v>
       </c>
       <c r="H162" t="str">
-        <v>Courtney Barnett</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L162" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Soft Launch</v>
+        <v>Mantis</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-03</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G163" t="str">
-        <v>2:25</v>
+        <v>4:40</v>
       </c>
       <c r="H163" t="str">
-        <v>Cely</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L163" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>picky choosy</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-03</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:53</v>
+        <v>2:25</v>
       </c>
       <c r="H164" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Cely</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L164" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>La Mala Era Yo</v>
+        <v>picky choosy</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-03</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G165" t="str">
-        <v>2:30</v>
+        <v>2:53</v>
       </c>
       <c r="H165" t="str">
-        <v>Kany García</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L165" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Quiet Part Loud</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-03</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Joy Next Door</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:08</v>
+        <v>2:30</v>
       </c>
       <c r="H166" t="str">
-        <v>The Maine</v>
+        <v>Kany García</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L166" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>favorite girl</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-03</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>favorite girl - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G167" t="str">
-        <v>3:24</v>
+        <v>3:08</v>
       </c>
       <c r="H167" t="str">
-        <v>Alaina Castillo</v>
+        <v>The Maine</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L167" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>The Blade</v>
+        <v>favorite girl</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-03</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>The Blade - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H168" t="str">
-        <v>Kingfishr</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L168" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Blunt Force Blues</v>
+        <v>The Blade</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-03</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Into Oblivion</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:11</v>
+        <v>3:15</v>
       </c>
       <c r="H169" t="str">
-        <v>Lamb of God</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L169" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>The Black Scorpion</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-03</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>The Great Satan</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G170" t="str">
-        <v>1:33</v>
+        <v>4:11</v>
       </c>
       <c r="H170" t="str">
-        <v>Rob Zombie</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L170" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>The Place</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-03</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G171" t="str">
-        <v>5:58</v>
+        <v>1:33</v>
       </c>
       <c r="H171" t="str">
-        <v>Sepultura</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L171" t="str">
-        <v>The Place - Sepultura</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>The Place</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-03</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G172" t="str">
-        <v>3:18</v>
+        <v>5:58</v>
       </c>
       <c r="H172" t="str">
-        <v>Wage War</v>
+        <v>Sepultura</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L172" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-03</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H173" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Wage War</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L173" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Tu Cárcel</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-03</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:36</v>
+        <v>2:26</v>
       </c>
       <c r="H174" t="str">
-        <v>Morat</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L174" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Facts</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-03</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Be Very Afraid (Vol. 1)</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H175" t="str">
-        <v>CHASE B</v>
+        <v>Morat</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L175" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>me &amp; you</v>
+        <v>Facts</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-03</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>big country</v>
+        <v>Be Very Afraid (Vol. 1)</v>
       </c>
       <c r="G176" t="str">
-        <v>2:29</v>
+        <v>3:29</v>
       </c>
       <c r="H176" t="str">
-        <v>sosocamo</v>
+        <v>CHASE B</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L176" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>badman</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-03</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>badman - Single</v>
+        <v>big country</v>
       </c>
       <c r="G177" t="str">
-        <v>2:54</v>
+        <v>2:29</v>
       </c>
       <c r="H177" t="str">
-        <v>nomi.</v>
+        <v>sosocamo</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L177" t="str">
-        <v>badman - nomi.</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Shut It Down</v>
+        <v>badman</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-03</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Shut It Down - Single</v>
+        <v>badman - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:26</v>
+        <v>2:54</v>
       </c>
       <c r="H178" t="str">
-        <v>TheARTI$t</v>
+        <v>nomi.</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L178" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>AUTOMATIC</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-03</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:08</v>
+        <v>2:26</v>
       </c>
       <c r="H179" t="str">
-        <v>Hulvey</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L179" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Leaving Egypt</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-03</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:17</v>
+        <v>2:08</v>
       </c>
       <c r="H180" t="str">
-        <v>Alex Jude</v>
+        <v>Hulvey</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L180" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Not Your Mother</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-03</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H181" t="str">
-        <v>gracie</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L181" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-03</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:50</v>
+        <v>3:03</v>
       </c>
       <c r="H182" t="str">
-        <v>Social Distortion</v>
+        <v>gracie</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L182" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>When the Love is Gone</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-03</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G183" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H183" t="str">
-        <v>Des Rocs</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L183" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Miami Crest</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-03</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Miami Crest - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:39</v>
+        <v>3:20</v>
       </c>
       <c r="H184" t="str">
-        <v>Namasenda</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L184" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Say No Prayer</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-03</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:29</v>
+        <v>2:39</v>
       </c>
       <c r="H185" t="str">
-        <v>oskar med k</v>
+        <v>Namasenda</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L185" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-03</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H186" t="str">
-        <v>eee gee</v>
+        <v>oskar med k</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L186" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Pink Tongue</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-03</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Porcelain Heart</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:43</v>
+        <v>3:09</v>
       </c>
       <c r="H187" t="str">
-        <v>Diane Emerita</v>
+        <v>eee gee</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L187" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-03</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G188" t="str">
-        <v>3:23</v>
+        <v>3:43</v>
       </c>
       <c r="H188" t="str">
-        <v>Ber</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L188" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-03</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:26</v>
+        <v>3:23</v>
       </c>
       <c r="H189" t="str">
-        <v>Forest Blakk</v>
+        <v>Ber</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L189" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Heartbeat</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-03</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Heartbeat - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:52</v>
+        <v>3:26</v>
       </c>
       <c r="H190" t="str">
-        <v>Lola Blue</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L190" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-03</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:16</v>
+        <v>2:52</v>
       </c>
       <c r="H191" t="str">
-        <v>doggone</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L191" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>I’m Every Woman</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-03</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:35</v>
+        <v>4:16</v>
       </c>
       <c r="H192" t="str">
-        <v>Ashley Jackson</v>
+        <v>doggone</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L192" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-03</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G193" t="str">
-        <v>2:46</v>
+        <v>4:35</v>
       </c>
       <c r="H193" t="str">
-        <v>Chris Morrissey</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L193" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Slow Tonight</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-03</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Full Circle</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G194" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H194" t="str">
-        <v>Tom Misch</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L194" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Freak No More</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-03</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Freak No More - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G195" t="str">
-        <v>3:57</v>
+        <v>3:12</v>
       </c>
       <c r="H195" t="str">
-        <v>AC Slater</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L195" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Don't Stop</v>
+        <v>Freak No More</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-03</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:55</v>
+        <v>3:57</v>
       </c>
       <c r="H196" t="str">
-        <v>HoneyLuv</v>
+        <v>AC Slater</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L196" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Cause I Do</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-03</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:39</v>
+        <v>2:55</v>
       </c>
       <c r="H197" t="str">
-        <v>Preston Pablo</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L197" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Morning Comes</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-03</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>4:11</v>
+        <v>2:39</v>
       </c>
       <c r="H198" t="str">
-        <v>Ty Myers</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L198" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>BETTER ON ME</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-03</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G199" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H199" t="str">
-        <v>Johnny Huynh</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L199" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Speed or Perish</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-03</v>
@@ -7975,68 +7975,106 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Leather Temple</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>4:30</v>
+        <v>3:24</v>
       </c>
       <c r="H200" t="str">
-        <v>Carpenter Brut</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L200" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G201" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D201" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
+      <c r="D202" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G201" t="str">
+      <c r="G202" t="str">
         <v>2:27</v>
       </c>
-      <c r="H201" t="str">
+      <c r="H202" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K201" t="str">
+      <c r="K202" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L201" t="str">
+      <c r="L202" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B3" t="str">
-        <v>Streamed 1 day ago</v>
+        <v>Streamed 2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Streamed 1 day ago</v>
+        <v>Streamed 2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>27:54:45</v>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -591,19 +591,19 @@
         <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:01</v>
@@ -629,19 +629,19 @@
         <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:31</v>
@@ -667,19 +667,19 @@
         <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:00</v>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -743,19 +743,19 @@
         <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:32</v>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1997,19 +1997,19 @@
         <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>6:21</v>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B67" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>3:22</v>
@@ -2947,19 +2947,19 @@
         <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B68" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>4:08</v>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B73" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>4:17</v>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3783,19 +3783,19 @@
         <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G90" t="str">
         <v>2:51</v>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4087,19 +4087,19 @@
         <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G98" t="str">
         <v>2:58</v>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E202" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>5:18</v>
@@ -553,7 +553,7 @@
         <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>7:20</v>
@@ -1237,7 +1237,7 @@
         <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:18</v>
@@ -1275,7 +1275,7 @@
         <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:50</v>
@@ -1313,7 +1313,7 @@
         <v>MyKey - Ride With Me</v>
       </c>
       <c r="B25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>3:24</v>
@@ -1351,7 +1351,7 @@
         <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>2:36</v>
@@ -1389,7 +1389,7 @@
         <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:34</v>
@@ -1427,7 +1427,7 @@
         <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>4:03</v>
@@ -1465,7 +1465,7 @@
         <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:31</v>
@@ -1503,7 +1503,7 @@
         <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:22</v>
@@ -1541,7 +1541,7 @@
         <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>5:49</v>
@@ -1579,7 +1579,7 @@
         <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:47</v>
@@ -1617,7 +1617,7 @@
         <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>2:20</v>
@@ -1655,7 +1655,7 @@
         <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>4:18</v>
@@ -1693,7 +1693,7 @@
         <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>2:39</v>
@@ -1731,7 +1731,7 @@
         <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>3:52</v>
@@ -1769,7 +1769,7 @@
         <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>4:01</v>
@@ -1807,7 +1807,7 @@
         <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>2:54</v>
@@ -1921,7 +1921,7 @@
         <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:06</v>
@@ -1959,7 +1959,7 @@
         <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>2:43</v>
@@ -2339,7 +2339,7 @@
         <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>3:40</v>
@@ -2377,7 +2377,7 @@
         <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>2:49</v>
@@ -3365,7 +3365,7 @@
         <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>4:22</v>
@@ -3441,7 +3441,7 @@
         <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>3:02</v>
@@ -3479,7 +3479,7 @@
         <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>3:12</v>
@@ -3517,7 +3517,7 @@
         <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B83" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>3:38</v>
@@ -3555,7 +3555,7 @@
         <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>4:40</v>
@@ -3593,7 +3593,7 @@
         <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>2:57</v>
@@ -3631,7 +3631,7 @@
         <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B86" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>2:13</v>
@@ -3669,7 +3669,7 @@
         <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G87" t="str">
         <v>4:12</v>
@@ -3707,7 +3707,7 @@
         <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B88" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G88" t="str">
         <v>2:55</v>
@@ -3745,7 +3745,7 @@
         <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:51</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:30</v>
@@ -1161,7 +1161,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>5:12</v>
@@ -1199,7 +1199,7 @@
         <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>3:47</v>
@@ -2301,7 +2301,7 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:47</v>
@@ -2415,7 +2415,7 @@
         <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>4:49</v>
@@ -2681,7 +2681,7 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>4:39</v>
@@ -2719,7 +2719,7 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:40</v>
@@ -2757,7 +2757,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:57</v>
@@ -2871,7 +2871,7 @@
         <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B66" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>5:52</v>
@@ -3213,7 +3213,7 @@
         <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>4:50</v>
@@ -3251,7 +3251,7 @@
         <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>3:14</v>
@@ -3289,7 +3289,7 @@
         <v>Jessie Ware - Ride</v>
       </c>
       <c r="B77" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>4:37</v>
@@ -3327,7 +3327,7 @@
         <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B78" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>3:16</v>
@@ -3403,7 +3403,7 @@
         <v>Suburban Requiem</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>4:40</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L203"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -705,7 +705,7 @@
         <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:11</v>
@@ -819,7 +819,7 @@
         <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>4:50</v>
@@ -857,7 +857,7 @@
         <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:53</v>
@@ -895,7 +895,7 @@
         <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:04</v>
@@ -933,7 +933,7 @@
         <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>4:32</v>
@@ -971,7 +971,7 @@
         <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:47</v>
@@ -1009,7 +1009,7 @@
         <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:40</v>
@@ -1047,7 +1047,7 @@
         <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>4:05</v>
@@ -1085,7 +1085,7 @@
         <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>2:59</v>
@@ -1123,7 +1123,7 @@
         <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:55</v>
@@ -1845,7 +1845,7 @@
         <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>4:03</v>
@@ -1883,7 +1883,7 @@
         <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:50</v>
@@ -2035,7 +2035,7 @@
         <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>2:46</v>
@@ -2073,7 +2073,7 @@
         <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:42</v>
@@ -2111,7 +2111,7 @@
         <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:04</v>
@@ -2149,7 +2149,7 @@
         <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:59</v>
@@ -2187,7 +2187,7 @@
         <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:22</v>
@@ -2225,7 +2225,7 @@
         <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>3:53</v>
@@ -2263,7 +2263,7 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>2:28</v>
@@ -2491,7 +2491,7 @@
         <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>2:59</v>
@@ -2529,7 +2529,7 @@
         <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>4:38</v>
@@ -2567,7 +2567,7 @@
         <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:46</v>
@@ -2605,7 +2605,7 @@
         <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:08</v>
@@ -2643,7 +2643,7 @@
         <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>5:32</v>
@@ -2833,7 +2833,7 @@
         <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>4:49</v>
@@ -2985,7 +2985,7 @@
         <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B69" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>7:31</v>
@@ -3023,7 +3023,7 @@
         <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B70" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>3:21</v>
@@ -3061,7 +3061,7 @@
         <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>4:36</v>
@@ -3099,7 +3099,7 @@
         <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>5:06</v>
@@ -3175,7 +3175,7 @@
         <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>3:20</v>
@@ -3859,7 +3859,7 @@
         <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B92" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>4:11</v>
@@ -3897,7 +3897,7 @@
         <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:27</v>
@@ -3935,7 +3935,7 @@
         <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B94" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>3:06</v>
@@ -3973,7 +3973,7 @@
         <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B95" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G95" t="str">
         <v>3:01</v>
@@ -4011,7 +4011,7 @@
         <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B96" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>5:38</v>
@@ -4049,7 +4049,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B97" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v>3:43</v>
@@ -4125,7 +4125,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B99" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v>4:13</v>
@@ -4163,7 +4163,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v>5:48</v>
@@ -4201,7 +4201,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B101" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:55</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SOMEWHERE ELSE</v>
+        <v>Medicine</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
+        <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-04</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>COME CLOSER</v>
+        <v>Medicine - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>4:11</v>
+        <v>2:34</v>
       </c>
       <c r="H102" t="str">
-        <v>TOMORA</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
+        <v>https://music.apple.com/us/album/medicine/1874168007</v>
       </c>
       <c r="L102" t="str">
-        <v>SOMEWHERE ELSE - TOMORA</v>
+        <v>Medicine - Channel Tres</v>
       </c>
     </row>
     <row r="103">
@@ -4654,13 +4654,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Dog</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-04</v>
@@ -4669,25 +4669,25 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Torn</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G113" t="str">
-        <v>2:37</v>
+        <v>4:11</v>
       </c>
       <c r="H113" t="str">
-        <v>Cobrah</v>
+        <v>TOMORA</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L113" t="str">
-        <v>Dog - Cobrah</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="114">
@@ -4730,13 +4730,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>Dog</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-04</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Torn</v>
       </c>
       <c r="G115" t="str">
-        <v>2:39</v>
+        <v>2:37</v>
       </c>
       <c r="H115" t="str">
-        <v>Slayyyter</v>
+        <v>Cobrah</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L115" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ALICE</v>
+        <v>OLD TECHNOLOGY</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-04</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G116" t="str">
-        <v>4:39</v>
+        <v>2:39</v>
       </c>
       <c r="H116" t="str">
-        <v>Erin LeCount</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
       </c>
       <c r="L116" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>OLD TECHNOLOGY - Slayyyter</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Tiny Light</v>
+        <v>ALICE</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-04</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Tiny Light - Single</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G117" t="str">
-        <v>3:27</v>
+        <v>4:39</v>
       </c>
       <c r="H117" t="str">
-        <v>SEVENTEEN</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L117" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-04</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:50</v>
+        <v>3:27</v>
       </c>
       <c r="H118" t="str">
-        <v>aespa</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L118" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-04</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H119" t="str">
-        <v>Concrete Boys</v>
+        <v>aespa</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L119" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>If I Leave</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-04</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G120" t="str">
-        <v>3:00</v>
+        <v>3:23</v>
       </c>
       <c r="H120" t="str">
-        <v>Mitski</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L120" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Time Will Tell</v>
+        <v>If I Leave</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-04</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G121" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H121" t="str">
-        <v>Lee Brice</v>
+        <v>Mitski</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L121" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>How I Get</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-04</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H122" t="str">
-        <v>Laufey</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L122" t="str">
-        <v>How I Get - Laufey</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>How I Get</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-04</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G123" t="str">
-        <v>3:19</v>
+        <v>3:39</v>
       </c>
       <c r="H123" t="str">
-        <v>Jessie Murph</v>
+        <v>Laufey</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L123" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tonto</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-04</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Tonto - Single</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:20</v>
+        <v>3:19</v>
       </c>
       <c r="H124" t="str">
-        <v>J Balvin</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L124" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>Tonto</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-04</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:41</v>
+        <v>2:20</v>
       </c>
       <c r="H125" t="str">
-        <v>BLOND:ISH</v>
+        <v>J Balvin</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L125" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-04</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:50</v>
+        <v>2:41</v>
       </c>
       <c r="H126" t="str">
-        <v>Bautiii</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L126" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-04</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H127" t="str">
-        <v>Mýa</v>
+        <v>Bautiii</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L127" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-04</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>FENIAN</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:11</v>
+        <v>3:41</v>
       </c>
       <c r="H128" t="str">
-        <v>Kneecap</v>
+        <v>Mýa</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L128" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>What You Want</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-04</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>What You Want - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G129" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H129" t="str">
-        <v>Angèle</v>
+        <v>Kneecap</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L129" t="str">
-        <v>What You Want - Angèle</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>psychokiller</v>
+        <v>What You Want</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-04</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>getting up to no good</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>1:53</v>
+        <v>3:08</v>
       </c>
       <c r="H130" t="str">
-        <v>Artemas</v>
+        <v>Angèle</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L130" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>psychokiller</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-04</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>HADES</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G131" t="str">
-        <v>4:05</v>
+        <v>1:53</v>
       </c>
       <c r="H131" t="str">
-        <v>Melanie Martinez</v>
+        <v>Artemas</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L131" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>mariah</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-04</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>HADES</v>
       </c>
       <c r="G132" t="str">
-        <v>2:48</v>
+        <v>4:05</v>
       </c>
       <c r="H132" t="str">
-        <v>Lauv</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L132" t="str">
-        <v>mariah - Lauv</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>BLACKHOLE</v>
+        <v>mariah</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-04</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>REVIVE+</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G133" t="str">
-        <v>3:14</v>
+        <v>2:48</v>
       </c>
       <c r="H133" t="str">
-        <v>IVE</v>
+        <v>Lauv</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L133" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Walk</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-04</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Walk - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G134" t="str">
-        <v>2:56</v>
+        <v>3:14</v>
       </c>
       <c r="H134" t="str">
-        <v>Skye Newman</v>
+        <v>IVE</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L134" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>FLAMMABLE</v>
+        <v>Walk</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-04</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:17</v>
+        <v>2:56</v>
       </c>
       <c r="H135" t="str">
-        <v>Swae Lee</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L135" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>3am (Remix)</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-04</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>3am (Remix) - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:44</v>
+        <v>3:17</v>
       </c>
       <c r="H136" t="str">
-        <v>Łaszewo</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L136" t="str">
-        <v>3am (Remix) - Łaszewo</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>mutual destruction</v>
+        <v>3am (Remix)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-04</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>mutual destruction - Single</v>
+        <v>3am (Remix) - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:31</v>
+        <v>2:44</v>
       </c>
       <c r="H137" t="str">
-        <v>kenzie</v>
+        <v>Łaszewo</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
       </c>
       <c r="L137" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>3am (Remix) - Łaszewo</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Dear Worry</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-04</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Dear Worry - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H138" t="str">
-        <v>Common People</v>
+        <v>kenzie</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L138" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Gentleman</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-04</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Gentleman - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:16</v>
+        <v>3:01</v>
       </c>
       <c r="H139" t="str">
-        <v>Towa Bird</v>
+        <v>Common People</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L139" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>NYX00</v>
+        <v>Gentleman</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-04</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>NYX00 - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:00</v>
+        <v>2:16</v>
       </c>
       <c r="H140" t="str">
-        <v>Dei V</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L140" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Helicopters</v>
+        <v>NYX00</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-04</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>HELP(2)</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:58</v>
+        <v>3:00</v>
       </c>
       <c r="H141" t="str">
-        <v>Ezra Collective</v>
+        <v>Dei V</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L141" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Helicopters</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-04</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G142" t="str">
-        <v>4:58</v>
+        <v>3:58</v>
       </c>
       <c r="H142" t="str">
-        <v>Max Richter</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L142" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>It's You I Want</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-04</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G143" t="str">
-        <v>1:39</v>
+        <v>4:58</v>
       </c>
       <c r="H143" t="str">
-        <v>Kris Bowers</v>
+        <v>Max Richter</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L143" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>If I Was With You</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-04</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G144" t="str">
-        <v>3:25</v>
+        <v>1:39</v>
       </c>
       <c r="H144" t="str">
-        <v>Presley Regier</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L144" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Stay With Me</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-04</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H145" t="str">
-        <v>Nessa Barrett</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L145" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>My Loving</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-04</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>My Loving - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G146" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H146" t="str">
-        <v>Sonny Fodera</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L146" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Easy On The Eyes</v>
+        <v>My Loving</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-04</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:44</v>
+        <v>2:50</v>
       </c>
       <c r="H147" t="str">
-        <v>Willow Avalon</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L147" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Beautiful</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-04</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Let It Die Here</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:47</v>
+        <v>3:44</v>
       </c>
       <c r="H148" t="str">
-        <v>Linda Perry</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L148" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Beautiful</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-04</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G149" t="str">
-        <v>4:34</v>
+        <v>3:47</v>
       </c>
       <c r="H149" t="str">
-        <v>Jason Segel</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L149" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Control Freak</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-04</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Control Freak - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:53</v>
+        <v>4:34</v>
       </c>
       <c r="H150" t="str">
-        <v>Broadside</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L150" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Done For</v>
+        <v>Control Freak</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-04</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Done For - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:33</v>
+        <v>2:53</v>
       </c>
       <c r="H151" t="str">
-        <v>Max McNown</v>
+        <v>Broadside</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L151" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ready for the Ride</v>
+        <v>Done For</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-04</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H152" t="str">
-        <v>Sean Paul</v>
+        <v>Max McNown</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L152" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>push the pipe</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-04</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H153" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L153" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>push the pipe</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-04</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>With No Due Respect</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G154" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H154" t="str">
-        <v>Foggieraw</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L154" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Moonlight</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-04</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>McKenzie 2.0</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G155" t="str">
-        <v>2:00</v>
+        <v>3:13</v>
       </c>
       <c r="H155" t="str">
-        <v>FattMack</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L155" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Boat Named After You</v>
+        <v>Moonlight</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-04</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G156" t="str">
-        <v>3:56</v>
+        <v>2:00</v>
       </c>
       <c r="H156" t="str">
-        <v>ERNEST</v>
+        <v>FattMack</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L156" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>fall into you</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-04</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>fall into you - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H157" t="str">
-        <v>Camylio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L157" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Van Gogh</v>
+        <v>fall into you</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-04</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:25</v>
+        <v>3:28</v>
       </c>
       <c r="H158" t="str">
-        <v>Em Beihold</v>
+        <v>Camylio</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L158" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>popstar Nervous</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-04</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>the rumors are true - EP</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G159" t="str">
         <v>2:25</v>
       </c>
       <c r="H159" t="str">
-        <v>DC THE DON</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L159" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Free</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-04</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Free - Single</v>
+        <v>the rumors are true - EP</v>
       </c>
       <c r="G160" t="str">
-        <v>3:08</v>
+        <v>2:25</v>
       </c>
       <c r="H160" t="str">
-        <v>Beartooth</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L160" t="str">
-        <v>Free - Beartooth</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>never come never morning</v>
+        <v>Free</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-04</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>a short history of decay</v>
+        <v>Free - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:39</v>
+        <v>3:08</v>
       </c>
       <c r="H161" t="str">
-        <v>Nothing</v>
+        <v>Beartooth</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L161" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Over My Head</v>
+        <v>never come never morning</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-04</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G162" t="str">
-        <v>2:30</v>
+        <v>3:39</v>
       </c>
       <c r="H162" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Nothing</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L162" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Mantis</v>
+        <v>Over My Head</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-04</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Creature of Habit</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G163" t="str">
-        <v>4:40</v>
+        <v>2:30</v>
       </c>
       <c r="H163" t="str">
-        <v>Courtney Barnett</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L163" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Soft Launch</v>
+        <v>Mantis</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-04</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G164" t="str">
-        <v>2:25</v>
+        <v>4:40</v>
       </c>
       <c r="H164" t="str">
-        <v>Cely</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L164" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>picky choosy</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-04</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:53</v>
+        <v>2:25</v>
       </c>
       <c r="H165" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Cely</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L165" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>La Mala Era Yo</v>
+        <v>picky choosy</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-04</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G166" t="str">
-        <v>2:30</v>
+        <v>2:53</v>
       </c>
       <c r="H166" t="str">
-        <v>Kany García</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L166" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Quiet Part Loud</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-04</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Joy Next Door</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:08</v>
+        <v>2:30</v>
       </c>
       <c r="H167" t="str">
-        <v>The Maine</v>
+        <v>Kany García</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L167" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>favorite girl</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-04</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>favorite girl - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G168" t="str">
-        <v>3:24</v>
+        <v>3:08</v>
       </c>
       <c r="H168" t="str">
-        <v>Alaina Castillo</v>
+        <v>The Maine</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L168" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>The Blade</v>
+        <v>favorite girl</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-04</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>The Blade - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H169" t="str">
-        <v>Kingfishr</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L169" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Blunt Force Blues</v>
+        <v>The Blade</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-04</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Into Oblivion</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>4:11</v>
+        <v>3:15</v>
       </c>
       <c r="H170" t="str">
-        <v>Lamb of God</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L170" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>The Black Scorpion</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-04</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>The Great Satan</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G171" t="str">
-        <v>1:33</v>
+        <v>4:11</v>
       </c>
       <c r="H171" t="str">
-        <v>Rob Zombie</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L171" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>The Place</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-04</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G172" t="str">
-        <v>5:58</v>
+        <v>1:33</v>
       </c>
       <c r="H172" t="str">
-        <v>Sepultura</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L172" t="str">
-        <v>The Place - Sepultura</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>The Place</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-04</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>3:18</v>
+        <v>5:58</v>
       </c>
       <c r="H173" t="str">
-        <v>Wage War</v>
+        <v>Sepultura</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L173" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-04</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H174" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Wage War</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L174" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Tu Cárcel</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-04</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:36</v>
+        <v>2:26</v>
       </c>
       <c r="H175" t="str">
-        <v>Morat</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L175" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Facts</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-04</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Be Very Afraid (Vol. 1)</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H176" t="str">
-        <v>CHASE B</v>
+        <v>Morat</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L176" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>me &amp; you</v>
+        <v>Facts</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-04</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>big country</v>
+        <v>Be Very Afraid (Vol. 1)</v>
       </c>
       <c r="G177" t="str">
-        <v>2:29</v>
+        <v>3:29</v>
       </c>
       <c r="H177" t="str">
-        <v>sosocamo</v>
+        <v>CHASE B</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L177" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>badman</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-04</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>badman - Single</v>
+        <v>big country</v>
       </c>
       <c r="G178" t="str">
-        <v>2:54</v>
+        <v>2:29</v>
       </c>
       <c r="H178" t="str">
-        <v>nomi.</v>
+        <v>sosocamo</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L178" t="str">
-        <v>badman - nomi.</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Shut It Down</v>
+        <v>badman</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-04</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Shut It Down - Single</v>
+        <v>badman - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:26</v>
+        <v>2:54</v>
       </c>
       <c r="H179" t="str">
-        <v>TheARTI$t</v>
+        <v>nomi.</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L179" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>AUTOMATIC</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-04</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:08</v>
+        <v>2:26</v>
       </c>
       <c r="H180" t="str">
-        <v>Hulvey</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L180" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Leaving Egypt</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-04</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:17</v>
+        <v>2:08</v>
       </c>
       <c r="H181" t="str">
-        <v>Alex Jude</v>
+        <v>Hulvey</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L181" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Not Your Mother</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-04</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H182" t="str">
-        <v>gracie</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L182" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-04</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:50</v>
+        <v>3:03</v>
       </c>
       <c r="H183" t="str">
-        <v>Social Distortion</v>
+        <v>gracie</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L183" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>When the Love is Gone</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-04</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G184" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H184" t="str">
-        <v>Des Rocs</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L184" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Miami Crest</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-04</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Miami Crest - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:39</v>
+        <v>3:20</v>
       </c>
       <c r="H185" t="str">
-        <v>Namasenda</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L185" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Say No Prayer</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-04</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:29</v>
+        <v>2:39</v>
       </c>
       <c r="H186" t="str">
-        <v>oskar med k</v>
+        <v>Namasenda</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L186" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-04</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H187" t="str">
-        <v>eee gee</v>
+        <v>oskar med k</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L187" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Pink Tongue</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-04</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Porcelain Heart</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:43</v>
+        <v>3:09</v>
       </c>
       <c r="H188" t="str">
-        <v>Diane Emerita</v>
+        <v>eee gee</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L188" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-04</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G189" t="str">
-        <v>3:23</v>
+        <v>3:43</v>
       </c>
       <c r="H189" t="str">
-        <v>Ber</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L189" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-04</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:26</v>
+        <v>3:23</v>
       </c>
       <c r="H190" t="str">
-        <v>Forest Blakk</v>
+        <v>Ber</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L190" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Heartbeat</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-04</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Heartbeat - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:52</v>
+        <v>3:26</v>
       </c>
       <c r="H191" t="str">
-        <v>Lola Blue</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L191" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-04</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:16</v>
+        <v>2:52</v>
       </c>
       <c r="H192" t="str">
-        <v>doggone</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L192" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>I’m Every Woman</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-04</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:35</v>
+        <v>4:16</v>
       </c>
       <c r="H193" t="str">
-        <v>Ashley Jackson</v>
+        <v>doggone</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L193" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-04</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G194" t="str">
-        <v>2:46</v>
+        <v>4:35</v>
       </c>
       <c r="H194" t="str">
-        <v>Chris Morrissey</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L194" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Slow Tonight</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-04</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Full Circle</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G195" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H195" t="str">
-        <v>Tom Misch</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L195" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Freak No More</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-04</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Freak No More - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G196" t="str">
-        <v>3:57</v>
+        <v>3:12</v>
       </c>
       <c r="H196" t="str">
-        <v>AC Slater</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L196" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Don't Stop</v>
+        <v>Freak No More</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-04</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:55</v>
+        <v>3:57</v>
       </c>
       <c r="H197" t="str">
-        <v>HoneyLuv</v>
+        <v>AC Slater</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L197" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Cause I Do</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-04</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:39</v>
+        <v>2:55</v>
       </c>
       <c r="H198" t="str">
-        <v>Preston Pablo</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L198" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Morning Comes</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-04</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>4:11</v>
+        <v>2:39</v>
       </c>
       <c r="H199" t="str">
-        <v>Ty Myers</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L199" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>BETTER ON ME</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-04</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G200" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H200" t="str">
-        <v>Johnny Huynh</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L200" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Speed or Perish</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-04</v>
@@ -8013,68 +8013,106 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Leather Temple</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>4:30</v>
+        <v>3:24</v>
       </c>
       <c r="H201" t="str">
-        <v>Carpenter Brut</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L201" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G202" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D202" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
+      <c r="D203" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G202" t="str">
+      <c r="G203" t="str">
         <v>2:27</v>
       </c>
-      <c r="H202" t="str">
+      <c r="H203" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K202" t="str">
+      <c r="K203" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L202" t="str">
+      <c r="L203" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -781,7 +781,7 @@
         <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B11" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>5:03</v>
@@ -2453,7 +2453,7 @@
         <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>3:35</v>
@@ -2795,7 +2795,7 @@
         <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B64" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>2:27</v>
@@ -3821,7 +3821,7 @@
         <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G91" t="str">
         <v>3:24</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -667,7 +667,7 @@
         <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:00</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -436,28 +436,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>4:30</v>
+        <v>4:37</v>
       </c>
       <c r="H2" t="str">
-        <v>Jessie J</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,33 +469,33 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B3" t="str">
-        <v>Streamed 2 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Streamed 2 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>27:54:45</v>
+        <v>4:52</v>
       </c>
       <c r="H3" t="str">
-        <v>BRITs</v>
+        <v>Cannons</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,33 +507,33 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B4" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>5:18</v>
+        <v>2:13</v>
       </c>
       <c r="H4" t="str">
-        <v>Harry Styles</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,33 +545,33 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B5" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>7:20</v>
+        <v>3:19</v>
       </c>
       <c r="H5" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,33 +583,33 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H6" t="str">
-        <v>BRITs</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,33 +621,33 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:31</v>
+        <v>2:43</v>
       </c>
       <c r="H7" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,33 +659,33 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B8" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:00</v>
+        <v>3:10</v>
       </c>
       <c r="H8" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,33 +697,33 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:11</v>
+        <v>3:55</v>
       </c>
       <c r="H9" t="str">
-        <v>The Kiffness</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,33 +735,33 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B10" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:32</v>
+        <v>3:52</v>
       </c>
       <c r="H10" t="str">
-        <v>Lauv</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,33 +773,33 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>5:03</v>
+        <v>2:53</v>
       </c>
       <c r="H11" t="str">
-        <v>RAYE</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:50</v>
+        <v>4:30</v>
       </c>
       <c r="H12" t="str">
-        <v>Armik</v>
+        <v>Jessie J</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>Streamed 3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>Streamed 3 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:53</v>
+        <v>27:54:45</v>
       </c>
       <c r="H13" t="str">
-        <v>Scorpions</v>
+        <v>BRITs</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:04</v>
+        <v>5:18</v>
       </c>
       <c r="H14" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,33 +925,33 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:32</v>
+        <v>7:20</v>
       </c>
       <c r="H15" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:47</v>
+        <v>3:01</v>
       </c>
       <c r="H16" t="str">
-        <v>Girl Tones</v>
+        <v>BRITs</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,33 +1001,33 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:40</v>
+        <v>3:31</v>
       </c>
       <c r="H17" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:05</v>
+        <v>3:00</v>
       </c>
       <c r="H18" t="str">
-        <v>HAUSER</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:59</v>
+        <v>3:11</v>
       </c>
       <c r="H19" t="str">
-        <v>Queen Official</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B20" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1138,10 +1138,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:55</v>
+        <v>3:32</v>
       </c>
       <c r="H20" t="str">
-        <v>Tenille Townes</v>
+        <v>Lauv</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B21" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1176,10 +1176,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:12</v>
+        <v>5:03</v>
       </c>
       <c r="H21" t="str">
-        <v>Self Esteem</v>
+        <v>RAYE</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B22" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1214,10 +1214,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:47</v>
+        <v>4:50</v>
       </c>
       <c r="H22" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Armik</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B23" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1252,10 +1252,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:18</v>
+        <v>4:53</v>
       </c>
       <c r="H23" t="str">
-        <v>Em Beihold</v>
+        <v>Scorpions</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B24" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1290,10 +1290,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:50</v>
+        <v>3:04</v>
       </c>
       <c r="H24" t="str">
-        <v>Michael Bublé</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B25" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1328,10 +1328,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:24</v>
+        <v>4:32</v>
       </c>
       <c r="H25" t="str">
-        <v>MyKey</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1366,10 +1366,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:36</v>
+        <v>3:47</v>
       </c>
       <c r="H26" t="str">
-        <v>Max McNown</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B27" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:34</v>
+        <v>3:40</v>
       </c>
       <c r="H27" t="str">
-        <v>Megan Moroney</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B28" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1442,10 +1442,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:03</v>
+        <v>4:05</v>
       </c>
       <c r="H28" t="str">
-        <v>ERNEST</v>
+        <v>HAUSER</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,21 +1457,21 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1480,10 +1480,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:31</v>
+        <v>2:59</v>
       </c>
       <c r="H29" t="str">
-        <v>Bruno Mars</v>
+        <v>Queen Official</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,21 +1495,21 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B30" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1518,10 +1518,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:22</v>
+        <v>3:55</v>
       </c>
       <c r="H30" t="str">
-        <v>BLACKPINK</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,21 +1533,21 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B31" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1556,10 +1556,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:49</v>
+        <v>5:12</v>
       </c>
       <c r="H31" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,21 +1571,21 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B32" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1597,7 +1597,7 @@
         <v>3:47</v>
       </c>
       <c r="H32" t="str">
-        <v>Nessa Barrett</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,21 +1609,21 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B33" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1632,10 +1632,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:20</v>
+        <v>3:18</v>
       </c>
       <c r="H33" t="str">
-        <v>Towa Bird</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,21 +1647,21 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B34" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1670,10 +1670,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:18</v>
+        <v>3:50</v>
       </c>
       <c r="H34" t="str">
-        <v>Ty Myers</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,21 +1685,21 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B35" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1708,10 +1708,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:39</v>
+        <v>3:24</v>
       </c>
       <c r="H35" t="str">
-        <v>kenzie</v>
+        <v>MyKey</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,21 +1723,21 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1746,10 +1746,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:52</v>
+        <v>2:36</v>
       </c>
       <c r="H36" t="str">
-        <v>Leanna Crawford</v>
+        <v>Max McNown</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,21 +1761,21 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1784,10 +1784,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H37" t="str">
-        <v>Bryan Adams</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,21 +1799,21 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B38" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1822,10 +1822,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:54</v>
+        <v>4:03</v>
       </c>
       <c r="H38" t="str">
-        <v>CHESCA</v>
+        <v>ERNEST</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:03</v>
+        <v>3:31</v>
       </c>
       <c r="H39" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:50</v>
+        <v>3:22</v>
       </c>
       <c r="H40" t="str">
-        <v>earMUSIC</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:06</v>
+        <v>5:49</v>
       </c>
       <c r="H41" t="str">
-        <v>Y2K</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:43</v>
+        <v>3:47</v>
       </c>
       <c r="H42" t="str">
-        <v>Lainey Wilson</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>6:21</v>
+        <v>2:20</v>
       </c>
       <c r="H43" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:46</v>
+        <v>4:18</v>
       </c>
       <c r="H44" t="str">
-        <v>Bryan Ferry</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:42</v>
+        <v>2:39</v>
       </c>
       <c r="H45" t="str">
-        <v>Saint Harison</v>
+        <v>kenzie</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:04</v>
+        <v>3:52</v>
       </c>
       <c r="H46" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:59</v>
+        <v>4:01</v>
       </c>
       <c r="H47" t="str">
-        <v>Catie Turner</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:22</v>
+        <v>2:54</v>
       </c>
       <c r="H48" t="str">
-        <v>Lauren Sanderson</v>
+        <v>CHESCA</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:53</v>
+        <v>4:03</v>
       </c>
       <c r="H49" t="str">
-        <v>Roxette</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:28</v>
+        <v>4:50</v>
       </c>
       <c r="H50" t="str">
-        <v>Marcin</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:47</v>
+        <v>3:06</v>
       </c>
       <c r="H51" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Y2K</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:40</v>
+        <v>2:43</v>
       </c>
       <c r="H52" t="str">
-        <v>Laufey</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,21 +2369,21 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B53" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2392,10 +2392,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:49</v>
+        <v>6:21</v>
       </c>
       <c r="H53" t="str">
-        <v>Ava Max</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:49</v>
+        <v>2:46</v>
       </c>
       <c r="H54" t="str">
-        <v>U2</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:35</v>
+        <v>2:42</v>
       </c>
       <c r="H55" t="str">
-        <v>Taylor Swift</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:59</v>
+        <v>3:04</v>
       </c>
       <c r="H56" t="str">
-        <v>Kiana Ledé</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:38</v>
+        <v>2:59</v>
       </c>
       <c r="H57" t="str">
-        <v>Jessie Ware</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:46</v>
+        <v>2:22</v>
       </c>
       <c r="H58" t="str">
-        <v>Madison Beer</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:08</v>
+        <v>3:53</v>
       </c>
       <c r="H59" t="str">
-        <v>Sean Stemaly</v>
+        <v>Roxette</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>5:32</v>
+        <v>2:28</v>
       </c>
       <c r="H60" t="str">
-        <v>earMUSIC</v>
+        <v>Marcin</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:39</v>
+        <v>2:47</v>
       </c>
       <c r="H61" t="str">
-        <v>georgemichael</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:40</v>
       </c>
       <c r="H62" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Laufey</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:57</v>
+        <v>2:49</v>
       </c>
       <c r="H63" t="str">
-        <v>Self Esteem</v>
+        <v>Ava Max</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B64" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:27</v>
+        <v>4:49</v>
       </c>
       <c r="H64" t="str">
-        <v>070 Shake</v>
+        <v>U2</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:49</v>
+        <v>3:35</v>
       </c>
       <c r="H65" t="str">
-        <v>georgemichael</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B66" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:52</v>
+        <v>2:59</v>
       </c>
       <c r="H66" t="str">
-        <v>georgemichael</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B67" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:22</v>
+        <v>4:38</v>
       </c>
       <c r="H67" t="str">
-        <v>Foo Fighters</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B68" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:08</v>
+        <v>3:46</v>
       </c>
       <c r="H68" t="str">
-        <v>Romeo Santos and 2 more</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>7:31</v>
+        <v>3:08</v>
       </c>
       <c r="H69" t="str">
-        <v>Jacob Collier</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B70" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:21</v>
+        <v>5:32</v>
       </c>
       <c r="H70" t="str">
-        <v>Gabi Sklar</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B71" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:36</v>
+        <v>4:39</v>
       </c>
       <c r="H71" t="str">
-        <v>YUNGBLUD</v>
+        <v>georgemichael</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B72" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>5:06</v>
+        <v>3:40</v>
       </c>
       <c r="H72" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B73" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:17</v>
+        <v>3:57</v>
       </c>
       <c r="H73" t="str">
-        <v>Marc Anthony and 2 more</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B74" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:20</v>
+        <v>2:27</v>
       </c>
       <c r="H74" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:50</v>
+        <v>4:49</v>
       </c>
       <c r="H75" t="str">
-        <v>Cliff Richard</v>
+        <v>georgemichael</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:14</v>
+        <v>5:52</v>
       </c>
       <c r="H76" t="str">
-        <v>Freya Ridings</v>
+        <v>georgemichael</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,21 +3281,21 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B77" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3304,10 +3304,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:37</v>
+        <v>3:22</v>
       </c>
       <c r="H77" t="str">
-        <v>Jessie Ware</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,21 +3319,21 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B78" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3342,10 +3342,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:16</v>
+        <v>4:08</v>
       </c>
       <c r="H78" t="str">
-        <v>Alan Walker</v>
+        <v>Romeo Santos and 2 more</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,21 +3357,21 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B79" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3380,10 +3380,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:22</v>
+        <v>7:31</v>
       </c>
       <c r="H79" t="str">
-        <v>The Neighbourhood</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Suburban Requiem</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:40</v>
+        <v>3:21</v>
       </c>
       <c r="H80" t="str">
-        <v>YUNGBLUD</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,21 +3433,21 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3456,10 +3456,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:02</v>
+        <v>4:36</v>
       </c>
       <c r="H81" t="str">
-        <v>Calum Scott</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,21 +3471,21 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B82" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3494,10 +3494,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:12</v>
+        <v>5:06</v>
       </c>
       <c r="H82" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,21 +3509,21 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B83" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3532,10 +3532,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:38</v>
+        <v>4:17</v>
       </c>
       <c r="H83" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Marc Anthony and 2 more</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,21 +3547,21 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B84" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:40</v>
+        <v>3:20</v>
       </c>
       <c r="H84" t="str">
-        <v>Cannons</v>
+        <v>georgemichael</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,21 +3585,21 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B85" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3608,10 +3608,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:57</v>
+        <v>4:50</v>
       </c>
       <c r="H85" t="str">
-        <v>Mimi Webb</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,21 +3623,21 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3646,10 +3646,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:13</v>
+        <v>3:14</v>
       </c>
       <c r="H86" t="str">
-        <v>Jorja Smith</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,21 +3661,21 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B87" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3684,10 +3684,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:12</v>
+        <v>4:37</v>
       </c>
       <c r="H87" t="str">
-        <v>Sam Williams</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,21 +3699,21 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B88" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3722,10 +3722,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:55</v>
+        <v>3:16</v>
       </c>
       <c r="H88" t="str">
-        <v>YUNGBLUD</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,21 +3737,21 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3760,10 +3760,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:51</v>
+        <v>4:22</v>
       </c>
       <c r="H89" t="str">
-        <v>Megan Moroney</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B90" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:51</v>
+        <v>4:40</v>
       </c>
       <c r="H90" t="str">
-        <v>Nico Santos</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B91" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:24</v>
+        <v>3:02</v>
       </c>
       <c r="H91" t="str">
-        <v>REALITY CLUB</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:11</v>
+        <v>3:12</v>
       </c>
       <c r="H92" t="str">
-        <v>We Three</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:27</v>
+        <v>3:38</v>
       </c>
       <c r="H93" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:06</v>
+        <v>4:40</v>
       </c>
       <c r="H94" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>Cannons</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:01</v>
+        <v>2:57</v>
       </c>
       <c r="H95" t="str">
-        <v>Peach PRC</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B96" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:38</v>
+        <v>2:13</v>
       </c>
       <c r="H96" t="str">
-        <v>georgemichael</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:43</v>
+        <v>4:12</v>
       </c>
       <c r="H97" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>13 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:58</v>
+        <v>2:55</v>
       </c>
       <c r="H98" t="str">
-        <v>Catie Turner</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:13</v>
+        <v>3:51</v>
       </c>
       <c r="H99" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:48</v>
+        <v>2:51</v>
       </c>
       <c r="H100" t="str">
-        <v>U2</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:55</v>
+        <v>3:24</v>
       </c>
       <c r="H101" t="str">
-        <v>Lawrence</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="102">
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E203" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:37</v>
@@ -477,7 +477,7 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B3" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>11 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:52</v>
@@ -781,7 +781,7 @@
         <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:53</v>
@@ -1617,7 +1617,7 @@
         <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:18</v>
@@ -1655,7 +1655,7 @@
         <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:50</v>
@@ -1693,7 +1693,7 @@
         <v>MyKey - Ride With Me</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:24</v>
@@ -1731,7 +1731,7 @@
         <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>2:36</v>
@@ -1769,7 +1769,7 @@
         <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:34</v>
@@ -1807,7 +1807,7 @@
         <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>4:03</v>
@@ -1845,7 +1845,7 @@
         <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:31</v>
@@ -1883,7 +1883,7 @@
         <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:22</v>
@@ -1921,7 +1921,7 @@
         <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>5:49</v>
@@ -1959,7 +1959,7 @@
         <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>3:47</v>
@@ -1997,7 +1997,7 @@
         <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>2:20</v>
@@ -2035,7 +2035,7 @@
         <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>4:18</v>
@@ -2073,7 +2073,7 @@
         <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:39</v>
@@ -2111,7 +2111,7 @@
         <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:52</v>
@@ -2149,7 +2149,7 @@
         <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>4:01</v>
@@ -2301,7 +2301,7 @@
         <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:06</v>
@@ -2339,7 +2339,7 @@
         <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>2:43</v>
@@ -2719,7 +2719,7 @@
         <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:40</v>
@@ -2757,7 +2757,7 @@
         <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>2:49</v>
@@ -3745,7 +3745,7 @@
         <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>4:22</v>
@@ -3821,7 +3821,7 @@
         <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B91" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G91" t="str">
         <v>3:02</v>
@@ -3859,7 +3859,7 @@
         <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>3:12</v>
@@ -3897,7 +3897,7 @@
         <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:38</v>
@@ -3935,7 +3935,7 @@
         <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>4:40</v>
@@ -3973,7 +3973,7 @@
         <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G95" t="str">
         <v>2:57</v>
@@ -4011,7 +4011,7 @@
         <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B96" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>2:13</v>
@@ -4049,7 +4049,7 @@
         <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G97" t="str">
         <v>4:12</v>
@@ -4087,7 +4087,7 @@
         <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G98" t="str">
         <v>2:55</v>
@@ -4125,7 +4125,7 @@
         <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G99" t="str">
         <v>3:51</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:37</v>
@@ -477,7 +477,7 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:52</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:37</v>
@@ -477,7 +477,7 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:52</v>
@@ -819,7 +819,7 @@
         <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>4:30</v>
@@ -1579,7 +1579,7 @@
         <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:47</v>
@@ -2681,7 +2681,7 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>2:47</v>
@@ -3061,7 +3061,7 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>4:39</v>
@@ -3099,7 +3099,7 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>3:40</v>
@@ -3251,7 +3251,7 @@
         <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>5:52</v>
@@ -3669,7 +3669,7 @@
         <v>Jessie Ware - Ride</v>
       </c>
       <c r="B87" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G87" t="str">
         <v>4:37</v>
@@ -3707,7 +3707,7 @@
         <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B88" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G88" t="str">
         <v>3:16</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:37</v>
@@ -477,7 +477,7 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:52</v>
@@ -3593,7 +3593,7 @@
         <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B85" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>4:50</v>
@@ -3631,7 +3631,7 @@
         <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>3:14</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:37</v>
@@ -477,7 +477,7 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B3" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:52</v>
@@ -1541,7 +1541,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>5:12</v>
@@ -2643,7 +2643,7 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:28</v>
@@ -2795,7 +2795,7 @@
         <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>4:49</v>
@@ -3137,7 +3137,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B73" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>3:57</v>
@@ -3555,7 +3555,7 @@
         <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B84" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>3:20</v>
@@ -3783,7 +3783,7 @@
         <v>Suburban Requiem</v>
       </c>
       <c r="B90" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v>4:40</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:37</v>
@@ -477,7 +477,7 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B3" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:52</v>
@@ -629,7 +629,7 @@
         <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v>2:43</v>
@@ -1085,7 +1085,7 @@
         <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:11</v>
@@ -1503,7 +1503,7 @@
         <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>3:55</v>
@@ -2263,7 +2263,7 @@
         <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>4:50</v>
@@ -3023,7 +3023,7 @@
         <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>5:32</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:37</v>
@@ -477,7 +477,7 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:52</v>
@@ -1427,7 +1427,7 @@
         <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>4:05</v>
@@ -1465,7 +1465,7 @@
         <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>2:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:37</v>
@@ -477,7 +477,7 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:52</v>
@@ -591,7 +591,7 @@
         <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v>2:31</v>
@@ -2567,7 +2567,7 @@
         <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>2:22</v>
@@ -2605,7 +2605,7 @@
         <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:53</v>
@@ -2871,7 +2871,7 @@
         <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>2:59</v>
@@ -3213,7 +3213,7 @@
         <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>4:49</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,19 +439,19 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:37</v>
@@ -477,19 +477,19 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:52</v>
@@ -515,19 +515,19 @@
         <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:13</v>
@@ -553,19 +553,19 @@
         <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:19</v>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:10</v>
@@ -705,19 +705,19 @@
         <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v>3:55</v>
@@ -743,19 +743,19 @@
         <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:52</v>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -857,19 +857,19 @@
         <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B13" t="str">
-        <v>Streamed 3 days ago</v>
+        <v>Streamed 4 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Streamed 3 days ago</v>
+        <v>Streamed 4 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>27:54:45</v>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -933,19 +933,19 @@
         <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>7:20</v>
@@ -971,19 +971,19 @@
         <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:01</v>
@@ -1009,19 +1009,19 @@
         <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:31</v>
@@ -1047,19 +1047,19 @@
         <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:00</v>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:32</v>
@@ -1161,19 +1161,19 @@
         <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>5:03</v>
@@ -1199,19 +1199,19 @@
         <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>4:50</v>
@@ -1237,19 +1237,19 @@
         <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>4:53</v>
@@ -1275,19 +1275,19 @@
         <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>3:04</v>
@@ -1313,19 +1313,19 @@
         <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>4:32</v>
@@ -1351,19 +1351,19 @@
         <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>3:47</v>
@@ -1389,19 +1389,19 @@
         <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>3:40</v>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>4:03</v>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2377,19 +2377,19 @@
         <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>6:21</v>
@@ -2415,19 +2415,19 @@
         <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>2:46</v>
@@ -2453,19 +2453,19 @@
         <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>2:42</v>
@@ -2491,19 +2491,19 @@
         <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>3:04</v>
@@ -2529,19 +2529,19 @@
         <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>2:59</v>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>3:35</v>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>4:38</v>
@@ -2947,19 +2947,19 @@
         <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>3:46</v>
@@ -2985,19 +2985,19 @@
         <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>3:08</v>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>2:27</v>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>3:22</v>
@@ -3327,19 +3327,19 @@
         <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>4:08</v>
@@ -3365,19 +3365,19 @@
         <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>7:31</v>
@@ -3403,19 +3403,19 @@
         <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>3:21</v>
@@ -3441,19 +3441,19 @@
         <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>4:36</v>
@@ -3479,19 +3479,19 @@
         <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>5:06</v>
@@ -3517,19 +3517,19 @@
         <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B83" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>4:17</v>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4163,19 +4163,19 @@
         <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v>2:51</v>
@@ -4201,19 +4201,19 @@
         <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:24</v>
@@ -4236,40 +4236,40 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Medicine</v>
+        <v>bad bitch alert</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/medicine/1874168009</v>
+        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Medicine - Single</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G102" t="str">
-        <v>2:34</v>
+        <v>2:24</v>
       </c>
       <c r="H102" t="str">
-        <v>Channel Tres</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/medicine/1874168007</v>
+        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
       </c>
       <c r="L102" t="str">
-        <v>Medicine - Channel Tres</v>
+        <v>bad bitch alert - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="103">
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4654,40 +4654,40 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>SOMEWHERE ELSE</v>
+        <v>Medicine</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
+        <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>COME CLOSER</v>
+        <v>Medicine - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>4:11</v>
+        <v>2:34</v>
       </c>
       <c r="H113" t="str">
-        <v>TOMORA</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
+        <v>https://music.apple.com/us/album/medicine/1874168007</v>
       </c>
       <c r="L113" t="str">
-        <v>SOMEWHERE ELSE - TOMORA</v>
+        <v>Medicine - Channel Tres</v>
       </c>
     </row>
     <row r="114">
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4730,40 +4730,40 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Dog</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Torn</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G115" t="str">
-        <v>2:37</v>
+        <v>4:11</v>
       </c>
       <c r="H115" t="str">
-        <v>Cobrah</v>
+        <v>TOMORA</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L115" t="str">
-        <v>Dog - Cobrah</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="116">
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4806,3313 +4806,3351 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ALICE</v>
+        <v>Dog</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>Torn</v>
       </c>
       <c r="G117" t="str">
-        <v>4:39</v>
+        <v>2:37</v>
       </c>
       <c r="H117" t="str">
-        <v>Erin LeCount</v>
+        <v>Cobrah</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L117" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Tiny Light</v>
+        <v>ALICE</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Tiny Light - Single</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G118" t="str">
-        <v>3:27</v>
+        <v>4:39</v>
       </c>
       <c r="H118" t="str">
-        <v>SEVENTEEN</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L118" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:50</v>
+        <v>3:27</v>
       </c>
       <c r="H119" t="str">
-        <v>aespa</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L119" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H120" t="str">
-        <v>Concrete Boys</v>
+        <v>aespa</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L120" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>If I Leave</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G121" t="str">
-        <v>3:00</v>
+        <v>3:23</v>
       </c>
       <c r="H121" t="str">
-        <v>Mitski</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L121" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Time Will Tell</v>
+        <v>If I Leave</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G122" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H122" t="str">
-        <v>Lee Brice</v>
+        <v>Mitski</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L122" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>How I Get</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H123" t="str">
-        <v>Laufey</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L123" t="str">
-        <v>How I Get - Laufey</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>How I Get</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G124" t="str">
-        <v>3:19</v>
+        <v>3:39</v>
       </c>
       <c r="H124" t="str">
-        <v>Jessie Murph</v>
+        <v>Laufey</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L124" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Tonto</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Tonto - Single</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:20</v>
+        <v>3:19</v>
       </c>
       <c r="H125" t="str">
-        <v>J Balvin</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L125" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>Tonto</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:41</v>
+        <v>2:20</v>
       </c>
       <c r="H126" t="str">
-        <v>BLOND:ISH</v>
+        <v>J Balvin</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L126" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:50</v>
+        <v>2:41</v>
       </c>
       <c r="H127" t="str">
-        <v>Bautiii</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L127" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H128" t="str">
-        <v>Mýa</v>
+        <v>Bautiii</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L128" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>FENIAN</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:11</v>
+        <v>3:41</v>
       </c>
       <c r="H129" t="str">
-        <v>Kneecap</v>
+        <v>Mýa</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L129" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>What You Want</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>What You Want - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G130" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H130" t="str">
-        <v>Angèle</v>
+        <v>Kneecap</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L130" t="str">
-        <v>What You Want - Angèle</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>psychokiller</v>
+        <v>What You Want</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>getting up to no good</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>1:53</v>
+        <v>3:08</v>
       </c>
       <c r="H131" t="str">
-        <v>Artemas</v>
+        <v>Angèle</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L131" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>psychokiller</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>HADES</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G132" t="str">
-        <v>4:05</v>
+        <v>1:53</v>
       </c>
       <c r="H132" t="str">
-        <v>Melanie Martinez</v>
+        <v>Artemas</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L132" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>mariah</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>HADES</v>
       </c>
       <c r="G133" t="str">
-        <v>2:48</v>
+        <v>4:05</v>
       </c>
       <c r="H133" t="str">
-        <v>Lauv</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L133" t="str">
-        <v>mariah - Lauv</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>BLACKHOLE</v>
+        <v>mariah</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>REVIVE+</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G134" t="str">
-        <v>3:14</v>
+        <v>2:48</v>
       </c>
       <c r="H134" t="str">
-        <v>IVE</v>
+        <v>Lauv</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L134" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Walk</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Walk - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G135" t="str">
-        <v>2:56</v>
+        <v>3:14</v>
       </c>
       <c r="H135" t="str">
-        <v>Skye Newman</v>
+        <v>IVE</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L135" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>FLAMMABLE</v>
+        <v>Walk</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:17</v>
+        <v>2:56</v>
       </c>
       <c r="H136" t="str">
-        <v>Swae Lee</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L136" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3am (Remix)</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>3am (Remix) - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:44</v>
+        <v>3:17</v>
       </c>
       <c r="H137" t="str">
-        <v>Łaszewo</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L137" t="str">
-        <v>3am (Remix) - Łaszewo</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>mutual destruction</v>
+        <v>3am (Remix)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>mutual destruction - Single</v>
+        <v>3am (Remix) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:31</v>
+        <v>2:44</v>
       </c>
       <c r="H138" t="str">
-        <v>kenzie</v>
+        <v>Łaszewo</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
       </c>
       <c r="L138" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>3am (Remix) - Łaszewo</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Dear Worry</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Dear Worry - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H139" t="str">
-        <v>Common People</v>
+        <v>kenzie</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L139" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Gentleman</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Gentleman - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:16</v>
+        <v>3:01</v>
       </c>
       <c r="H140" t="str">
-        <v>Towa Bird</v>
+        <v>Common People</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L140" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>NYX00</v>
+        <v>Gentleman</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>NYX00 - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:00</v>
+        <v>2:16</v>
       </c>
       <c r="H141" t="str">
-        <v>Dei V</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L141" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Helicopters</v>
+        <v>NYX00</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>HELP(2)</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:58</v>
+        <v>3:00</v>
       </c>
       <c r="H142" t="str">
-        <v>Ezra Collective</v>
+        <v>Dei V</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L142" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Helicopters</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G143" t="str">
-        <v>4:58</v>
+        <v>3:58</v>
       </c>
       <c r="H143" t="str">
-        <v>Max Richter</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L143" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>It's You I Want</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G144" t="str">
-        <v>1:39</v>
+        <v>4:58</v>
       </c>
       <c r="H144" t="str">
-        <v>Kris Bowers</v>
+        <v>Max Richter</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L144" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>If I Was With You</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G145" t="str">
-        <v>3:25</v>
+        <v>1:39</v>
       </c>
       <c r="H145" t="str">
-        <v>Presley Regier</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L145" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Stay With Me</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H146" t="str">
-        <v>Nessa Barrett</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L146" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>My Loving</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>My Loving - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G147" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H147" t="str">
-        <v>Sonny Fodera</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L147" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Easy On The Eyes</v>
+        <v>My Loving</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:44</v>
+        <v>2:50</v>
       </c>
       <c r="H148" t="str">
-        <v>Willow Avalon</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L148" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Beautiful</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Let It Die Here</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:47</v>
+        <v>3:44</v>
       </c>
       <c r="H149" t="str">
-        <v>Linda Perry</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L149" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Beautiful</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G150" t="str">
-        <v>4:34</v>
+        <v>3:47</v>
       </c>
       <c r="H150" t="str">
-        <v>Jason Segel</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L150" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Control Freak</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Control Freak - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:53</v>
+        <v>4:34</v>
       </c>
       <c r="H151" t="str">
-        <v>Broadside</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L151" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Done For</v>
+        <v>Control Freak</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Done For - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:33</v>
+        <v>2:53</v>
       </c>
       <c r="H152" t="str">
-        <v>Max McNown</v>
+        <v>Broadside</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L152" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ready for the Ride</v>
+        <v>Done For</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H153" t="str">
-        <v>Sean Paul</v>
+        <v>Max McNown</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L153" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>push the pipe</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H154" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L154" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>push the pipe</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>With No Due Respect</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G155" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H155" t="str">
-        <v>Foggieraw</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L155" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Moonlight</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>McKenzie 2.0</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G156" t="str">
-        <v>2:00</v>
+        <v>3:13</v>
       </c>
       <c r="H156" t="str">
-        <v>FattMack</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L156" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Boat Named After You</v>
+        <v>Moonlight</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G157" t="str">
-        <v>3:56</v>
+        <v>2:00</v>
       </c>
       <c r="H157" t="str">
-        <v>ERNEST</v>
+        <v>FattMack</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L157" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>fall into you</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>fall into you - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H158" t="str">
-        <v>Camylio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L158" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Van Gogh</v>
+        <v>fall into you</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:25</v>
+        <v>3:28</v>
       </c>
       <c r="H159" t="str">
-        <v>Em Beihold</v>
+        <v>Camylio</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L159" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>popstar Nervous</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>the rumors are true - EP</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G160" t="str">
         <v>2:25</v>
       </c>
       <c r="H160" t="str">
-        <v>DC THE DON</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L160" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Free</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Free - Single</v>
+        <v>the rumors are true - EP</v>
       </c>
       <c r="G161" t="str">
-        <v>3:08</v>
+        <v>2:25</v>
       </c>
       <c r="H161" t="str">
-        <v>Beartooth</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L161" t="str">
-        <v>Free - Beartooth</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>never come never morning</v>
+        <v>Free</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>a short history of decay</v>
+        <v>Free - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:39</v>
+        <v>3:08</v>
       </c>
       <c r="H162" t="str">
-        <v>Nothing</v>
+        <v>Beartooth</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L162" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Over My Head</v>
+        <v>never come never morning</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G163" t="str">
-        <v>2:30</v>
+        <v>3:39</v>
       </c>
       <c r="H163" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Nothing</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L163" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Mantis</v>
+        <v>Over My Head</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Creature of Habit</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G164" t="str">
-        <v>4:40</v>
+        <v>2:30</v>
       </c>
       <c r="H164" t="str">
-        <v>Courtney Barnett</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L164" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Soft Launch</v>
+        <v>Mantis</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G165" t="str">
-        <v>2:25</v>
+        <v>4:40</v>
       </c>
       <c r="H165" t="str">
-        <v>Cely</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L165" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>picky choosy</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:53</v>
+        <v>2:25</v>
       </c>
       <c r="H166" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Cely</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L166" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>La Mala Era Yo</v>
+        <v>picky choosy</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G167" t="str">
-        <v>2:30</v>
+        <v>2:53</v>
       </c>
       <c r="H167" t="str">
-        <v>Kany García</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L167" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Quiet Part Loud</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Joy Next Door</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:08</v>
+        <v>2:30</v>
       </c>
       <c r="H168" t="str">
-        <v>The Maine</v>
+        <v>Kany García</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L168" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>favorite girl</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>favorite girl - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G169" t="str">
-        <v>3:24</v>
+        <v>3:08</v>
       </c>
       <c r="H169" t="str">
-        <v>Alaina Castillo</v>
+        <v>The Maine</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L169" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>The Blade</v>
+        <v>favorite girl</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>The Blade - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H170" t="str">
-        <v>Kingfishr</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L170" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Blunt Force Blues</v>
+        <v>The Blade</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Into Oblivion</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>4:11</v>
+        <v>3:15</v>
       </c>
       <c r="H171" t="str">
-        <v>Lamb of God</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L171" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>The Black Scorpion</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>The Great Satan</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G172" t="str">
-        <v>1:33</v>
+        <v>4:11</v>
       </c>
       <c r="H172" t="str">
-        <v>Rob Zombie</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L172" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>The Place</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G173" t="str">
-        <v>5:58</v>
+        <v>1:33</v>
       </c>
       <c r="H173" t="str">
-        <v>Sepultura</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L173" t="str">
-        <v>The Place - Sepultura</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>The Place</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>3:18</v>
+        <v>5:58</v>
       </c>
       <c r="H174" t="str">
-        <v>Wage War</v>
+        <v>Sepultura</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L174" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G175" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H175" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Wage War</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L175" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Tu Cárcel</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:36</v>
+        <v>2:26</v>
       </c>
       <c r="H176" t="str">
-        <v>Morat</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L176" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Facts</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Be Very Afraid (Vol. 1)</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H177" t="str">
-        <v>CHASE B</v>
+        <v>Morat</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L177" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>me &amp; you</v>
+        <v>Facts</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>big country</v>
+        <v>Be Very Afraid (Vol. 1)</v>
       </c>
       <c r="G178" t="str">
-        <v>2:29</v>
+        <v>3:29</v>
       </c>
       <c r="H178" t="str">
-        <v>sosocamo</v>
+        <v>CHASE B</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L178" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>badman</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>badman - Single</v>
+        <v>big country</v>
       </c>
       <c r="G179" t="str">
-        <v>2:54</v>
+        <v>2:29</v>
       </c>
       <c r="H179" t="str">
-        <v>nomi.</v>
+        <v>sosocamo</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L179" t="str">
-        <v>badman - nomi.</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Shut It Down</v>
+        <v>badman</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Shut It Down - Single</v>
+        <v>badman - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:26</v>
+        <v>2:54</v>
       </c>
       <c r="H180" t="str">
-        <v>TheARTI$t</v>
+        <v>nomi.</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L180" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>AUTOMATIC</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:08</v>
+        <v>2:26</v>
       </c>
       <c r="H181" t="str">
-        <v>Hulvey</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L181" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Leaving Egypt</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:17</v>
+        <v>2:08</v>
       </c>
       <c r="H182" t="str">
-        <v>Alex Jude</v>
+        <v>Hulvey</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L182" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Not Your Mother</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H183" t="str">
-        <v>gracie</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L183" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:50</v>
+        <v>3:03</v>
       </c>
       <c r="H184" t="str">
-        <v>Social Distortion</v>
+        <v>gracie</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L184" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>When the Love is Gone</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G185" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H185" t="str">
-        <v>Des Rocs</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L185" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Miami Crest</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Miami Crest - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:39</v>
+        <v>3:20</v>
       </c>
       <c r="H186" t="str">
-        <v>Namasenda</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L186" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Say No Prayer</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:29</v>
+        <v>2:39</v>
       </c>
       <c r="H187" t="str">
-        <v>oskar med k</v>
+        <v>Namasenda</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L187" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H188" t="str">
-        <v>eee gee</v>
+        <v>oskar med k</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L188" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Pink Tongue</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Porcelain Heart</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:43</v>
+        <v>3:09</v>
       </c>
       <c r="H189" t="str">
-        <v>Diane Emerita</v>
+        <v>eee gee</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L189" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G190" t="str">
-        <v>3:23</v>
+        <v>3:43</v>
       </c>
       <c r="H190" t="str">
-        <v>Ber</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L190" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:26</v>
+        <v>3:23</v>
       </c>
       <c r="H191" t="str">
-        <v>Forest Blakk</v>
+        <v>Ber</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L191" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Heartbeat</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Heartbeat - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:52</v>
+        <v>3:26</v>
       </c>
       <c r="H192" t="str">
-        <v>Lola Blue</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L192" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:16</v>
+        <v>2:52</v>
       </c>
       <c r="H193" t="str">
-        <v>doggone</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L193" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>I’m Every Woman</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>4:35</v>
+        <v>4:16</v>
       </c>
       <c r="H194" t="str">
-        <v>Ashley Jackson</v>
+        <v>doggone</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L194" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G195" t="str">
-        <v>2:46</v>
+        <v>4:35</v>
       </c>
       <c r="H195" t="str">
-        <v>Chris Morrissey</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L195" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Slow Tonight</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Full Circle</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G196" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H196" t="str">
-        <v>Tom Misch</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L196" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Freak No More</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Freak No More - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G197" t="str">
-        <v>3:57</v>
+        <v>3:12</v>
       </c>
       <c r="H197" t="str">
-        <v>AC Slater</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L197" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Don't Stop</v>
+        <v>Freak No More</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:55</v>
+        <v>3:57</v>
       </c>
       <c r="H198" t="str">
-        <v>HoneyLuv</v>
+        <v>AC Slater</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L198" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Cause I Do</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:39</v>
+        <v>2:55</v>
       </c>
       <c r="H199" t="str">
-        <v>Preston Pablo</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L199" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Morning Comes</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>4:11</v>
+        <v>2:39</v>
       </c>
       <c r="H200" t="str">
-        <v>Ty Myers</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L200" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>BETTER ON ME</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G201" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H201" t="str">
-        <v>Johnny Huynh</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L201" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Speed or Perish</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E202" t="str">
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Leather Temple</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>4:30</v>
+        <v>3:24</v>
       </c>
       <c r="H202" t="str">
-        <v>Carpenter Brut</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L202" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G203" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D203" t="str">
-        <v>2026-03-05</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
+      <c r="D204" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G203" t="str">
+      <c r="G204" t="str">
         <v>2:27</v>
       </c>
-      <c r="H203" t="str">
+      <c r="H204" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K203" t="str">
+      <c r="K204" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L203" t="str">
+      <c r="L204" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -781,7 +781,7 @@
         <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v>2:53</v>
@@ -895,7 +895,7 @@
         <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>5:18</v>
@@ -1617,7 +1617,7 @@
         <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:18</v>
@@ -1655,7 +1655,7 @@
         <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:50</v>
@@ -1693,7 +1693,7 @@
         <v>MyKey - Ride With Me</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>3:24</v>
@@ -1731,7 +1731,7 @@
         <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>2:36</v>
@@ -1769,7 +1769,7 @@
         <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v>3:34</v>
@@ -1807,7 +1807,7 @@
         <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v>4:03</v>
@@ -1845,7 +1845,7 @@
         <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>3:31</v>
@@ -1883,7 +1883,7 @@
         <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>3:22</v>
@@ -1921,7 +1921,7 @@
         <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>5:49</v>
@@ -1959,7 +1959,7 @@
         <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>3:47</v>
@@ -1997,7 +1997,7 @@
         <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>2:20</v>
@@ -2035,7 +2035,7 @@
         <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>4:18</v>
@@ -2073,7 +2073,7 @@
         <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:39</v>
@@ -2111,7 +2111,7 @@
         <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:52</v>
@@ -2149,7 +2149,7 @@
         <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>4:01</v>
@@ -2187,7 +2187,7 @@
         <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:54</v>
@@ -2301,7 +2301,7 @@
         <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:06</v>
@@ -2339,7 +2339,7 @@
         <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>2:43</v>
@@ -2719,7 +2719,7 @@
         <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:40</v>
@@ -2757,7 +2757,7 @@
         <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>2:49</v>
@@ -3745,7 +3745,7 @@
         <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v>4:22</v>
@@ -3821,7 +3821,7 @@
         <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B91" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v>3:02</v>
@@ -3859,7 +3859,7 @@
         <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v>3:12</v>
@@ -3897,7 +3897,7 @@
         <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:38</v>
@@ -3935,7 +3935,7 @@
         <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v>4:40</v>
@@ -3973,7 +3973,7 @@
         <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v>2:57</v>
@@ -4011,7 +4011,7 @@
         <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B96" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v>2:13</v>
@@ -4049,7 +4049,7 @@
         <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v>4:12</v>
@@ -4087,7 +4087,7 @@
         <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v>2:55</v>
@@ -4125,7 +4125,7 @@
         <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v>3:51</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>bad bitch alert</v>
+        <v>American Girls</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
+        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-06</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G102" t="str">
-        <v>2:24</v>
+        <v>3:33</v>
       </c>
       <c r="H102" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
+        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
       </c>
       <c r="L102" t="str">
-        <v>bad bitch alert - Ty Dolla $ign</v>
+        <v>American Girls - Harry Styles</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
+        <v>ALGO TÚ</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
+        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-06</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Mountain</v>
+        <v>ALGO TÚ - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>4:57</v>
+        <v>3:33</v>
       </c>
       <c r="H103" t="str">
-        <v>Gorillaz</v>
+        <v>Shakira</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
+        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
       </c>
       <c r="L103" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
+        <v>ALGO TÚ - Shakira</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>GO</v>
+        <v>New Religion</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/go/1870067581</v>
+        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-06</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>DEADLINE - EP</v>
+        <v>New Religion - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:15</v>
+        <v>2:54</v>
       </c>
       <c r="H104" t="str">
-        <v>BLACKPINK</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/go/1870067304</v>
+        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
       </c>
       <c r="L104" t="str">
-        <v>GO - BLACKPINK</v>
+        <v>New Religion - Bebe Rexha</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Risk It All</v>
+        <v>Where Do We Go</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
+        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-06</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Romantic</v>
+        <v>Where Do We Go - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:24</v>
+        <v>2:56</v>
       </c>
       <c r="H105" t="str">
-        <v>Bruno Mars</v>
+        <v>Ayra Starr</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
+        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
       </c>
       <c r="L105" t="str">
-        <v>Risk It All - Bruno Mars</v>
+        <v>Where Do We Go - Ayra Starr</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>FEVER DREAM</v>
+        <v>if you wanna party, come over to my house</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
+        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-06</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>FEVER DREAM - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G106" t="str">
-        <v>2:33</v>
+        <v>2:51</v>
       </c>
       <c r="H106" t="str">
-        <v>Alex Warren</v>
+        <v>Fcukers</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
+        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
       </c>
       <c r="L106" t="str">
-        <v>FEVER DREAM - Alex Warren</v>
+        <v>if you wanna party, come over to my house - Fcukers</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Nightingale Lane.</v>
+        <v>We Don’t Get Along</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
+        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-06</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>We Don’t Get Along - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>5:02</v>
+        <v>2:29</v>
       </c>
       <c r="H107" t="str">
-        <v>RAYE</v>
+        <v>Juice WRLD</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
+        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
       </c>
       <c r="L107" t="str">
-        <v>Nightingale Lane. - RAYE</v>
+        <v>We Don’t Get Along - Juice WRLD</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Made It On Our Own</v>
+        <v>bad bitch alert</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
+        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-06</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Made It On Our Own - Single</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G108" t="str">
-        <v>2:49</v>
+        <v>2:24</v>
       </c>
       <c r="H108" t="str">
-        <v>Yeat</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
+        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
       </c>
       <c r="L108" t="str">
-        <v>Made It On Our Own - Yeat</v>
+        <v>bad bitch alert - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ganga</v>
+        <v>Medicine</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/ganga/1879903219</v>
+        <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-06</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>DINASTÍA (DELUXE)</v>
+        <v>Medicine - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:45</v>
+        <v>2:34</v>
       </c>
       <c r="H109" t="str">
-        <v>Peso Pluma</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/ganga/1879902711</v>
+        <v>https://music.apple.com/us/album/medicine/1874168007</v>
       </c>
       <c r="L109" t="str">
-        <v>ganga - Peso Pluma</v>
+        <v>Medicine - Channel Tres</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WITH ME</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/with-me/1874015492</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-06</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G110" t="str">
-        <v>3:03</v>
+        <v>4:11</v>
       </c>
       <c r="H110" t="str">
-        <v>John Summit</v>
+        <v>TOMORA</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/with-me/1874015470</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L110" t="str">
-        <v>WITH ME - John Summit</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Sorry... I Meant Tonight (Bonus)</v>
+        <v>Dog</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-06</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Cloud 9</v>
+        <v>Torn</v>
       </c>
       <c r="G111" t="str">
-        <v>3:33</v>
+        <v>2:37</v>
       </c>
       <c r="H111" t="str">
-        <v>Megan Moroney</v>
+        <v>Cobrah</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L111" t="str">
-        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Miss That</v>
+        <v>Dance No More</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
+        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-06</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Miss That - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G112" t="str">
-        <v>2:56</v>
+        <v>3:14</v>
       </c>
       <c r="H112" t="str">
-        <v>Naomi Sharon</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
+        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
       </c>
       <c r="L112" t="str">
-        <v>Miss That - Naomi Sharon</v>
+        <v>Dance No More - Harry Styles</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Medicine</v>
+        <v>Burial (from Mother Mary)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/medicine/1874168009</v>
+        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-06</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Medicine - Single</v>
+        <v>Burial (from Mother Mary) - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>2:34</v>
+        <v>3:09</v>
       </c>
       <c r="H113" t="str">
-        <v>Channel Tres</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/medicine/1874168007</v>
+        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
       </c>
       <c r="L113" t="str">
-        <v>Medicine - Channel Tres</v>
+        <v>Burial (from Mother Mary) - Anne Hathaway</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>glass houses</v>
+        <v>Tweak</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
+        <v>https://music.apple.com/us/song/tweak/1875414202</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-06</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>ghosted - EP</v>
+        <v>Tweak - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:09</v>
+        <v>2:28</v>
       </c>
       <c r="H114" t="str">
-        <v>Saint Harison</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
+        <v>https://music.apple.com/us/album/tweak/1875414200</v>
       </c>
       <c r="L114" t="str">
-        <v>glass houses - Saint Harison</v>
+        <v>Tweak - GIRLSET</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>SOMEWHERE ELSE</v>
+        <v>ATTITUDE</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
+        <v>https://music.apple.com/us/song/attitude/1879665813</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-06</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>COME CLOSER</v>
+        <v>ATTITUDE - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>4:11</v>
+        <v>3:05</v>
       </c>
       <c r="H115" t="str">
-        <v>TOMORA</v>
+        <v>aespa</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
+        <v>https://music.apple.com/us/album/attitude/1879665810</v>
       </c>
       <c r="L115" t="str">
-        <v>SOMEWHERE ELSE - TOMORA</v>
+        <v>ATTITUDE - aespa</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>Blame Texas</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-06</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Blame Texas - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:39</v>
+        <v>3:12</v>
       </c>
       <c r="H116" t="str">
-        <v>Slayyyter</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
       </c>
       <c r="L116" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>Blame Texas - Cody Johnson</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Dog</v>
+        <v>Kerosene</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-06</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Torn</v>
+        <v>Kerosene - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:37</v>
+        <v>3:26</v>
       </c>
       <c r="H117" t="str">
-        <v>Cobrah</v>
+        <v>The Warning</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
       </c>
       <c r="L117" t="str">
-        <v>Dog - Cobrah</v>
+        <v>Kerosene - The Warning</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>ALICE</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-06</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>4:39</v>
+        <v>3:28</v>
       </c>
       <c r="H118" t="str">
-        <v>Erin LeCount</v>
+        <v>J Balvin</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
       </c>
       <c r="L118" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Tiny Light</v>
+        <v>Save Me Tonight</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-06</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Tiny Light - Single</v>
+        <v>Save Me Tonight - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:27</v>
+        <v>3:16</v>
       </c>
       <c r="H119" t="str">
-        <v>SEVENTEEN</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
       </c>
       <c r="L119" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>Save Me Tonight - Jennifer Lopez</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Universal Soldier</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-06</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G120" t="str">
-        <v>2:50</v>
+        <v>3:20</v>
       </c>
       <c r="H120" t="str">
-        <v>aespa</v>
+        <v>Depeche Mode</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
       </c>
       <c r="L120" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Universal Soldier - Depeche Mode</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Coming Up Roses</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-06</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G121" t="str">
-        <v>3:23</v>
+        <v>4:08</v>
       </c>
       <c r="H121" t="str">
-        <v>Concrete Boys</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
       </c>
       <c r="L121" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Coming Up Roses - Harry Styles</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>If I Leave</v>
+        <v>Light Over the Hill (from Reminders of Him)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-06</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>Light Over the Hill (from Reminders of Him) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:00</v>
+        <v>4:43</v>
       </c>
       <c r="H122" t="str">
-        <v>Mitski</v>
+        <v>Noah Cyrus</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
       </c>
       <c r="L122" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Time Will Tell</v>
+        <v>Feel Better</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-06</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
       </c>
       <c r="G123" t="str">
-        <v>3:04</v>
+        <v>3:46</v>
       </c>
       <c r="H123" t="str">
-        <v>Lee Brice</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
       </c>
       <c r="L123" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>Feel Better - Koe Wetzel</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>How I Get</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-06</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G124" t="str">
-        <v>3:39</v>
+        <v>4:02</v>
       </c>
       <c r="H124" t="str">
-        <v>Laufey</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
       </c>
       <c r="L124" t="str">
-        <v>How I Get - Laufey</v>
+        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>Pinterest (Portuguese)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-06</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>Pinterest (Portuguese) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:19</v>
+        <v>2:14</v>
       </c>
       <c r="H125" t="str">
-        <v>Jessie Murph</v>
+        <v>Anitta</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
       </c>
       <c r="L125" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>Pinterest (Portuguese) - Anitta</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Tonto</v>
+        <v>San Charly</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-06</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Tonto - Single</v>
+        <v>San Charly - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:20</v>
+        <v>2:54</v>
       </c>
       <c r="H126" t="str">
-        <v>J Balvin</v>
+        <v>Xavi</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
       </c>
       <c r="L126" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>San Charly - Xavi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>Timelapse de Sol</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-06</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>JuanesTeban</v>
       </c>
       <c r="G127" t="str">
-        <v>2:41</v>
+        <v>3:05</v>
       </c>
       <c r="H127" t="str">
-        <v>BLOND:ISH</v>
+        <v>Juanes</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
       </c>
       <c r="L127" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>Timelapse de Sol - Juanes</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>solo (KETTAMA remix)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-06</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>USB002 REMIXES</v>
       </c>
       <c r="G128" t="str">
-        <v>2:50</v>
+        <v>4:20</v>
       </c>
       <c r="H128" t="str">
-        <v>Bautiii</v>
+        <v>Fred again..</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
       </c>
       <c r="L128" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>solo (KETTAMA remix) - Fred again..</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>It’s Been Too Long</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-06</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>Long Long Road</v>
       </c>
       <c r="G129" t="str">
-        <v>3:41</v>
+        <v>2:42</v>
       </c>
       <c r="H129" t="str">
-        <v>Mýa</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
       </c>
       <c r="L129" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>It’s Been Too Long - Ringo Starr</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>Turn Your Heart Back On</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-06</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>FENIAN</v>
+        <v>Atlanta</v>
       </c>
       <c r="G130" t="str">
-        <v>3:11</v>
+        <v>3:07</v>
       </c>
       <c r="H130" t="str">
-        <v>Kneecap</v>
+        <v>Gnarls Barkley</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
       </c>
       <c r="L130" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>Turn Your Heart Back On - Gnarls Barkley</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>What You Want</v>
+        <v>Devil You Know</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-06</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>What You Want - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G131" t="str">
-        <v>3:08</v>
+        <v>3:10</v>
       </c>
       <c r="H131" t="str">
-        <v>Angèle</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
       </c>
       <c r="L131" t="str">
-        <v>What You Want - Angèle</v>
+        <v>Devil You Know - Maya Hawke</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>psychokiller</v>
+        <v>Earth, Wind &amp; California</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-06</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>getting up to no good</v>
+        <v>Jean</v>
       </c>
       <c r="G132" t="str">
-        <v>1:53</v>
+        <v>3:04</v>
       </c>
       <c r="H132" t="str">
-        <v>Artemas</v>
+        <v>Yebba</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
       </c>
       <c r="L132" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>Earth, Wind &amp; California - Yebba</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>400 Cities</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-06</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>HADES</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G133" t="str">
-        <v>4:05</v>
+        <v>2:17</v>
       </c>
       <c r="H133" t="str">
-        <v>Melanie Martinez</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
       </c>
       <c r="L133" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>400 Cities - Paul Russell</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>mariah</v>
+        <v>THE BOXER</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-06</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>THE BOXER - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:48</v>
+        <v>3:19</v>
       </c>
       <c r="H134" t="str">
-        <v>Lauv</v>
+        <v>Kids That Fly</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
       </c>
       <c r="L134" t="str">
-        <v>mariah - Lauv</v>
+        <v>THE BOXER - Kids That Fly</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>BLACKHOLE</v>
+        <v>Borrowed Time</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-06</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>REVIVE+</v>
+        <v>Borrowed Time - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:14</v>
+        <v>3:49</v>
       </c>
       <c r="H135" t="str">
-        <v>IVE</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
       </c>
       <c r="L135" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>Borrowed Time - Sam Barber</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Walk</v>
+        <v>BREEZER</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/breezer/1858041251</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-06</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Walk - Single</v>
+        <v>Lost on You</v>
       </c>
       <c r="G136" t="str">
-        <v>2:56</v>
+        <v>3:30</v>
       </c>
       <c r="H136" t="str">
-        <v>Skye Newman</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/breezer/1858041075</v>
       </c>
       <c r="L136" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>BREEZER - Tigers Jaw</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>FLAMMABLE</v>
+        <v>War To Love</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-06</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Tragic Magic</v>
       </c>
       <c r="G137" t="str">
-        <v>3:17</v>
+        <v>3:46</v>
       </c>
       <c r="H137" t="str">
-        <v>Swae Lee</v>
+        <v>Matt Corby</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
       </c>
       <c r="L137" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>War To Love - Matt Corby</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>3am (Remix)</v>
+        <v>Incompatibles</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
+        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-06</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>3am (Remix) - Single</v>
+        <v>Incompatibles - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:44</v>
+        <v>2:53</v>
       </c>
       <c r="H138" t="str">
-        <v>Łaszewo</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
+        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
       </c>
       <c r="L138" t="str">
-        <v>3am (Remix) - Łaszewo</v>
+        <v>Incompatibles - Christian Nodal</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>mutual destruction</v>
+        <v>Oídos Sordos</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-06</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>mutual destruction - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G139" t="str">
-        <v>2:31</v>
+        <v>3:34</v>
       </c>
       <c r="H139" t="str">
-        <v>kenzie</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
       </c>
       <c r="L139" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Dear Worry</v>
+        <v>Angel</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/angel/1877142613</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-06</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Dear Worry - Single</v>
+        <v>Angel - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:01</v>
+        <v>2:27</v>
       </c>
       <c r="H140" t="str">
-        <v>Common People</v>
+        <v>December 10</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/angel/1877142610</v>
       </c>
       <c r="L140" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>Angel - December 10</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Gentleman</v>
+        <v>Trust Myself</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-06</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Gentleman - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G141" t="str">
-        <v>2:16</v>
+        <v>3:03</v>
       </c>
       <c r="H141" t="str">
-        <v>Towa Bird</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
       </c>
       <c r="L141" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Trust Myself - Katelyn Tarver</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>NYX00</v>
+        <v>Tears Ago</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-06</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>NYX00 - Single</v>
+        <v>Tears Ago - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:00</v>
+        <v>2:35</v>
       </c>
       <c r="H142" t="str">
-        <v>Dei V</v>
+        <v>ili</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/ili/1474855634</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
       </c>
       <c r="L142" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Tears Ago - ili</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Helicopters</v>
+        <v>Bleed</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/bleed/1871562994</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-06</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>HELP(2)</v>
+        <v>House of Cards</v>
       </c>
       <c r="G143" t="str">
-        <v>3:58</v>
+        <v>3:40</v>
       </c>
       <c r="H143" t="str">
-        <v>Ezra Collective</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/bleed/1871562765</v>
       </c>
       <c r="L143" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>Bleed - The Amity Affliction</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Die for You</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-06</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>Reflections</v>
       </c>
       <c r="G144" t="str">
-        <v>4:58</v>
+        <v>3:27</v>
       </c>
       <c r="H144" t="str">
-        <v>Max Richter</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
       </c>
       <c r="L144" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Die for You - From Ashes to New</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>It's You I Want</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-06</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>1:39</v>
+        <v>3:35</v>
       </c>
       <c r="H145" t="str">
-        <v>Kris Bowers</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
       </c>
       <c r="L145" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>If I Was With You</v>
+        <v>Wish</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/wish/1876893995</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-06</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Wish - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:25</v>
+        <v>2:45</v>
       </c>
       <c r="H146" t="str">
-        <v>Presley Regier</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/wish/1876893993</v>
       </c>
       <c r="L146" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>Wish - Cash Cobain</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Stay With Me</v>
+        <v>Clean Up Song</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-06</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>Clean Up Song - EP</v>
       </c>
       <c r="G147" t="str">
-        <v>3:47</v>
+        <v>2:46</v>
       </c>
       <c r="H147" t="str">
-        <v>Nessa Barrett</v>
+        <v>Tessa Violet</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
       </c>
       <c r="L147" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>Clean Up Song - Tessa Violet</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>My Loving</v>
+        <v>Fantasy</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-06</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>My Loving - Single</v>
+        <v>Fantasy - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:50</v>
+        <v>3:42</v>
       </c>
       <c r="H148" t="str">
-        <v>Sonny Fodera</v>
+        <v>Omarion</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/omarion/15559682</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
       </c>
       <c r="L148" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Fantasy - Omarion</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Easy On The Eyes</v>
+        <v>why am i like this</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-06</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>why am i like this - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:44</v>
+        <v>2:56</v>
       </c>
       <c r="H149" t="str">
-        <v>Willow Avalon</v>
+        <v>bbno$</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
       </c>
       <c r="L149" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>why am i like this - bbno$</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Beautiful</v>
+        <v>How the Fire Started</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-06</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Let It Die Here</v>
+        <v>How the Fire Started - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:47</v>
+        <v>2:55</v>
       </c>
       <c r="H150" t="str">
-        <v>Linda Perry</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
       </c>
       <c r="L150" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>How the Fire Started - Eric Nam</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Take Off Late</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-06</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Mārara</v>
       </c>
       <c r="G151" t="str">
-        <v>4:34</v>
+        <v>3:23</v>
       </c>
       <c r="H151" t="str">
-        <v>Jason Segel</v>
+        <v>15 15</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
       </c>
       <c r="L151" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Take Off Late - 15 15</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Control Freak</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-06</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Control Freak - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G152" t="str">
-        <v>2:53</v>
+        <v>3:13</v>
       </c>
       <c r="H152" t="str">
-        <v>Broadside</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L152" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Done For</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-06</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Done For - Single</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G153" t="str">
-        <v>2:33</v>
+        <v>4:06</v>
       </c>
       <c r="H153" t="str">
-        <v>Max McNown</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
       </c>
       <c r="L153" t="str">
-        <v>Done For - Max McNown</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Ready for the Ride</v>
+        <v>Wonderful Thing</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-06</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Wonderful Thing - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:27</v>
+        <v>2:14</v>
       </c>
       <c r="H154" t="str">
-        <v>Sean Paul</v>
+        <v>aron!</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
       </c>
       <c r="L154" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Wonderful Thing - aron!</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>push the pipe</v>
+        <v>leaving is easy</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-06</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>leaving is easy - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:08</v>
+        <v>3:33</v>
       </c>
       <c r="H155" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>almost monday</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
       </c>
       <c r="L155" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>leaving is easy - almost monday</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>You and Me</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-06</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>With No Due Respect</v>
+        <v>You and Me - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:13</v>
+        <v>2:46</v>
       </c>
       <c r="H156" t="str">
-        <v>Foggieraw</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
       </c>
       <c r="L156" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>You and Me - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Moonlight</v>
+        <v>Tumbleweeds and Chewing Gum</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-06</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>McKenzie 2.0</v>
+        <v>Tumbleweeds and Chewing Gum - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:00</v>
+        <v>2:39</v>
       </c>
       <c r="H157" t="str">
-        <v>FattMack</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
       </c>
       <c r="L157" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Boat Named After You</v>
+        <v>Everything to Nothing</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-06</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>Everything to Nothing - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:56</v>
+        <v>3:31</v>
       </c>
       <c r="H158" t="str">
-        <v>ERNEST</v>
+        <v>Michael Sanzone</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
       </c>
       <c r="L158" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Everything to Nothing - Michael Sanzone</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>fall into you</v>
+        <v>DELETED</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/deleted/1880220796</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-06</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>fall into you - Single</v>
+        <v>DELETED - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:28</v>
+        <v>3:24</v>
       </c>
       <c r="H159" t="str">
-        <v>Camylio</v>
+        <v>vaultboy</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/deleted/1880220075</v>
       </c>
       <c r="L159" t="str">
-        <v>fall into you - Camylio</v>
+        <v>DELETED - vaultboy</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Van Gogh</v>
+        <v>A Thousand Years</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-06</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>A Thousand Years - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:25</v>
+        <v>3:00</v>
       </c>
       <c r="H160" t="str">
-        <v>Em Beihold</v>
+        <v>John Michael Howell</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
       </c>
       <c r="L160" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>A Thousand Years - John Michael Howell</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>popstar Nervous</v>
+        <v>Freedom (feat. EZI)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-06</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>the rumors are true - EP</v>
+        <v>Freedom (feat. EZI) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:25</v>
+        <v>5:29</v>
       </c>
       <c r="H161" t="str">
-        <v>DC THE DON</v>
+        <v>Kaskade</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
       </c>
       <c r="L161" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Freedom (feat. EZI) - Kaskade</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Free</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-06</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Free - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G162" t="str">
-        <v>3:08</v>
+        <v>3:16</v>
       </c>
       <c r="H162" t="str">
-        <v>Beartooth</v>
+        <v>MORGXN</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
       </c>
       <c r="L162" t="str">
-        <v>Free - Beartooth</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>never come never morning</v>
+        <v>To Myself</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-06</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>a short history of decay</v>
+        <v>MINDFIELDS</v>
       </c>
       <c r="G163" t="str">
-        <v>3:39</v>
+        <v>3:40</v>
       </c>
       <c r="H163" t="str">
-        <v>Nothing</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
       </c>
       <c r="L163" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>To Myself - Alicia Creti</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Over My Head</v>
+        <v>TABOO</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/taboo/1880750236</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-06</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>TABOO - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:30</v>
+        <v>2:45</v>
       </c>
       <c r="H164" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/taboo/1880750235</v>
       </c>
       <c r="L164" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>TABOO - Isaiah Falls</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Mantis</v>
+        <v>Under The Table (feat. Chris Lane)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-06</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Creature of Habit</v>
+        <v>Under The Table (feat. Chris Lane) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:40</v>
+        <v>2:52</v>
       </c>
       <c r="H165" t="str">
-        <v>Courtney Barnett</v>
+        <v>Two Friends</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
       </c>
       <c r="L165" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Soft Launch</v>
+        <v>Be Mine</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-06</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Be Mine - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:25</v>
+        <v>1:53</v>
       </c>
       <c r="H166" t="str">
-        <v>Cely</v>
+        <v>James Hype</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
       </c>
       <c r="L166" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Be Mine - James Hype</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>picky choosy</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-06</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:53</v>
+        <v>3:11</v>
       </c>
       <c r="H167" t="str">
-        <v>Chelsea Jordan</v>
+        <v>ANOTR</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
       </c>
       <c r="L167" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>La Mala Era Yo</v>
+        <v>Evil Against Me</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-06</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>Evil Against Me - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:30</v>
+        <v>3:24</v>
       </c>
       <c r="H168" t="str">
-        <v>Kany García</v>
+        <v>Shaya Zamora</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
       </c>
       <c r="L168" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>Evil Against Me - Shaya Zamora</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Quiet Part Loud</v>
+        <v>Still Do</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/still-do/1877250216</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-06</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Joy Next Door</v>
+        <v>Still Do - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:08</v>
+        <v>3:03</v>
       </c>
       <c r="H169" t="str">
-        <v>The Maine</v>
+        <v>Anne Wilson</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/still-do/1877250210</v>
       </c>
       <c r="L169" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>Still Do - Anne Wilson</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>favorite girl</v>
+        <v>DIE 4 ME</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-06</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>favorite girl - Single</v>
+        <v>DIE 4 ME - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:24</v>
+        <v>2:37</v>
       </c>
       <c r="H170" t="str">
-        <v>Alaina Castillo</v>
+        <v>Taylor Hill</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
       </c>
       <c r="L170" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>DIE 4 ME - Taylor Hill</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>The Blade</v>
+        <v>Havin'</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/havin/1878165152</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-06</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>The Blade - Single</v>
+        <v>Havin' - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:15</v>
+        <v>2:49</v>
       </c>
       <c r="H171" t="str">
-        <v>Kingfishr</v>
+        <v>1K Phew</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/havin/1878165149</v>
       </c>
       <c r="L171" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>Havin' - 1K Phew</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Blunt Force Blues</v>
+        <v>Se Me Va A Pasar</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-06</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Into Oblivion</v>
+        <v>Coleccionando Corazones</v>
       </c>
       <c r="G172" t="str">
-        <v>4:11</v>
+        <v>3:16</v>
       </c>
       <c r="H172" t="str">
-        <v>Lamb of God</v>
+        <v>Carolina Ross</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
       </c>
       <c r="L172" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>Se Me Va A Pasar - Carolina Ross</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>The Black Scorpion</v>
+        <v>Mi Amante</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-06</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>The Great Satan</v>
+        <v>Mi Amante - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>1:33</v>
+        <v>3:16</v>
       </c>
       <c r="H173" t="str">
-        <v>Rob Zombie</v>
+        <v>Juanchito</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
       </c>
       <c r="L173" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Mi Amante - Juanchito</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>The Place</v>
+        <v>Ay Pequeña</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-06</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>La Rubia Enamorada - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>5:58</v>
+        <v>2:00</v>
       </c>
       <c r="H174" t="str">
-        <v>Sepultura</v>
+        <v>Flavia Laos</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
       </c>
       <c r="L174" t="str">
-        <v>The Place - Sepultura</v>
+        <v>Ay Pequeña - Flavia Laos</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>Need it Bad</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-06</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>Need it Bad - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:18</v>
+        <v>3:07</v>
       </c>
       <c r="H175" t="str">
-        <v>Wage War</v>
+        <v>Ama</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
       </c>
       <c r="L175" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>Need it Bad - Ama</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>Time Is A Bomb</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-06</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G176" t="str">
-        <v>2:26</v>
+        <v>4:24</v>
       </c>
       <c r="H176" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Metric</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
       </c>
       <c r="L176" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>Time Is A Bomb - Metric</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Tu Cárcel</v>
+        <v>NOISE</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/noise/1878401282</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-06</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>NOISE - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:36</v>
+        <v>2:42</v>
       </c>
       <c r="H177" t="str">
-        <v>Morat</v>
+        <v>ivri</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/noise/1878401279</v>
       </c>
       <c r="L177" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>NOISE - ivri</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Facts</v>
+        <v>Delicate (feat. Jake Clemons)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-06</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Be Very Afraid (Vol. 1)</v>
+        <v>Prairie</v>
       </c>
       <c r="G178" t="str">
-        <v>3:29</v>
+        <v>4:46</v>
       </c>
       <c r="H178" t="str">
-        <v>CHASE B</v>
+        <v>Bike Routes</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
       </c>
       <c r="L178" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>me &amp; you</v>
+        <v>Bird Eye View</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-06</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>big country</v>
+        <v>Bird Eye View - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:29</v>
+        <v>4:24</v>
       </c>
       <c r="H179" t="str">
-        <v>sosocamo</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
       </c>
       <c r="L179" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Bird Eye View - Hayden Everett</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>badman</v>
+        <v>Whip-Poor-Will</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-06</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>badman - Single</v>
+        <v>Whip-Poor-Will - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:54</v>
+        <v>3:46</v>
       </c>
       <c r="H180" t="str">
-        <v>nomi.</v>
+        <v>Erin Rae</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
       </c>
       <c r="L180" t="str">
-        <v>badman - nomi.</v>
+        <v>Whip-Poor-Will - Erin Rae</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Shut It Down</v>
+        <v>Good Friend</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-06</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Shut It Down - Single</v>
+        <v>Singing</v>
       </c>
       <c r="G181" t="str">
-        <v>2:26</v>
+        <v>3:39</v>
       </c>
       <c r="H181" t="str">
-        <v>TheARTI$t</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
       </c>
       <c r="L181" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>Good Friend - Gia Margaret</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>AUTOMATIC</v>
+        <v>NEVER BE THE SAME</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-06</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>NEVER BE THE SAME - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:08</v>
+        <v>2:52</v>
       </c>
       <c r="H182" t="str">
-        <v>Hulvey</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
       </c>
       <c r="L182" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>NEVER BE THE SAME - THEHONESTGUY</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Leaving Egypt</v>
+        <v>Tellme</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/tellme/1880089949</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-06</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>Tellme - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:17</v>
+        <v>3:04</v>
       </c>
       <c r="H183" t="str">
-        <v>Alex Jude</v>
+        <v>Joon</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/joon/1515228137</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/tellme/1880089948</v>
       </c>
       <c r="L183" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>Tellme - Joon</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Not Your Mother</v>
+        <v>I Can Be Yours</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-06</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>I Can Be Yours - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:03</v>
+        <v>4:07</v>
       </c>
       <c r="H184" t="str">
-        <v>gracie</v>
+        <v>zzzahara</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
       </c>
       <c r="L184" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>I Can Be Yours - zzzahara</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Born to Kill</v>
+        <v>Soren</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/soren/1876596568</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-06</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Born to Kill</v>
+        <v>Soren - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:50</v>
+        <v>3:41</v>
       </c>
       <c r="H185" t="str">
-        <v>Social Distortion</v>
+        <v>Orca</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/soren/1876596567</v>
       </c>
       <c r="L185" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Soren - Orca</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>When the Love is Gone</v>
+        <v>Gloria</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/gloria/1842363092</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-06</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>The Guesthouse</v>
       </c>
       <c r="G186" t="str">
-        <v>3:20</v>
+        <v>3:24</v>
       </c>
       <c r="H186" t="str">
-        <v>Des Rocs</v>
+        <v>Shai Maestro</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/gloria/1842362686</v>
       </c>
       <c r="L186" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Gloria - Shai Maestro</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Miami Crest</v>
+        <v>Gemini Eyes</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-06</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Miami Crest - Single</v>
+        <v>A Rush To Nowhere</v>
       </c>
       <c r="G187" t="str">
-        <v>2:39</v>
+        <v>4:59</v>
       </c>
       <c r="H187" t="str">
-        <v>Namasenda</v>
+        <v>Arima Ederra</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
       </c>
       <c r="L187" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>Gemini Eyes - Arima Ederra</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Say No Prayer</v>
+        <v>Tough</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/tough/1878716666</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-06</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Tough - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:29</v>
+        <v>3:15</v>
       </c>
       <c r="H188" t="str">
-        <v>oskar med k</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/tough/1878716664</v>
       </c>
       <c r="L188" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Tough - Nia Smith</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>NO HOOK</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-06</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>NO HOOK - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:09</v>
+        <v>1:08</v>
       </c>
       <c r="H189" t="str">
-        <v>eee gee</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
       </c>
       <c r="L189" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>NO HOOK - KARRAHBOOO</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Pink Tongue</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-06</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Porcelain Heart</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:43</v>
+        <v>4:08</v>
       </c>
       <c r="H190" t="str">
-        <v>Diane Emerita</v>
+        <v>Rosie Bennet</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
       </c>
       <c r="L190" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Mean 2 Me</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-06</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Mean 2 Me - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:23</v>
+        <v>4:27</v>
       </c>
       <c r="H191" t="str">
-        <v>Ber</v>
+        <v>Skyla Tylaa</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
       </c>
       <c r="L191" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Mean 2 Me - Skyla Tylaa</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>CAPTAIN KERNEL</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-06</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>BIG MAMA</v>
       </c>
       <c r="G192" t="str">
-        <v>3:26</v>
+        <v>3:04</v>
       </c>
       <c r="H192" t="str">
-        <v>Forest Blakk</v>
+        <v>Flying Lotus</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
       </c>
       <c r="L192" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>CAPTAIN KERNEL - Flying Lotus</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Heartbeat</v>
+        <v>Nothings What It Seems</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-06</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Heartbeat - Single</v>
+        <v>Midwest Memoir</v>
       </c>
       <c r="G193" t="str">
-        <v>2:52</v>
+        <v>3:12</v>
       </c>
       <c r="H193" t="str">
-        <v>Lola Blue</v>
+        <v>Tyler Nance</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
       </c>
       <c r="L193" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>Nothings What It Seems - Tyler Nance</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>No Need For Leavin'</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-06</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>No Need For Leavin' - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>4:16</v>
+        <v>3:35</v>
       </c>
       <c r="H194" t="str">
-        <v>doggone</v>
+        <v>Kameron Marlowe</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
       </c>
       <c r="L194" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>No Need For Leavin' - Kameron Marlowe</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>I’m Every Woman</v>
+        <v>ii. in the gut of the wolf</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-06</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Cover Girl - EP</v>
+        <v>silence outlives the earth</v>
       </c>
       <c r="G195" t="str">
-        <v>4:35</v>
+        <v>3:30</v>
       </c>
       <c r="H195" t="str">
-        <v>Ashley Jackson</v>
+        <v>ERRA</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/erra/408917738</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
       </c>
       <c r="L195" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>ii. in the gut of the wolf - ERRA</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>Poison Icon</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-06</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>The Crawl</v>
       </c>
       <c r="G196" t="str">
-        <v>2:46</v>
+        <v>5:12</v>
       </c>
       <c r="H196" t="str">
-        <v>Chris Morrissey</v>
+        <v>Temple of Void</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
       </c>
       <c r="L196" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>Poison Icon - Temple of Void</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Slow Tonight</v>
+        <v>Lay Down Your Soul</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-06</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Full Circle</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G197" t="str">
-        <v>3:12</v>
+        <v>3:13</v>
       </c>
       <c r="H197" t="str">
-        <v>Tom Misch</v>
+        <v>Venom</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
       </c>
       <c r="L197" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Lay Down Your Soul - Venom</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Freak No More</v>
+        <v>Ghost Notes</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-06</v>
@@ -7899,258 +7899,30 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Freak No More - Single</v>
+        <v>Slave Machine</v>
       </c>
       <c r="G198" t="str">
-        <v>3:57</v>
+        <v>4:27</v>
       </c>
       <c r="H198" t="str">
-        <v>AC Slater</v>
+        <v>Nervosa</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/nervosa/511556134</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/ghost-notes/1862228924</v>
       </c>
       <c r="L198" t="str">
-        <v>Freak No More - AC Slater</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Don't Stop</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Don't Stop - Single</v>
-      </c>
-      <c r="G199" t="str">
-        <v>2:55</v>
-      </c>
-      <c r="H199" t="str">
-        <v>HoneyLuv</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
-      </c>
-      <c r="L199" t="str">
-        <v>Don't Stop - HoneyLuv</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Cause I Do</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Cause I Do - Single</v>
-      </c>
-      <c r="G200" t="str">
-        <v>2:39</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Preston Pablo</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
-      </c>
-      <c r="L200" t="str">
-        <v>Cause I Do - Preston Pablo</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Morning Comes</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Heavy On The Soul</v>
-      </c>
-      <c r="G201" t="str">
-        <v>4:11</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Ty Myers</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
-      </c>
-      <c r="L201" t="str">
-        <v>Morning Comes - Ty Myers</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>BETTER ON ME</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>BETTER ON ME - Single</v>
-      </c>
-      <c r="G202" t="str">
-        <v>3:24</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Johnny Huynh</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
-      </c>
-      <c r="L202" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Speed or Perish</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Leather Temple</v>
-      </c>
-      <c r="G203" t="str">
-        <v>4:30</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Carpenter Brut</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
-      </c>
-      <c r="L203" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>The Scumbag Grift</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Cheap Heat</v>
-      </c>
-      <c r="G204" t="str">
-        <v>2:27</v>
-      </c>
-      <c r="H204" t="str">
-        <v>A Wilhelm Scream</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
-      </c>
-      <c r="L204" t="str">
-        <v>The Scumbag Grift - A Wilhelm Scream</v>
+        <v>Ghost Notes - Nervosa</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -436,28 +436,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jessie Ware - Ride (Official Video)</v>
+        <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
+        <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>4:37</v>
+        <v>3:48</v>
       </c>
       <c r="H2" t="str">
-        <v>Jessie Ware</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,33 +469,33 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
+        <v>Harry Styles - American Girls (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Cannons - These Nights (Live at The Fonda)</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
+        <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>4:52</v>
+        <v>4:58</v>
       </c>
       <c r="H3" t="str">
-        <v>Cannons</v>
+        <v>Warner Records</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,33 +507,33 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
+        <v>Morrissey - The Monsters of Pig Alley (Official Music Video) - Warner Records</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
+        <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
+        <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:13</v>
+        <v>2:33</v>
       </c>
       <c r="H4" t="str">
-        <v>Kim Petras</v>
+        <v>Ellise</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,33 +545,33 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
+        <v>Ellise - Littlepill (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
+        <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:19</v>
+        <v>5:01</v>
       </c>
       <c r="H5" t="str">
-        <v>Vanessa Carlton</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,33 +583,33 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
+        <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer]</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
+        <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>2:31</v>
+        <v>4:56</v>
       </c>
       <c r="H6" t="str">
-        <v>Kiana Ledé</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,33 +621,33 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
+        <v>OneRepublic - Counting Stars | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
+        <v>https://www.youtube.com/watch?v=366CV87TguE</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:43</v>
+        <v>2:54</v>
       </c>
       <c r="H7" t="str">
-        <v>Ringo Starr</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,33 +659,33 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
+        <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio)</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
+        <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:10</v>
+        <v>2:46</v>
       </c>
       <c r="H8" t="str">
-        <v>Maya Hawke</v>
+        <v>NathanEvanss</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,33 +697,33 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
+        <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video) - NathanEvanss</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
+        <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:55</v>
+        <v>2:56</v>
       </c>
       <c r="H9" t="str">
-        <v>Armin van Buuren</v>
+        <v>R3HAB</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,33 +735,33 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>R3HAB x RHODES - Right here... (Official Lyric Video) - R3HAB</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Demi Lovato - Really Don't Care (Live)</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
+        <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:52</v>
+        <v>3:21</v>
       </c>
       <c r="H10" t="str">
-        <v>Demi Lovato</v>
+        <v>War Child UK and Depeche Mode</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,33 +773,33 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
+        <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2) - War Child UK and Depeche Mode</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
+        <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G11" t="str">
-        <v>2:53</v>
+        <v>3:16</v>
       </c>
       <c r="H11" t="str">
-        <v>Peter Gabriel</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:30</v>
+        <v>2:41</v>
       </c>
       <c r="H12" t="str">
-        <v>Jessie J</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Johnny Orlando - Have Your Lovin' (Official Audio) - Johnny Orlando</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>Streamed 4 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Streamed 4 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G13" t="str">
-        <v>27:54:45</v>
+        <v>2:29</v>
       </c>
       <c r="H13" t="str">
-        <v>BRITs</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Russell Dickerson - B.O.A.T. (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G14" t="str">
-        <v>5:18</v>
+        <v>2:43</v>
       </c>
       <c r="H14" t="str">
-        <v>Harry Styles</v>
+        <v>OneRepublic and Nova's Red Room</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,33 +925,33 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room - OneRepublic and Nova's Red Room</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G15" t="str">
-        <v>7:20</v>
+        <v>3:46</v>
       </c>
       <c r="H15" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Matt Hansen - SAME TIME (Official Live Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:01</v>
+        <v>4:01</v>
       </c>
       <c r="H16" t="str">
-        <v>BRITs</v>
+        <v>Mike Posner</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,33 +1001,33 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video) - Mike Posner</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:31</v>
+        <v>3:23</v>
       </c>
       <c r="H17" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Katelyn Tarver - Trust Myself (Live Performance Video) - Katelyn Tarver</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:00</v>
+        <v>3:39</v>
       </c>
       <c r="H18" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>almost monday</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>almost monday - leaving is easy (official video) - almost monday</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:11</v>
+        <v>3:04</v>
       </c>
       <c r="H19" t="str">
-        <v>The Kiffness</v>
+        <v>Anne Wilson and Cole Swindell</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video) - Anne Wilson and Cole Swindell</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:32</v>
+        <v>3:25</v>
       </c>
       <c r="H20" t="str">
-        <v>Lauv</v>
+        <v>vaultboy</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>vaultboy - DELETED (Official Lyric Video) - vaultboy</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:03</v>
+        <v>3:49</v>
       </c>
       <c r="H21" t="str">
-        <v>RAYE</v>
+        <v>The Warning</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,33 +1191,33 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>The Warning - Kerosene (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:50</v>
+        <v>2:14</v>
       </c>
       <c r="H22" t="str">
-        <v>Armik</v>
+        <v>aron!</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,33 +1229,33 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>aron! - Wonderful Thing (City View Video) - aron!</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:53</v>
+        <v>2:43</v>
       </c>
       <c r="H23" t="str">
-        <v>Scorpions</v>
+        <v>Bazzi</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,33 +1267,33 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Bazzi - moment (Official Music Video) - Bazzi</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:04</v>
+        <v>4:43</v>
       </c>
       <c r="H24" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Sting</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,33 +1305,33 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Sting - Shape of My Heart (Live at the Rijksmuseum) - Sting</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:32</v>
+        <v>2:44</v>
       </c>
       <c r="H25" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Dean Lewis - Enjoy It While It Lasts (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:47</v>
+        <v>4:37</v>
       </c>
       <c r="H26" t="str">
-        <v>Girl Tones</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,33 +1381,33 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Jessie Ware - Ride (Official Video) - Jessie Ware</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:40</v>
+        <v>4:52</v>
       </c>
       <c r="H27" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Cannons</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Cannons - These Nights (Live at The Fonda) - Cannons</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:05</v>
+        <v>2:13</v>
       </c>
       <c r="H28" t="str">
-        <v>HAUSER</v>
+        <v>Kim Petras</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour] - Kim Petras</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:59</v>
+        <v>3:19</v>
       </c>
       <c r="H29" t="str">
-        <v>Queen Official</v>
+        <v>Vanessa Carlton</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Vanessa Carlton - "Great House" [Official Music Video] - Vanessa Carlton</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:55</v>
+        <v>2:31</v>
       </c>
       <c r="H30" t="str">
-        <v>Tenille Townes</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Kiana Ledé - Jury [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:12</v>
+        <v>2:43</v>
       </c>
       <c r="H31" t="str">
-        <v>Self Esteem</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Ringo Starr - It’s Been Too Long (Visualizer) - Ringo Starr</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Maya Hawke - Devil You Know (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=UOq9hJG4-m0</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:47</v>
+        <v>3:10</v>
       </c>
       <c r="H32" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Maya Hawke - Devil You Know (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:18</v>
+        <v>3:55</v>
       </c>
       <c r="H33" t="str">
-        <v>Em Beihold</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:50</v>
+        <v>3:52</v>
       </c>
       <c r="H34" t="str">
-        <v>Michael Bublé</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Demi Lovato - Really Don't Care (Live) - Demi Lovato</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:24</v>
+        <v>2:53</v>
       </c>
       <c r="H35" t="str">
-        <v>MyKey</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:36</v>
+        <v>4:30</v>
       </c>
       <c r="H36" t="str">
-        <v>Max McNown</v>
+        <v>Jessie J</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>Streamed 5 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>Streamed 5 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:34</v>
+        <v>27:54:45</v>
       </c>
       <c r="H37" t="str">
-        <v>Megan Moroney</v>
+        <v>BRITs</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:03</v>
+        <v>5:18</v>
       </c>
       <c r="H38" t="str">
-        <v>ERNEST</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:31</v>
+        <v>7:20</v>
       </c>
       <c r="H39" t="str">
-        <v>Bruno Mars</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:22</v>
+        <v>3:01</v>
       </c>
       <c r="H40" t="str">
-        <v>BLACKPINK</v>
+        <v>BRITs</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:49</v>
+        <v>3:31</v>
       </c>
       <c r="H41" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:47</v>
+        <v>3:00</v>
       </c>
       <c r="H42" t="str">
-        <v>Nessa Barrett</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:20</v>
+        <v>3:11</v>
       </c>
       <c r="H43" t="str">
-        <v>Towa Bird</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,21 +2027,21 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2050,10 +2050,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:18</v>
+        <v>3:32</v>
       </c>
       <c r="H44" t="str">
-        <v>Ty Myers</v>
+        <v>Lauv</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,21 +2065,21 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B45" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2088,10 +2088,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:39</v>
+        <v>5:03</v>
       </c>
       <c r="H45" t="str">
-        <v>kenzie</v>
+        <v>RAYE</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,21 +2103,21 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B46" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2126,10 +2126,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:52</v>
+        <v>4:50</v>
       </c>
       <c r="H46" t="str">
-        <v>Leanna Crawford</v>
+        <v>Armik</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,21 +2141,21 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B47" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2164,10 +2164,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:01</v>
+        <v>4:53</v>
       </c>
       <c r="H47" t="str">
-        <v>Bryan Adams</v>
+        <v>Scorpions</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,21 +2179,21 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B48" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2202,10 +2202,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:54</v>
+        <v>3:04</v>
       </c>
       <c r="H48" t="str">
-        <v>CHESCA</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,21 +2217,21 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B49" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2240,10 +2240,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:03</v>
+        <v>4:32</v>
       </c>
       <c r="H49" t="str">
-        <v>Dermot Kennedy</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,21 +2255,21 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2278,10 +2278,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:50</v>
+        <v>3:47</v>
       </c>
       <c r="H50" t="str">
-        <v>earMUSIC</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:06</v>
+        <v>3:40</v>
       </c>
       <c r="H51" t="str">
-        <v>Y2K</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:43</v>
+        <v>4:05</v>
       </c>
       <c r="H52" t="str">
-        <v>Lainey Wilson</v>
+        <v>HAUSER</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>6:21</v>
+        <v>2:59</v>
       </c>
       <c r="H53" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Queen Official</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:46</v>
+        <v>3:55</v>
       </c>
       <c r="H54" t="str">
-        <v>Bryan Ferry</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:42</v>
+        <v>5:12</v>
       </c>
       <c r="H55" t="str">
-        <v>Saint Harison</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:04</v>
+        <v>3:47</v>
       </c>
       <c r="H56" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:59</v>
+        <v>3:18</v>
       </c>
       <c r="H57" t="str">
-        <v>Catie Turner</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:22</v>
+        <v>3:50</v>
       </c>
       <c r="H58" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:53</v>
+        <v>3:24</v>
       </c>
       <c r="H59" t="str">
-        <v>Roxette</v>
+        <v>MyKey</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:28</v>
+        <v>2:36</v>
       </c>
       <c r="H60" t="str">
-        <v>Marcin</v>
+        <v>Max McNown</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:47</v>
+        <v>3:34</v>
       </c>
       <c r="H61" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:40</v>
+        <v>4:03</v>
       </c>
       <c r="H62" t="str">
-        <v>Laufey</v>
+        <v>ERNEST</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B63" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:49</v>
+        <v>3:31</v>
       </c>
       <c r="H63" t="str">
-        <v>Ava Max</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B64" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:49</v>
+        <v>3:22</v>
       </c>
       <c r="H64" t="str">
-        <v>U2</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:35</v>
+        <v>5:49</v>
       </c>
       <c r="H65" t="str">
-        <v>Taylor Swift</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:59</v>
+        <v>3:47</v>
       </c>
       <c r="H66" t="str">
-        <v>Kiana Ledé</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:38</v>
+        <v>2:20</v>
       </c>
       <c r="H67" t="str">
-        <v>Jessie Ware</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:46</v>
+        <v>4:18</v>
       </c>
       <c r="H68" t="str">
-        <v>Madison Beer</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:08</v>
+        <v>2:39</v>
       </c>
       <c r="H69" t="str">
-        <v>Sean Stemaly</v>
+        <v>kenzie</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>5:32</v>
+        <v>3:52</v>
       </c>
       <c r="H70" t="str">
-        <v>earMUSIC</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:39</v>
+        <v>4:01</v>
       </c>
       <c r="H71" t="str">
-        <v>georgemichael</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:40</v>
+        <v>2:54</v>
       </c>
       <c r="H72" t="str">
-        <v>Nothing But Thieves</v>
+        <v>CHESCA</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B73" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:57</v>
+        <v>4:03</v>
       </c>
       <c r="H73" t="str">
-        <v>Self Esteem</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B74" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:27</v>
+        <v>4:50</v>
       </c>
       <c r="H74" t="str">
-        <v>070 Shake</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:49</v>
+        <v>3:06</v>
       </c>
       <c r="H75" t="str">
-        <v>georgemichael</v>
+        <v>Y2K</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>5:52</v>
+        <v>2:43</v>
       </c>
       <c r="H76" t="str">
-        <v>georgemichael</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B77" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:22</v>
+        <v>6:21</v>
       </c>
       <c r="H77" t="str">
-        <v>Foo Fighters</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B78" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:08</v>
+        <v>2:46</v>
       </c>
       <c r="H78" t="str">
-        <v>Romeo Santos and 2 more</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>7:31</v>
+        <v>2:42</v>
       </c>
       <c r="H79" t="str">
-        <v>Jacob Collier</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:21</v>
+        <v>3:04</v>
       </c>
       <c r="H80" t="str">
-        <v>Gabi Sklar</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:36</v>
+        <v>2:59</v>
       </c>
       <c r="H81" t="str">
-        <v>YUNGBLUD</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B82" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>5:06</v>
+        <v>2:22</v>
       </c>
       <c r="H82" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:17</v>
+        <v>3:53</v>
       </c>
       <c r="H83" t="str">
-        <v>Marc Anthony and 2 more</v>
+        <v>Roxette</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:20</v>
+        <v>2:28</v>
       </c>
       <c r="H84" t="str">
-        <v>georgemichael</v>
+        <v>Marcin</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:50</v>
+        <v>2:47</v>
       </c>
       <c r="H85" t="str">
-        <v>Cliff Richard</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,33 +3623,33 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B86" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:14</v>
+        <v>3:40</v>
       </c>
       <c r="H86" t="str">
-        <v>Freya Ridings</v>
+        <v>Laufey</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,33 +3661,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:37</v>
+        <v>2:49</v>
       </c>
       <c r="H87" t="str">
-        <v>Jessie Ware</v>
+        <v>Ava Max</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B88" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>13 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:16</v>
+        <v>4:49</v>
       </c>
       <c r="H88" t="str">
-        <v>Alan Walker</v>
+        <v>U2</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,33 +3737,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:22</v>
+        <v>3:35</v>
       </c>
       <c r="H89" t="str">
-        <v>The Neighbourhood</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Suburban Requiem</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:40</v>
+        <v>2:59</v>
       </c>
       <c r="H90" t="str">
-        <v>YUNGBLUD</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:02</v>
+        <v>4:38</v>
       </c>
       <c r="H91" t="str">
-        <v>Calum Scott</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:12</v>
+        <v>3:46</v>
       </c>
       <c r="H92" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:38</v>
+        <v>3:08</v>
       </c>
       <c r="H93" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:40</v>
+        <v>5:32</v>
       </c>
       <c r="H94" t="str">
-        <v>Cannons</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:57</v>
+        <v>4:39</v>
       </c>
       <c r="H95" t="str">
-        <v>Mimi Webb</v>
+        <v>georgemichael</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:13</v>
+        <v>3:40</v>
       </c>
       <c r="H96" t="str">
-        <v>Jorja Smith</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:12</v>
+        <v>3:57</v>
       </c>
       <c r="H97" t="str">
-        <v>Sam Williams</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:55</v>
+        <v>2:27</v>
       </c>
       <c r="H98" t="str">
-        <v>YUNGBLUD</v>
+        <v>070 Shake</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:51</v>
+        <v>4:49</v>
       </c>
       <c r="H99" t="str">
-        <v>Megan Moroney</v>
+        <v>georgemichael</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:51</v>
+        <v>5:52</v>
       </c>
       <c r="H100" t="str">
-        <v>Nico Santos</v>
+        <v>georgemichael</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,21 +4193,21 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4216,10 +4216,10 @@
         <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:24</v>
+        <v>3:22</v>
       </c>
       <c r="H101" t="str">
-        <v>REALITY CLUB</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="102">
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/american-girls/1870984036</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/new-religion/1878015314</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/tweak/1875414202</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/attitude/1879665813</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/kerosene/1878542369</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/feel-better/1882859321</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/san-charly/1880240036</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/400-cities/1872496994</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/breezer/1858041251</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/angel/1877142613</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/bleed/1871562994</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/wish/1876893995</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/fantasy/1880786931</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/deleted/1880220796</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/to-myself/1880458049</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/taboo/1880750236</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/be-mine/1877013471</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/still-do/1877250216</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/havin/1878165152</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/noise/1878401282</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/good-friend/1869047706</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/tellme/1880089949</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/soren/1876596568</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/gloria/1842363092</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/tough/1878716666</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/no-hook/1880501939</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E198" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:48</v>
@@ -477,7 +477,7 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 hours ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:58</v>
@@ -515,7 +515,7 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:33</v>
@@ -553,7 +553,7 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:01</v>
@@ -629,7 +629,7 @@
         <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B7" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>2:54</v>
@@ -667,7 +667,7 @@
         <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>2:46</v>
@@ -705,7 +705,7 @@
         <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -781,7 +781,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:16</v>
@@ -933,7 +933,7 @@
         <v>Matt Hansen - SAME TIME (Official Live Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=_cQOUDPhC_o</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:46</v>
@@ -971,7 +971,7 @@
         <v>Mike Posner - I Went Back To Ibiza (Official Lyric Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=UDL6SEW4xKU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v>4:01</v>
@@ -1009,7 +1009,7 @@
         <v>Katelyn Tarver - Trust Myself (Live Performance Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=GtS_T6vl6GI</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:23</v>
@@ -1047,7 +1047,7 @@
         <v>almost monday - leaving is easy (official video)</v>
       </c>
       <c r="B18" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=LqKGqnnjwVw</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:39</v>
@@ -1085,7 +1085,7 @@
         <v>Anne Wilson - Still Do (with Cole Swindell) (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=_TDAMdpCcis</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:04</v>
@@ -1123,7 +1123,7 @@
         <v>vaultboy - DELETED (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=aVNt_k2plm4</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v>3:25</v>
@@ -1161,7 +1161,7 @@
         <v>The Warning - Kerosene (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=xGRH6MvX2Oo</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v>3:49</v>
@@ -1199,7 +1199,7 @@
         <v>aron! - Wonderful Thing (City View Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=0_nllPJGCsE</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
         <v>2:14</v>
@@ -2719,7 +2719,7 @@
         <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>4:03</v>
@@ -2757,7 +2757,7 @@
         <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:31</v>
@@ -2795,7 +2795,7 @@
         <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B64" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>3:22</v>
@@ -2833,7 +2833,7 @@
         <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B65" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>5:49</v>
@@ -2871,7 +2871,7 @@
         <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>3:47</v>
@@ -2909,7 +2909,7 @@
         <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>2:20</v>
@@ -2947,7 +2947,7 @@
         <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
         <v>4:18</v>
@@ -2985,7 +2985,7 @@
         <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>2:39</v>
@@ -3023,7 +3023,7 @@
         <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>3:52</v>
@@ -3061,7 +3061,7 @@
         <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B71" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>4:01</v>
@@ -3213,7 +3213,7 @@
         <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>3:06</v>
@@ -3251,7 +3251,7 @@
         <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B76" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>2:43</v>
@@ -3669,7 +3669,7 @@
         <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
         <v>2:49</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:48</v>
@@ -477,7 +477,7 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>5 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:58</v>
@@ -515,7 +515,7 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:33</v>
@@ -553,7 +553,7 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>9 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>9 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:01</v>
@@ -591,7 +591,7 @@
         <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B6" t="str">
-        <v>11 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>11 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:56</v>
@@ -629,7 +629,7 @@
         <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B7" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>2:54</v>
@@ -667,7 +667,7 @@
         <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>2:46</v>
@@ -705,7 +705,7 @@
         <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>14 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>14 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -743,7 +743,7 @@
         <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B10" t="str">
-        <v>18 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>18 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:21</v>
@@ -781,7 +781,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Performance Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=y8HLQn3YAiw</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v>3:16</v>
@@ -819,7 +819,7 @@
         <v>Johnny Orlando - Have Your Lovin' (Official Audio)</v>
       </c>
       <c r="B12" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=vNk9lO1Fl0k</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v>2:41</v>
@@ -857,7 +857,7 @@
         <v>Russell Dickerson - B.O.A.T. (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=gF4aZUwpb_s</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v>2:29</v>
@@ -895,7 +895,7 @@
         <v>OneRepublic - I Ain’t Worried | Live in Nova’s Red Room</v>
       </c>
       <c r="B14" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=b3NygKKMB0Q</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v>2:43</v>
@@ -1693,7 +1693,7 @@
         <v>Peter Gabriel - What Lies Ahead (Bright-Side Mix)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=_70wPbKbssM</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
         <v>2:53</v>
@@ -1731,7 +1731,7 @@
         <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v>4:30</v>
@@ -2491,7 +2491,7 @@
         <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>3:47</v>
@@ -2529,7 +2529,7 @@
         <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>3:18</v>
@@ -2567,7 +2567,7 @@
         <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:50</v>
@@ -2605,7 +2605,7 @@
         <v>MyKey - Ride With Me</v>
       </c>
       <c r="B59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:24</v>
@@ -2643,7 +2643,7 @@
         <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>2:36</v>
@@ -2681,7 +2681,7 @@
         <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>3:34</v>
@@ -3593,7 +3593,7 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
         <v>2:47</v>
@@ -3631,7 +3631,7 @@
         <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B86" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
         <v>3:40</v>
@@ -3973,7 +3973,7 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B95" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G95" t="str">
         <v>4:39</v>
@@ -4011,7 +4011,7 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B96" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>3:40</v>
@@ -4163,7 +4163,7 @@
         <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B100" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v>5:52</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:48</v>
@@ -477,7 +477,7 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>9 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>9 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:58</v>
@@ -515,7 +515,7 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:33</v>
@@ -553,7 +553,7 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>12 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:01</v>
@@ -591,7 +591,7 @@
         <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B6" t="str">
-        <v>15 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>15 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:56</v>
@@ -629,7 +629,7 @@
         <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B7" t="str">
-        <v>15 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>15 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>2:54</v>
@@ -667,7 +667,7 @@
         <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>15 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>15 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>2:46</v>
@@ -705,7 +705,7 @@
         <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>17 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>17 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -743,7 +743,7 @@
         <v>Depeche Mode – Universal Soldier (Visualiser) – HELP(2)</v>
       </c>
       <c r="B10" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=hm-ZIm7eNpc</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:21</v>
@@ -2453,7 +2453,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>5:12</v>
@@ -3555,7 +3555,7 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B84" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
         <v>2:28</v>
@@ -3707,7 +3707,7 @@
         <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B88" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
         <v>4:49</v>
@@ -4049,7 +4049,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B97" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G97" t="str">
         <v>3:57</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:48</v>
@@ -477,7 +477,7 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:58</v>
@@ -515,7 +515,7 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:33</v>
@@ -553,7 +553,7 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:01</v>
@@ -591,7 +591,7 @@
         <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B6" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:56</v>
@@ -629,7 +629,7 @@
         <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B7" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>2:54</v>
@@ -667,7 +667,7 @@
         <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>2:46</v>
@@ -705,7 +705,7 @@
         <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -1997,7 +1997,7 @@
         <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v>3:11</v>
@@ -3935,7 +3935,7 @@
         <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B94" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>5:32</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:48</v>
@@ -477,7 +477,7 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:58</v>
@@ -515,7 +515,7 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:33</v>
@@ -553,7 +553,7 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:01</v>
@@ -591,7 +591,7 @@
         <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B6" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:56</v>
@@ -629,7 +629,7 @@
         <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B7" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>2:54</v>
@@ -667,7 +667,7 @@
         <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>2:46</v>
@@ -705,7 +705,7 @@
         <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>21 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -1313,7 +1313,7 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=vtuqQ3MBEyQ</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v>2:44</v>
@@ -2415,7 +2415,7 @@
         <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v>3:55</v>
@@ -3175,7 +3175,7 @@
         <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B74" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
         <v>4:50</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:48</v>
@@ -477,7 +477,7 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:58</v>
@@ -515,7 +515,7 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:33</v>
@@ -553,7 +553,7 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:01</v>
@@ -591,7 +591,7 @@
         <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B6" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:56</v>
@@ -629,7 +629,7 @@
         <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B7" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>2:54</v>
@@ -667,7 +667,7 @@
         <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>2:46</v>
@@ -705,7 +705,7 @@
         <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>22 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -1541,7 +1541,7 @@
         <v>Ringo Starr - It’s Been Too Long (Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=aXR078sbCDk</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v>2:43</v>
@@ -2339,7 +2339,7 @@
         <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>4:05</v>
@@ -2377,7 +2377,7 @@
         <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v>2:59</v>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Harry Styles - American Girls (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=o6jQo3-iCao</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v>3:48</v>
@@ -477,7 +477,7 @@
         <v>Morrissey - The Monsters of Pig Alley (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wsq3ovBKxMY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:58</v>
@@ -515,7 +515,7 @@
         <v>Ellise - Littlepill (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>17 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=vR3hP5jHzTA</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>17 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v>2:33</v>
@@ -553,7 +553,7 @@
         <v>The Doobie Brothers - Learn to Let Go (Live from The Late Show)</v>
       </c>
       <c r="B5" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=ZRFLQY9-p4I</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>18 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v>5:01</v>
@@ -591,7 +591,7 @@
         <v>OneRepublic - Counting Stars | Live in Nova’s Red Room</v>
       </c>
       <c r="B6" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=ToxQ4ktRWz4</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v>4:56</v>
@@ -629,7 +629,7 @@
         <v>Bebe Rexha &amp; Faithless - New Religion (Official Visual)</v>
       </c>
       <c r="B7" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=366CV87TguE</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v>2:54</v>
@@ -667,7 +667,7 @@
         <v>Nathan Evans x Saint PHNX - Country Roads (Official Acoustic Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=RmZ10A3QxT4</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v>2:46</v>
@@ -705,7 +705,7 @@
         <v>R3HAB x RHODES - Right here... (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=-qR0LPNxXC8</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v>2:56</v>
@@ -1237,7 +1237,7 @@
         <v>Bazzi - moment (Official Music Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=h0GlEE1n43Y</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>2:43</v>
@@ -1275,7 +1275,7 @@
         <v>Sting - Shape of My Heart (Live at the Rijksmuseum)</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=hKks7D7DVZw</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v>4:43</v>
@@ -1351,7 +1351,7 @@
         <v>Jessie Ware - Ride (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=HE8XRHOGhtQ</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v>4:37</v>
@@ -1389,7 +1389,7 @@
         <v>Cannons - These Nights (Live at The Fonda)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=J5PAtczdmFY</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v>4:52</v>
@@ -1427,7 +1427,7 @@
         <v>Kim Petras - "Get Some (feat. Cortisa Star)" [Pretour]</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=G9kJ9t8kfH4</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
         <v>2:13</v>
@@ -1465,7 +1465,7 @@
         <v>Vanessa Carlton - "Great House" [Official Music Video]</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=zLAZR346xdI</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
         <v>3:19</v>
@@ -1503,7 +1503,7 @@
         <v>Kiana Ledé - Jury [Official Visualizer]</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=6C9-YTWO-TQ</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v>2:31</v>
@@ -1617,7 +1617,7 @@
         <v>Armin van Buuren - Here For You (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=Lh4mbBwA_Qo</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v>3:55</v>
@@ -1655,7 +1655,7 @@
         <v>Demi Lovato - Really Don't Care (Live)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=Vvp1R7HwkfI</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v>3:52</v>
@@ -1921,7 +1921,7 @@
         <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>3:31</v>
@@ -1959,7 +1959,7 @@
         <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v>3:00</v>
@@ -2073,7 +2073,7 @@
         <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>5:03</v>
@@ -2111,7 +2111,7 @@
         <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>4:50</v>
@@ -2149,7 +2149,7 @@
         <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>4:53</v>
@@ -2187,7 +2187,7 @@
         <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:04</v>
@@ -2225,7 +2225,7 @@
         <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>4:32</v>
@@ -2263,7 +2263,7 @@
         <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:47</v>
@@ -2301,7 +2301,7 @@
         <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>3:40</v>
@@ -3137,7 +3137,7 @@
         <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>4:03</v>
@@ -3327,7 +3327,7 @@
         <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>2:46</v>
@@ -3365,7 +3365,7 @@
         <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>2:42</v>
@@ -3403,7 +3403,7 @@
         <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
         <v>3:04</v>
@@ -3441,7 +3441,7 @@
         <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>2:59</v>
@@ -3479,7 +3479,7 @@
         <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B82" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
         <v>2:22</v>
@@ -3517,7 +3517,7 @@
         <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B83" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
         <v>3:53</v>
@@ -3745,7 +3745,7 @@
         <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:35</v>
@@ -3783,7 +3783,7 @@
         <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B90" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
         <v>2:59</v>
@@ -3821,7 +3821,7 @@
         <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
         <v>4:38</v>
@@ -3859,7 +3859,7 @@
         <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B92" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>3:46</v>
@@ -3897,7 +3897,7 @@
         <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:08</v>
@@ -4087,7 +4087,7 @@
         <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B98" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v>2:27</v>
@@ -4125,7 +4125,7 @@
         <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B99" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v>4:49</v>
